--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -386,7 +386,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="str">
-        <v>multi-venue - Sales Summary - 2026-06-28/2026-06-28</v>
+        <v>multi-venue - Sales Summary - 2026-06-29/2026-06-29</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -411,22 +411,22 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
-        <v>#004 Weston Town Center FL</v>
+        <v>#002 American Dream Mall NJ</v>
       </c>
       <c r="B3" t="str">
-        <v>3,747.41</v>
+        <v>2,569.03</v>
       </c>
       <c r="C3" t="str">
-        <v>3,746.63</v>
+        <v>2,564.37</v>
       </c>
       <c r="D3" t="str">
-        <v>0.78</v>
+        <v>4.66</v>
       </c>
       <c r="E3" t="str">
-        <v>55.43</v>
+        <v>34.64</v>
       </c>
       <c r="F3" t="str">
-        <v>222</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -434,119 +434,119 @@
         <v>#001 Florida Mall Orlando FL</v>
       </c>
       <c r="B4" t="str">
-        <v>3,055.25</v>
+        <v>1,975.47</v>
       </c>
       <c r="C4" t="str">
-        <v>3,050.35</v>
+        <v>1,968.87</v>
       </c>
       <c r="D4" t="str">
-        <v>4.90</v>
+        <v>6.60</v>
       </c>
       <c r="E4" t="str">
-        <v>48.94</v>
+        <v>8.99</v>
       </c>
       <c r="F4" t="str">
-        <v>190</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
-        <v>#002 American Dream Mall NJ</v>
+        <v>#003 Sawgrass Mills Mall FL</v>
       </c>
       <c r="B5" t="str">
-        <v>4,198.38</v>
+        <v>2,883.97</v>
       </c>
       <c r="C5" t="str">
-        <v>4,196.60</v>
+        <v>2,883.11</v>
       </c>
       <c r="D5" t="str">
-        <v>1.78</v>
+        <v>0.86</v>
       </c>
       <c r="E5" t="str">
-        <v>86.65</v>
+        <v>18.18</v>
       </c>
       <c r="F5" t="str">
-        <v>228</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
-        <v>#005 Vineland Orlando FL</v>
+        <v>#006 Aventura, FL</v>
       </c>
       <c r="B6" t="str">
-        <v>0.00</v>
+        <v>975.48</v>
       </c>
       <c r="C6" t="str">
-        <v>0.00</v>
+        <v>973.44</v>
       </c>
       <c r="D6" t="str">
-        <v>0.00</v>
+        <v>2.04</v>
       </c>
       <c r="E6" t="str">
         <v>0.00</v>
       </c>
       <c r="F6" t="str">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
-        <v>Lucciano's Vineland 2026</v>
+        <v>#004 Weston Town Center FL</v>
       </c>
       <c r="B7" t="str">
-        <v>1,857.90</v>
+        <v>1,270.54</v>
       </c>
       <c r="C7" t="str">
-        <v>1,857.90</v>
+        <v>1,268.78</v>
       </c>
       <c r="D7" t="str">
-        <v>0.00</v>
+        <v>1.76</v>
       </c>
       <c r="E7" t="str">
-        <v>0.00</v>
+        <v>25.37</v>
       </c>
       <c r="F7" t="str">
-        <v>136</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
-        <v>#006 Aventura, FL</v>
+        <v>#005 Vineland Orlando FL</v>
       </c>
       <c r="B8" t="str">
-        <v>2,799.63</v>
+        <v>0.00</v>
       </c>
       <c r="C8" t="str">
-        <v>2,798.46</v>
+        <v>0.00</v>
       </c>
       <c r="D8" t="str">
-        <v>1.17</v>
+        <v>0.00</v>
       </c>
       <c r="E8" t="str">
-        <v>80.02</v>
+        <v>0.00</v>
       </c>
       <c r="F8" t="str">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
-        <v>#003 Sawgrass Mills Mall FL</v>
+        <v>Lucciano's Vineland 2026</v>
       </c>
       <c r="B9" t="str">
-        <v>4,544.91</v>
+        <v>1,127.12</v>
       </c>
       <c r="C9" t="str">
-        <v>4,530.60</v>
+        <v>1,127.12</v>
       </c>
       <c r="D9" t="str">
-        <v>14.31</v>
+        <v>0.00</v>
       </c>
       <c r="E9" t="str">
-        <v>47.35</v>
+        <v>0.00</v>
       </c>
       <c r="F9" t="str">
-        <v>270</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -554,19 +554,19 @@
         <v>REPORT SUMMARY (7 entries)</v>
       </c>
       <c r="B10" t="str">
-        <v>20,203.48</v>
+        <v>10,801.61</v>
       </c>
       <c r="C10" t="str">
-        <v>20,180.54</v>
+        <v>10,785.69</v>
       </c>
       <c r="D10" t="str">
-        <v>22.94</v>
+        <v>15.92</v>
       </c>
       <c r="E10" t="str">
-        <v>318.39</v>
+        <v>87.18</v>
       </c>
       <c r="F10" t="str">
-        <v>1,166</v>
+        <v>698</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -386,7 +386,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="str">
-        <v>multi-venue - Sales Summary - 2026-06-29/2026-06-29</v>
+        <v>multi-venue - Sales Summary - 2026-06-30/2026-06-30</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -411,142 +411,142 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
-        <v>#002 American Dream Mall NJ</v>
+        <v>#005 Vineland Orlando FL</v>
       </c>
       <c r="B3" t="str">
-        <v>2,569.03</v>
+        <v>0.00</v>
       </c>
       <c r="C3" t="str">
-        <v>2,564.37</v>
+        <v>0.00</v>
       </c>
       <c r="D3" t="str">
-        <v>4.66</v>
+        <v>0.00</v>
       </c>
       <c r="E3" t="str">
-        <v>34.64</v>
+        <v>0.00</v>
       </c>
       <c r="F3" t="str">
-        <v>142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
-        <v>#001 Florida Mall Orlando FL</v>
+        <v>Lucciano's Vineland 2026</v>
       </c>
       <c r="B4" t="str">
-        <v>1,975.47</v>
+        <v>1,455.34</v>
       </c>
       <c r="C4" t="str">
-        <v>1,968.87</v>
+        <v>1,455.34</v>
       </c>
       <c r="D4" t="str">
-        <v>6.60</v>
+        <v>0.00</v>
       </c>
       <c r="E4" t="str">
-        <v>8.99</v>
+        <v>25.97</v>
       </c>
       <c r="F4" t="str">
-        <v>137</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
-        <v>#003 Sawgrass Mills Mall FL</v>
+        <v>#001 Florida Mall Orlando FL</v>
       </c>
       <c r="B5" t="str">
-        <v>2,883.97</v>
+        <v>2,609.29</v>
       </c>
       <c r="C5" t="str">
-        <v>2,883.11</v>
+        <v>2,605.88</v>
       </c>
       <c r="D5" t="str">
-        <v>0.86</v>
+        <v>3.41</v>
       </c>
       <c r="E5" t="str">
-        <v>18.18</v>
+        <v>23.56</v>
       </c>
       <c r="F5" t="str">
-        <v>179</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
-        <v>#006 Aventura, FL</v>
+        <v>#004 Weston Town Center FL</v>
       </c>
       <c r="B6" t="str">
-        <v>975.48</v>
+        <v>2,714.06</v>
       </c>
       <c r="C6" t="str">
-        <v>973.44</v>
+        <v>2,711.42</v>
       </c>
       <c r="D6" t="str">
-        <v>2.04</v>
+        <v>2.64</v>
       </c>
       <c r="E6" t="str">
-        <v>0.00</v>
+        <v>8.79</v>
       </c>
       <c r="F6" t="str">
-        <v>60</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
-        <v>#004 Weston Town Center FL</v>
+        <v>#003 Sawgrass Mills Mall FL</v>
       </c>
       <c r="B7" t="str">
-        <v>1,270.54</v>
+        <v>3,494.62</v>
       </c>
       <c r="C7" t="str">
-        <v>1,268.78</v>
+        <v>3,492.90</v>
       </c>
       <c r="D7" t="str">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="E7" t="str">
-        <v>25.37</v>
+        <v>89.50</v>
       </c>
       <c r="F7" t="str">
-        <v>87</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
-        <v>#005 Vineland Orlando FL</v>
+        <v>#006 Aventura, FL</v>
       </c>
       <c r="B8" t="str">
-        <v>0.00</v>
+        <v>1,360.32</v>
       </c>
       <c r="C8" t="str">
-        <v>0.00</v>
+        <v>1,358.38</v>
       </c>
       <c r="D8" t="str">
-        <v>0.00</v>
+        <v>1.94</v>
       </c>
       <c r="E8" t="str">
         <v>0.00</v>
       </c>
       <c r="F8" t="str">
-        <v>0</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
-        <v>Lucciano's Vineland 2026</v>
+        <v>#002 American Dream Mall NJ</v>
       </c>
       <c r="B9" t="str">
-        <v>1,127.12</v>
+        <v>2,528.91</v>
       </c>
       <c r="C9" t="str">
-        <v>1,127.12</v>
+        <v>2,521.04</v>
       </c>
       <c r="D9" t="str">
-        <v>0.00</v>
+        <v>7.87</v>
       </c>
       <c r="E9" t="str">
-        <v>0.00</v>
+        <v>49.45</v>
       </c>
       <c r="F9" t="str">
-        <v>93</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -554,19 +554,19 @@
         <v>REPORT SUMMARY (7 entries)</v>
       </c>
       <c r="B10" t="str">
-        <v>10,801.61</v>
+        <v>14,162.54</v>
       </c>
       <c r="C10" t="str">
-        <v>10,785.69</v>
+        <v>14,144.96</v>
       </c>
       <c r="D10" t="str">
-        <v>15.92</v>
+        <v>17.58</v>
       </c>
       <c r="E10" t="str">
-        <v>87.18</v>
+        <v>197.27</v>
       </c>
       <c r="F10" t="str">
-        <v>698</v>
+        <v>826</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -4,15 +4,98 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="sheet1" state="visible" r:id="rId3"/>
+    <sheet sheetId="1" name="Sales Summary" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-07-01/2026-07-01</t>
+  </si>
+  <si>
+    <t>Venue Name</t>
+  </si>
+  <si>
+    <t>Gross Sales</t>
+  </si>
+  <si>
+    <t>Net Sales</t>
+  </si>
+  <si>
+    <t>Discounts</t>
+  </si>
+  <si>
+    <t>Voids</t>
+  </si>
+  <si>
+    <t>Bill Count</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>1,118.44</t>
+  </si>
+  <si>
+    <t>1,117.46</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>2,824.24</t>
+  </si>
+  <si>
+    <t>2,816.52</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>2,320.63</t>
+  </si>
+  <si>
+    <t>2,320.23</t>
+  </si>
+  <si>
+    <t>#005 Vineland Orlando FL</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,378.49</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>4,011.26</t>
+  </si>
+  <si>
+    <t>4,006.41</t>
+  </si>
+  <si>
+    <t>REPORT SUMMARY (7 entries)</t>
+  </si>
+  <si>
+    <t>12,633.82</t>
+  </si>
+  <si>
+    <t>12,619.07</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts x14ac:knownFonts="1" count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -382,191 +465,192 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="str">
-        <v>multi-venue - Sales Summary - 2026-06-30/2026-06-30</v>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="str">
-        <v>"Venue Name"</v>
-      </c>
-      <c r="B2" t="str">
-        <v>"Gross Sales"</v>
-      </c>
-      <c r="C2" t="str">
-        <v>"Net Sales"</v>
-      </c>
-      <c r="D2" t="str">
-        <v>"Discounts"</v>
-      </c>
-      <c r="E2" t="str">
-        <v>"Voids"</v>
-      </c>
-      <c r="F2" t="str">
-        <v>"Bill Count"</v>
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="str">
-        <v>#005 Vineland Orlando FL</v>
-      </c>
-      <c r="B3" t="str">
-        <v>0.00</v>
-      </c>
-      <c r="C3" t="str">
-        <v>0.00</v>
-      </c>
-      <c r="D3" t="str">
-        <v>0.00</v>
-      </c>
-      <c r="E3" t="str">
-        <v>0.00</v>
-      </c>
-      <c r="F3" t="str">
-        <v>0</v>
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3">
+        <v>0.98</v>
+      </c>
+      <c r="E3">
+        <v>74.52</v>
+      </c>
+      <c r="F3">
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="str">
-        <v>Lucciano's Vineland 2026</v>
-      </c>
-      <c r="B4" t="str">
-        <v>1,455.34</v>
-      </c>
-      <c r="C4" t="str">
-        <v>1,455.34</v>
-      </c>
-      <c r="D4" t="str">
-        <v>0.00</v>
-      </c>
-      <c r="E4" t="str">
-        <v>25.97</v>
-      </c>
-      <c r="F4" t="str">
-        <v>110</v>
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4">
+        <v>7.72</v>
+      </c>
+      <c r="E4">
+        <v>9.85</v>
+      </c>
+      <c r="F4">
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="str">
-        <v>#001 Florida Mall Orlando FL</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2,609.29</v>
-      </c>
-      <c r="C5" t="str">
-        <v>2,605.88</v>
-      </c>
-      <c r="D5" t="str">
-        <v>3.41</v>
-      </c>
-      <c r="E5" t="str">
-        <v>23.56</v>
-      </c>
-      <c r="F5" t="str">
-        <v>172</v>
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5">
+        <v>980.76</v>
+      </c>
+      <c r="C5">
+        <v>979.96</v>
+      </c>
+      <c r="D5">
+        <v>0.8</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="str">
-        <v>#004 Weston Town Center FL</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2,714.06</v>
-      </c>
-      <c r="C6" t="str">
-        <v>2,711.42</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2.64</v>
-      </c>
-      <c r="E6" t="str">
-        <v>8.79</v>
-      </c>
-      <c r="F6" t="str">
-        <v>104</v>
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>0.4</v>
+      </c>
+      <c r="E6">
+        <v>7.99</v>
+      </c>
+      <c r="F6">
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="str">
-        <v>#003 Sawgrass Mills Mall FL</v>
-      </c>
-      <c r="B7" t="str">
-        <v>3,494.62</v>
-      </c>
-      <c r="C7" t="str">
-        <v>3,492.90</v>
-      </c>
-      <c r="D7" t="str">
-        <v>1.72</v>
-      </c>
-      <c r="E7" t="str">
-        <v>89.50</v>
-      </c>
-      <c r="F7" t="str">
-        <v>233</v>
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="str">
-        <v>#006 Aventura, FL</v>
-      </c>
-      <c r="B8" t="str">
-        <v>1,360.32</v>
-      </c>
-      <c r="C8" t="str">
-        <v>1,358.38</v>
-      </c>
-      <c r="D8" t="str">
-        <v>1.94</v>
-      </c>
-      <c r="E8" t="str">
-        <v>0.00</v>
-      </c>
-      <c r="F8" t="str">
-        <v>69</v>
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>66.62</v>
+      </c>
+      <c r="F8">
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="str">
-        <v>#002 American Dream Mall NJ</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2,528.91</v>
-      </c>
-      <c r="C9" t="str">
-        <v>2,521.04</v>
-      </c>
-      <c r="D9" t="str">
-        <v>7.87</v>
-      </c>
-      <c r="E9" t="str">
-        <v>49.45</v>
-      </c>
-      <c r="F9" t="str">
-        <v>138</v>
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9">
+        <v>4.85</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>265</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="str">
-        <v>REPORT SUMMARY (7 entries)</v>
-      </c>
-      <c r="B10" t="str">
-        <v>14,162.54</v>
-      </c>
-      <c r="C10" t="str">
-        <v>14,144.96</v>
-      </c>
-      <c r="D10" t="str">
-        <v>17.58</v>
-      </c>
-      <c r="E10" t="str">
-        <v>197.27</v>
-      </c>
-      <c r="F10" t="str">
-        <v>826</v>
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10">
+        <v>14.75</v>
+      </c>
+      <c r="E10">
+        <v>158.98</v>
+      </c>
+      <c r="F10">
+        <v>790</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
-    <t>multi-venue - Sales Summary - 2026-07-01/2026-07-01</t>
+    <t>multi-venue - Sales Summary - 2026-07-02/2026-07-02</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,61 +34,61 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>2,145.47</t>
+  </si>
+  <si>
+    <t>2,138.95</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>3,784.74</t>
+  </si>
+  <si>
+    <t>3,781.20</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>3,750.94</t>
+  </si>
+  <si>
+    <t>3,737.96</t>
+  </si>
+  <si>
+    <t>#005 Vineland Orlando FL</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>2,656.13</t>
+  </si>
+  <si>
+    <t>2,643.30</t>
+  </si>
+  <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,118.44</t>
-  </si>
-  <si>
-    <t>1,117.46</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>2,824.24</t>
-  </si>
-  <si>
-    <t>2,816.52</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>2,320.63</t>
-  </si>
-  <si>
-    <t>2,320.23</t>
-  </si>
-  <si>
-    <t>#005 Vineland Orlando FL</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,378.49</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>4,011.26</t>
-  </si>
-  <si>
-    <t>4,006.41</t>
+    <t>1,480.83</t>
   </si>
   <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>12,633.82</t>
-  </si>
-  <si>
-    <t>12,619.07</t>
+    <t>14,297.53</t>
+  </si>
+  <si>
+    <t>14,261.66</t>
   </si>
 </sst>
 </file>
@@ -504,13 +504,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>0.98</v>
+        <v>6.52</v>
       </c>
       <c r="E3">
-        <v>74.52</v>
+        <v>15.58</v>
       </c>
       <c r="F3">
-        <v>64</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -524,53 +524,53 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>7.72</v>
+        <v>3.54</v>
       </c>
       <c r="E4">
-        <v>9.85</v>
+        <v>39.76</v>
       </c>
       <c r="F4">
-        <v>134</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="B5">
-        <v>980.76</v>
-      </c>
-      <c r="C5">
-        <v>979.96</v>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>0.8</v>
+        <v>12.98</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>19.7</v>
       </c>
       <c r="F5">
-        <v>68</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
         <v>16</v>
       </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
       <c r="D6">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>7.99</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>151</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -578,10 +578,10 @@
         <v>17</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>479.42</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>479.42</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -590,7 +590,7 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -601,36 +601,36 @@
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>12.83</v>
       </c>
       <c r="E8">
-        <v>66.62</v>
+        <v>7.99</v>
       </c>
       <c r="F8">
-        <v>108</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
         <v>22</v>
       </c>
       <c r="D9">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>60.74</v>
       </c>
       <c r="F9">
-        <v>265</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -644,13 +644,13 @@
         <v>25</v>
       </c>
       <c r="D10">
-        <v>14.75</v>
+        <v>35.87</v>
       </c>
       <c r="E10">
-        <v>158.98</v>
+        <v>143.77</v>
       </c>
       <c r="F10">
-        <v>790</v>
+        <v>835</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-07-02/2026-07-02</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-07-03/2026-07-03</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,61 +34,67 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>3,815.23</t>
+  </si>
+  <si>
+    <t>3,813.13</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>7,256.98</t>
+  </si>
+  <si>
+    <t>7,243.67</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>3,948.46</t>
+  </si>
+  <si>
+    <t>3,942.07</t>
+  </si>
+  <si>
+    <t>#005 Vineland Orlando FL</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,341.61</t>
+  </si>
+  <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>2,145.47</t>
-  </si>
-  <si>
-    <t>2,138.95</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>3,784.74</t>
-  </si>
-  <si>
-    <t>3,781.20</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>3,750.94</t>
-  </si>
-  <si>
-    <t>3,737.96</t>
-  </si>
-  <si>
-    <t>#005 Vineland Orlando FL</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>2,656.13</t>
-  </si>
-  <si>
-    <t>2,643.30</t>
+    <t>2,495.83</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,480.83</t>
+    <t>2,368.30</t>
+  </si>
+  <si>
+    <t>2,365.09</t>
   </si>
   <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>14,297.53</t>
-  </si>
-  <si>
-    <t>14,261.66</t>
+    <t>21,226.41</t>
+  </si>
+  <si>
+    <t>21,201.40</t>
+  </si>
+  <si>
+    <t>1,218</t>
   </si>
 </sst>
 </file>
@@ -504,13 +510,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>6.52</v>
+        <v>2.1</v>
       </c>
       <c r="E3">
-        <v>15.58</v>
+        <v>121.68</v>
       </c>
       <c r="F3">
-        <v>131</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -524,13 +530,13 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>3.54</v>
+        <v>13.31</v>
       </c>
       <c r="E4">
-        <v>39.76</v>
+        <v>12.8</v>
       </c>
       <c r="F4">
-        <v>232</v>
+        <v>369</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -544,13 +550,13 @@
         <v>15</v>
       </c>
       <c r="D5">
-        <v>12.98</v>
+        <v>6.39</v>
       </c>
       <c r="E5">
-        <v>19.7</v>
+        <v>9.59</v>
       </c>
       <c r="F5">
-        <v>178</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -577,40 +583,40 @@
       <c r="A7" t="s">
         <v>17</v>
       </c>
-      <c r="B7">
-        <v>479.42</v>
-      </c>
-      <c r="C7">
-        <v>479.42</v>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>34.45</v>
       </c>
       <c r="F7">
-        <v>41</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
         <v>20</v>
       </c>
       <c r="D8">
-        <v>12.83</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>7.99</v>
+        <v>32.87</v>
       </c>
       <c r="F8">
-        <v>180</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -621,36 +627,36 @@
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="E9">
-        <v>60.74</v>
+        <v>48.45</v>
       </c>
       <c r="F9">
-        <v>73</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10">
-        <v>35.87</v>
+        <v>25.01</v>
       </c>
       <c r="E10">
-        <v>143.77</v>
-      </c>
-      <c r="F10">
-        <v>835</v>
+        <v>259.84</v>
+      </c>
+      <c r="F10" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
   <si>
-    <t>multi-venue - Sales Summary - 2026-07-03/2026-07-03</t>
+    <t>multi-venue - Sales Summary - 2026-07-04/2026-07-04</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,67 +34,67 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>3,958.37</t>
+  </si>
+  <si>
+    <t>3,911.26</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,317.02</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>6,678.43</t>
+  </si>
+  <si>
+    <t>6,674.61</t>
+  </si>
+  <si>
+    <t>#005 Vineland Orlando FL</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>5,019.10</t>
+  </si>
+  <si>
+    <t>5,007.18</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>2,998.00</t>
+  </si>
+  <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>3,815.23</t>
-  </si>
-  <si>
-    <t>3,813.13</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>7,256.98</t>
-  </si>
-  <si>
-    <t>7,243.67</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>3,948.46</t>
-  </si>
-  <si>
-    <t>3,942.07</t>
-  </si>
-  <si>
-    <t>#005 Vineland Orlando FL</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,341.61</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>2,495.83</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
-    <t>2,368.30</t>
-  </si>
-  <si>
-    <t>2,365.09</t>
+    <t>2,812.70</t>
+  </si>
+  <si>
+    <t>2,812.24</t>
   </si>
   <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>21,226.41</t>
-  </si>
-  <si>
-    <t>21,201.40</t>
-  </si>
-  <si>
-    <t>1,218</t>
+    <t>22,783.62</t>
+  </si>
+  <si>
+    <t>22,720.31</t>
+  </si>
+  <si>
+    <t>1,279</t>
   </si>
 </sst>
 </file>
@@ -510,13 +510,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>2.1</v>
+        <v>47.11</v>
       </c>
       <c r="E3">
-        <v>121.68</v>
+        <v>59.53</v>
       </c>
       <c r="F3">
-        <v>236</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -527,41 +527,41 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>13.31</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>12.8</v>
+        <v>35.96</v>
       </c>
       <c r="F4">
-        <v>369</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>14</v>
       </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
       <c r="D5">
-        <v>6.39</v>
+        <v>3.82</v>
       </c>
       <c r="E5">
-        <v>9.59</v>
+        <v>203.66</v>
       </c>
       <c r="F5">
-        <v>234</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -581,22 +581,22 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
         <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>11.92</v>
       </c>
       <c r="E7">
-        <v>34.45</v>
+        <v>29.55</v>
       </c>
       <c r="F7">
-        <v>101</v>
+        <v>310</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -613,10 +613,10 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>32.87</v>
+        <v>108.74</v>
       </c>
       <c r="F8">
-        <v>158</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -630,13 +630,13 @@
         <v>23</v>
       </c>
       <c r="D9">
-        <v>3.21</v>
+        <v>0.46</v>
       </c>
       <c r="E9">
-        <v>48.45</v>
+        <v>7.99</v>
       </c>
       <c r="F9">
-        <v>120</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -650,10 +650,10 @@
         <v>26</v>
       </c>
       <c r="D10">
-        <v>25.01</v>
+        <v>63.31</v>
       </c>
       <c r="E10">
-        <v>259.84</v>
+        <v>445.43</v>
       </c>
       <c r="F10" t="s">
         <v>27</v>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-07-04/2026-07-04</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-07-05/2026-07-05</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,67 +34,61 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>2,112.53</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>3,062.51</t>
+  </si>
+  <si>
+    <t>3,062.16</t>
+  </si>
+  <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>3,958.37</t>
-  </si>
-  <si>
-    <t>3,911.26</t>
+    <t>3,254.71</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>4,368.43</t>
+  </si>
+  <si>
+    <t>4,363.43</t>
+  </si>
+  <si>
+    <t>#005 Vineland Orlando FL</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,317.02</t>
-  </si>
-  <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>6,678.43</t>
-  </si>
-  <si>
-    <t>6,674.61</t>
-  </si>
-  <si>
-    <t>#005 Vineland Orlando FL</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>5,019.10</t>
-  </si>
-  <si>
-    <t>5,007.18</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
-    <t>2,998.00</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>2,812.70</t>
-  </si>
-  <si>
-    <t>2,812.24</t>
+    <t>3,991.06</t>
+  </si>
+  <si>
+    <t>3,988.29</t>
   </si>
   <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>22,783.62</t>
-  </si>
-  <si>
-    <t>22,720.31</t>
-  </si>
-  <si>
-    <t>1,279</t>
+    <t>17,487.62</t>
+  </si>
+  <si>
+    <t>17,479.50</t>
+  </si>
+  <si>
+    <t>1,015</t>
   </si>
 </sst>
 </file>
@@ -507,36 +501,36 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>47.11</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>59.53</v>
+        <v>12.98</v>
       </c>
       <c r="F3">
-        <v>226</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="E4">
-        <v>35.96</v>
+        <v>58.53</v>
       </c>
       <c r="F4">
-        <v>106</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -547,116 +541,116 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D5">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>203.66</v>
+        <v>67.22</v>
       </c>
       <c r="F5">
-        <v>344</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
+      <c r="C6" t="s">
+        <v>16</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>56.14</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" t="s">
-        <v>18</v>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>11.92</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>29.55</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>310</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="B8">
+        <v>698.38</v>
+      </c>
+      <c r="C8">
+        <v>698.38</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>108.74</v>
+        <v>9.99</v>
       </c>
       <c r="F8">
-        <v>119</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
         <v>21</v>
       </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>23</v>
-      </c>
       <c r="D9">
-        <v>0.46</v>
+        <v>2.77</v>
       </c>
       <c r="E9">
-        <v>7.99</v>
+        <v>124.45</v>
       </c>
       <c r="F9">
-        <v>174</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
         <v>24</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10">
+        <v>8.12</v>
+      </c>
+      <c r="E10">
+        <v>329.31</v>
+      </c>
+      <c r="F10" t="s">
         <v>25</v>
-      </c>
-      <c r="C10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10">
-        <v>63.31</v>
-      </c>
-      <c r="E10">
-        <v>445.43</v>
-      </c>
-      <c r="F10" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-07-05/2026-07-05</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-07-06/2026-07-06</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,61 +34,61 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>3,160.30</t>
+  </si>
+  <si>
+    <t>3,159.44</t>
+  </si>
+  <si>
+    <t>#005 Vineland Orlando FL</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>2,031.28</t>
+  </si>
+  <si>
+    <t>2,028.58</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>3,401.67</t>
+  </si>
+  <si>
+    <t>3,399.89</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>1,368.02</t>
+  </si>
+  <si>
+    <t>1,363.60</t>
+  </si>
+  <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>2,112.53</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>3,062.51</t>
-  </si>
-  <si>
-    <t>3,062.16</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>3,254.71</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>4,368.43</t>
-  </si>
-  <si>
-    <t>4,363.43</t>
-  </si>
-  <si>
-    <t>#005 Vineland Orlando FL</t>
-  </si>
-  <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>3,991.06</t>
-  </si>
-  <si>
-    <t>3,988.29</t>
+    <t>1,144.08</t>
   </si>
   <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>17,487.62</t>
-  </si>
-  <si>
-    <t>17,479.50</t>
-  </si>
-  <si>
-    <t>1,015</t>
+    <t>11,863.41</t>
+  </si>
+  <si>
+    <t>11,852.63</t>
   </si>
 </sst>
 </file>
@@ -501,56 +501,56 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="E3">
-        <v>12.98</v>
+        <v>52.95</v>
       </c>
       <c r="F3">
-        <v>104</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
-        <v>11</v>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>58.53</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>193</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
         <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="E5">
-        <v>67.22</v>
+        <v>24.97</v>
       </c>
       <c r="F5">
-        <v>170</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -564,93 +564,93 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>1.78</v>
       </c>
       <c r="E6">
-        <v>56.14</v>
+        <v>99.25</v>
       </c>
       <c r="F6">
-        <v>252</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>16.78</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B8">
-        <v>698.38</v>
+        <v>758.06</v>
       </c>
       <c r="C8">
-        <v>698.38</v>
+        <v>757.04</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="E8">
-        <v>9.99</v>
+        <v>10.19</v>
       </c>
       <c r="F8">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>124.45</v>
+        <v>24.96</v>
       </c>
       <c r="F9">
-        <v>247</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D10">
-        <v>8.12</v>
+        <v>10.78</v>
       </c>
       <c r="E10">
-        <v>329.31</v>
-      </c>
-      <c r="F10" t="s">
-        <v>25</v>
+        <v>229.1</v>
+      </c>
+      <c r="F10">
+        <v>733</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-07-06/2026-07-06</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-07-07/2026-07-07</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -37,58 +37,52 @@
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>3,160.30</t>
-  </si>
-  <si>
-    <t>3,159.44</t>
+    <t>1,929.77</t>
+  </si>
+  <si>
+    <t>1,927.81</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>2,181.09</t>
+  </si>
+  <si>
+    <t>2,177.69</t>
   </si>
   <si>
     <t>#005 Vineland Orlando FL</t>
   </si>
   <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>2,031.28</t>
-  </si>
-  <si>
-    <t>2,028.58</t>
-  </si>
-  <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>3,401.67</t>
-  </si>
-  <si>
-    <t>3,399.89</t>
+    <t>2,205.52</t>
+  </si>
+  <si>
+    <t>2,196.03</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
   </si>
   <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>1,368.02</t>
-  </si>
-  <si>
-    <t>1,363.60</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,144.08</t>
+    <t>1,621.69</t>
   </si>
   <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>11,863.41</t>
-  </si>
-  <si>
-    <t>11,852.63</t>
+    <t>9,408.66</t>
+  </si>
+  <si>
+    <t>9,390.31</t>
   </si>
 </sst>
 </file>
@@ -504,53 +498,53 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>0.86</v>
+        <v>1.96</v>
       </c>
       <c r="E3">
-        <v>52.95</v>
+        <v>19.78</v>
       </c>
       <c r="F3">
-        <v>185</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>7.99</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
         <v>13</v>
       </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
       <c r="D5">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>24.97</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -564,93 +558,93 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>1.78</v>
+        <v>9.49</v>
       </c>
       <c r="E6">
-        <v>99.25</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>194</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
+      <c r="B7">
+        <v>480.44</v>
+      </c>
+      <c r="C7">
+        <v>480.44</v>
       </c>
       <c r="D7">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>16.78</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>80</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B8">
-        <v>758.06</v>
+        <v>990.15</v>
       </c>
       <c r="C8">
-        <v>757.04</v>
+        <v>986.65</v>
       </c>
       <c r="D8">
-        <v>1.02</v>
+        <v>3.5</v>
       </c>
       <c r="E8">
-        <v>10.19</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>45</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>24.96</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>87</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
         <v>23</v>
       </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" t="s">
-        <v>25</v>
-      </c>
       <c r="D10">
-        <v>10.78</v>
+        <v>18.35</v>
       </c>
       <c r="E10">
-        <v>229.1</v>
+        <v>27.77</v>
       </c>
       <c r="F10">
-        <v>733</v>
+        <v>611</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-07-07/2026-07-07</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-07-08/2026-07-08</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,55 +34,61 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#005 Vineland Orlando FL</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>2,146.00</t>
+  </si>
+  <si>
+    <t>2,100.31</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>1,640.08</t>
+  </si>
+  <si>
+    <t>1,637.74</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>2,306.51</t>
+  </si>
+  <si>
+    <t>2,302.41</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>1,929.77</t>
-  </si>
-  <si>
-    <t>1,927.81</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>2,181.09</t>
-  </si>
-  <si>
-    <t>2,177.69</t>
-  </si>
-  <si>
-    <t>#005 Vineland Orlando FL</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>2,205.52</t>
-  </si>
-  <si>
-    <t>2,196.03</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
+    <t>3,716.91</t>
+  </si>
+  <si>
+    <t>3,700.63</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>1,621.69</t>
+    <t>1,297.47</t>
   </si>
   <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>9,408.66</t>
-  </si>
-  <si>
-    <t>9,390.31</t>
+    <t>11,694.27</t>
+  </si>
+  <si>
+    <t>11,625.86</t>
   </si>
 </sst>
 </file>
@@ -491,60 +497,60 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>19.78</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
       <c r="D4">
-        <v>3.4</v>
+        <v>45.69</v>
       </c>
       <c r="E4">
-        <v>7.99</v>
+        <v>8.85</v>
       </c>
       <c r="F4">
-        <v>147</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
       <c r="D5">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>23.83</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -558,13 +564,13 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>9.49</v>
+        <v>4.1</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>23.97</v>
       </c>
       <c r="F6">
-        <v>126</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -572,79 +578,79 @@
         <v>17</v>
       </c>
       <c r="B7">
-        <v>480.44</v>
+        <v>587.3</v>
       </c>
       <c r="C7">
-        <v>480.44</v>
+        <v>587.3</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>7.99</v>
       </c>
       <c r="F7">
-        <v>42</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>18</v>
       </c>
-      <c r="B8">
-        <v>990.15</v>
-      </c>
-      <c r="C8">
-        <v>986.65</v>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
       </c>
       <c r="D8">
-        <v>3.5</v>
+        <v>16.28</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>65</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>51.54</v>
       </c>
       <c r="F9">
-        <v>106</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D10">
-        <v>18.35</v>
+        <v>68.41</v>
       </c>
       <c r="E10">
-        <v>27.77</v>
+        <v>116.18</v>
       </c>
       <c r="F10">
-        <v>611</v>
+        <v>687</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-07-08/2026-07-08</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-07-09/2026-07-09</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,61 +34,67 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>1,950.07</t>
+  </si>
+  <si>
+    <t>1,903.93</t>
+  </si>
+  <si>
     <t>#005 Vineland Orlando FL</t>
   </si>
   <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,084.68</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>1,448.33</t>
+  </si>
+  <si>
+    <t>1,446.19</t>
+  </si>
+  <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>2,146.00</t>
-  </si>
-  <si>
-    <t>2,100.31</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>1,640.08</t>
-  </si>
-  <si>
-    <t>1,637.74</t>
+    <t>2,214.31</t>
+  </si>
+  <si>
+    <t>2,207.38</t>
   </si>
   <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>2,306.51</t>
-  </si>
-  <si>
-    <t>2,302.41</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
+    <t>1,991.34</t>
+  </si>
+  <si>
+    <t>1,990.84</t>
   </si>
   <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>3,716.91</t>
-  </si>
-  <si>
-    <t>3,700.63</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
-    <t>1,297.47</t>
+    <t>3,356.70</t>
+  </si>
+  <si>
+    <t>3,344.65</t>
   </si>
   <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>11,694.27</t>
-  </si>
-  <si>
-    <t>11,625.86</t>
+    <t>12,045.43</t>
+  </si>
+  <si>
+    <t>11,977.67</t>
   </si>
 </sst>
 </file>
@@ -497,40 +503,40 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>46.14</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
         <v>10</v>
       </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
       <c r="D4">
-        <v>45.69</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>8.85</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -541,116 +547,116 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D5">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>23.83</v>
+        <v>44.95</v>
       </c>
       <c r="F5">
-        <v>102</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
       <c r="D6">
-        <v>4.1</v>
+        <v>2.14</v>
       </c>
       <c r="E6">
-        <v>23.97</v>
+        <v>49.95</v>
       </c>
       <c r="F6">
-        <v>160</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="B7">
-        <v>587.3</v>
-      </c>
-      <c r="C7">
-        <v>587.3</v>
+      <c r="C7" t="s">
+        <v>18</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>6.93</v>
       </c>
       <c r="E7">
-        <v>7.99</v>
+        <v>27.05</v>
       </c>
       <c r="F7">
-        <v>59</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8">
-        <v>16.28</v>
+        <v>0.5</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>17.78</v>
       </c>
       <c r="F8">
-        <v>202</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>12.05</v>
       </c>
       <c r="E9">
-        <v>51.54</v>
+        <v>38.08</v>
       </c>
       <c r="F9">
-        <v>58</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D10">
-        <v>68.41</v>
+        <v>67.76</v>
       </c>
       <c r="E10">
-        <v>116.18</v>
+        <v>177.81</v>
       </c>
       <c r="F10">
-        <v>687</v>
+        <v>744</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
   <si>
-    <t>multi-venue - Sales Summary - 2026-07-09/2026-07-09</t>
+    <t>multi-venue - Sales Summary - 2026-07-10/2026-07-10</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,67 +34,67 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#005 Vineland Orlando FL</t>
+  </si>
+  <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>1,950.07</t>
-  </si>
-  <si>
-    <t>1,903.93</t>
-  </si>
-  <si>
-    <t>#005 Vineland Orlando FL</t>
+    <t>3,577.99</t>
+  </si>
+  <si>
+    <t>3,567.04</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>3,008.98</t>
+  </si>
+  <si>
+    <t>3,003.28</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>2,832.06</t>
+  </si>
+  <si>
+    <t>2,818.36</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>3,362.06</t>
+  </si>
+  <si>
+    <t>3,361.66</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>1,732.25</t>
+  </si>
+  <si>
+    <t>1,725.79</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,084.68</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
-    <t>1,448.33</t>
-  </si>
-  <si>
-    <t>1,446.19</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>2,214.31</t>
-  </si>
-  <si>
-    <t>2,207.38</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>1,991.34</t>
-  </si>
-  <si>
-    <t>1,990.84</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>3,356.70</t>
-  </si>
-  <si>
-    <t>3,344.65</t>
+    <t>1,113.11</t>
   </si>
   <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>12,045.43</t>
-  </si>
-  <si>
-    <t>11,977.67</t>
+    <t>15,626.45</t>
+  </si>
+  <si>
+    <t>15,589.24</t>
   </si>
 </sst>
 </file>
@@ -503,40 +503,40 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>46.14</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
       <c r="D4">
-        <v>0</v>
+        <v>10.95</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>54.64</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -547,96 +547,96 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="E5">
-        <v>44.95</v>
+        <v>66.95</v>
       </c>
       <c r="F5">
-        <v>74</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6">
-        <v>2.14</v>
+        <v>13.7</v>
       </c>
       <c r="E6">
-        <v>49.95</v>
+        <v>35.4</v>
       </c>
       <c r="F6">
-        <v>86</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>6.93</v>
+        <v>0.4</v>
       </c>
       <c r="E7">
-        <v>27.05</v>
+        <v>3.69</v>
       </c>
       <c r="F7">
-        <v>133</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>0.5</v>
+        <v>6.46</v>
       </c>
       <c r="E8">
-        <v>17.78</v>
+        <v>45.25</v>
       </c>
       <c r="F8">
-        <v>123</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
         <v>24</v>
       </c>
       <c r="D9">
-        <v>12.05</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>38.08</v>
+        <v>18.98</v>
       </c>
       <c r="F9">
-        <v>213</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -650,13 +650,13 @@
         <v>27</v>
       </c>
       <c r="D10">
-        <v>67.76</v>
+        <v>37.21</v>
       </c>
       <c r="E10">
-        <v>177.81</v>
+        <v>224.91</v>
       </c>
       <c r="F10">
-        <v>744</v>
+        <v>974</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-07-10/2026-07-10</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-07-11/2026-07-11</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,67 +34,64 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>6,038.54</t>
+  </si>
+  <si>
+    <t>6,015.82</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,614.04</t>
+  </si>
+  <si>
     <t>#005 Vineland Orlando FL</t>
   </si>
   <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>3,577.99</t>
-  </si>
-  <si>
-    <t>3,567.04</t>
+    <t>3,171.70</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>3,987.09</t>
   </si>
   <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>3,008.98</t>
-  </si>
-  <si>
-    <t>3,003.28</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>2,832.06</t>
-  </si>
-  <si>
-    <t>2,818.36</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>3,362.06</t>
-  </si>
-  <si>
-    <t>3,361.66</t>
+    <t>4,093.36</t>
+  </si>
+  <si>
+    <t>4,091.58</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,732.25</t>
-  </si>
-  <si>
-    <t>1,725.79</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,113.11</t>
+    <t>3,544.17</t>
+  </si>
+  <si>
+    <t>3,542.95</t>
   </si>
   <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>15,626.45</t>
-  </si>
-  <si>
-    <t>15,589.24</t>
+    <t>22,448.90</t>
+  </si>
+  <si>
+    <t>22,423.18</t>
+  </si>
+  <si>
+    <t>1,296</t>
   </si>
 </sst>
 </file>
@@ -503,160 +500,160 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>22.72</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>92.99</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>10.95</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>54.64</v>
+        <v>7.99</v>
       </c>
       <c r="F4">
-        <v>228</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" t="s">
-        <v>13</v>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>66.95</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>197</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D6">
-        <v>13.7</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>35.4</v>
+        <v>7.79</v>
       </c>
       <c r="F6">
-        <v>165</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D7">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>3.69</v>
+        <v>50.35</v>
       </c>
       <c r="F7">
-        <v>212</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D8">
-        <v>6.46</v>
+        <v>1.78</v>
       </c>
       <c r="E8">
-        <v>45.25</v>
+        <v>31.96</v>
       </c>
       <c r="F8">
-        <v>92</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="E9">
-        <v>18.98</v>
+        <v>9.19</v>
       </c>
       <c r="F9">
-        <v>80</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
         <v>25</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10">
+        <v>25.72</v>
+      </c>
+      <c r="E10">
+        <v>200.27</v>
+      </c>
+      <c r="F10" t="s">
         <v>26</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10">
-        <v>37.21</v>
-      </c>
-      <c r="E10">
-        <v>224.91</v>
-      </c>
-      <c r="F10">
-        <v>974</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-07-11/2026-07-11</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-07-12/2026-07-12</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -37,61 +37,64 @@
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>6,038.54</t>
-  </si>
-  <si>
-    <t>6,015.82</t>
+    <t>3,855.45</t>
+  </si>
+  <si>
+    <t>3,851.01</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>3,369.21</t>
+  </si>
+  <si>
+    <t>3,368.81</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>4,970.54</t>
+  </si>
+  <si>
+    <t>4,964.52</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>2,034.55</t>
+  </si>
+  <si>
+    <t>#005 Vineland Orlando FL</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>3,483.41</t>
+  </si>
+  <si>
+    <t>3,483.05</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,614.04</t>
-  </si>
-  <si>
-    <t>#005 Vineland Orlando FL</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>3,171.70</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>3,987.09</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>4,093.36</t>
-  </si>
-  <si>
-    <t>4,091.58</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
-    <t>3,544.17</t>
-  </si>
-  <si>
-    <t>3,542.95</t>
+    <t>1,386.73</t>
   </si>
   <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>22,448.90</t>
-  </si>
-  <si>
-    <t>22,423.18</t>
-  </si>
-  <si>
-    <t>1,296</t>
+    <t>19,099.89</t>
+  </si>
+  <si>
+    <t>19,088.67</t>
+  </si>
+  <si>
+    <t>1,107</t>
   </si>
 </sst>
 </file>
@@ -507,13 +510,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>22.72</v>
+        <v>4.44</v>
       </c>
       <c r="E3">
-        <v>92.99</v>
+        <v>820.5</v>
       </c>
       <c r="F3">
-        <v>344</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -524,136 +527,136 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E4">
-        <v>7.99</v>
+        <v>25.97</v>
       </c>
       <c r="F4">
-        <v>112</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>6.02</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>30.46</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>7.79</v>
+        <v>10.69</v>
       </c>
       <c r="F6">
-        <v>196</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>50.35</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>255</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D8">
-        <v>1.78</v>
+        <v>0.36</v>
       </c>
       <c r="E8">
-        <v>31.96</v>
+        <v>19.28</v>
       </c>
       <c r="F8">
-        <v>264</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>9.19</v>
+        <v>17.08</v>
       </c>
       <c r="F9">
-        <v>125</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10">
-        <v>25.72</v>
+        <v>11.22</v>
       </c>
       <c r="E10">
-        <v>200.27</v>
+        <v>923.98</v>
       </c>
       <c r="F10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-07-12/2026-07-12</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-07-13/2026-07-13</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,67 +34,64 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>1,963.92</t>
+  </si>
+  <si>
+    <t>1,958.72</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>3,385.85</t>
+  </si>
+  <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>3,855.45</t>
-  </si>
-  <si>
-    <t>3,851.01</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>3,369.21</t>
-  </si>
-  <si>
-    <t>3,368.81</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>4,970.54</t>
-  </si>
-  <si>
-    <t>4,964.52</t>
+    <t>2,082.97</t>
+  </si>
+  <si>
+    <t>2,079.84</t>
+  </si>
+  <si>
+    <t>#005 Vineland Orlando FL</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,167.32</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>1,742.43</t>
+  </si>
+  <si>
+    <t>1,740.87</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>2,034.55</t>
-  </si>
-  <si>
-    <t>#005 Vineland Orlando FL</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>3,483.41</t>
-  </si>
-  <si>
-    <t>3,483.05</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,386.73</t>
+    <t>1,011.27</t>
+  </si>
+  <si>
+    <t>1,010.10</t>
   </si>
   <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>19,099.89</t>
-  </si>
-  <si>
-    <t>19,088.67</t>
-  </si>
-  <si>
-    <t>1,107</t>
+    <t>11,353.76</t>
+  </si>
+  <si>
+    <t>11,342.70</t>
   </si>
 </sst>
 </file>
@@ -510,13 +507,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>4.44</v>
+        <v>5.2</v>
       </c>
       <c r="E3">
-        <v>820.5</v>
+        <v>8.99</v>
       </c>
       <c r="F3">
-        <v>214</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -527,116 +524,116 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>25.97</v>
+        <v>40.86</v>
       </c>
       <c r="F4">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>14</v>
       </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
       <c r="D5">
-        <v>6.02</v>
+        <v>3.13</v>
       </c>
       <c r="E5">
-        <v>30.46</v>
+        <v>20.7</v>
       </c>
       <c r="F5">
-        <v>279</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>10.69</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>101</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>12.34</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
         <v>19</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>20</v>
       </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
       <c r="D8">
-        <v>0.36</v>
+        <v>1.56</v>
       </c>
       <c r="E8">
-        <v>19.28</v>
+        <v>15.58</v>
       </c>
       <c r="F8">
-        <v>194</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
         <v>22</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
       </c>
       <c r="C9" t="s">
         <v>23</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="E9">
-        <v>17.08</v>
+        <v>10.19</v>
       </c>
       <c r="F9">
-        <v>101</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -650,13 +647,13 @@
         <v>26</v>
       </c>
       <c r="D10">
-        <v>11.22</v>
+        <v>11.06</v>
       </c>
       <c r="E10">
-        <v>923.98</v>
-      </c>
-      <c r="F10" t="s">
-        <v>27</v>
+        <v>108.66</v>
+      </c>
+      <c r="F10">
+        <v>717</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-07-13/2026-07-13</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-07-14/2026-07-14</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,64 +34,61 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>2,225.27</t>
+  </si>
+  <si>
+    <t>2,221.62</t>
+  </si>
+  <si>
+    <t>#005 Vineland Orlando FL</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>2,217.15</t>
+  </si>
+  <si>
+    <t>2,207.83</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>1,848.81</t>
+  </si>
+  <si>
+    <t>1,847.68</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>1,963.92</t>
-  </si>
-  <si>
-    <t>1,958.72</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>3,385.85</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>2,082.97</t>
-  </si>
-  <si>
-    <t>2,079.84</t>
-  </si>
-  <si>
-    <t>#005 Vineland Orlando FL</t>
+    <t>2,204.46</t>
+  </si>
+  <si>
+    <t>2,200.76</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,167.32</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>1,742.43</t>
-  </si>
-  <si>
-    <t>1,740.87</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
-    <t>1,011.27</t>
-  </si>
-  <si>
-    <t>1,010.10</t>
+    <t>1,213.77</t>
   </si>
   <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>11,353.76</t>
-  </si>
-  <si>
-    <t>11,342.70</t>
+    <t>10,540.88</t>
+  </si>
+  <si>
+    <t>10,523.08</t>
   </si>
 </sst>
 </file>
@@ -507,93 +504,93 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>5.2</v>
+        <v>3.65</v>
       </c>
       <c r="E3">
-        <v>8.99</v>
+        <v>43.08</v>
       </c>
       <c r="F3">
-        <v>144</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>40.86</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>215</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
       <c r="D5">
-        <v>3.13</v>
+        <v>9.32</v>
       </c>
       <c r="E5">
-        <v>20.7</v>
+        <v>18.27</v>
       </c>
       <c r="F5">
-        <v>107</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
+      <c r="C6" t="s">
+        <v>16</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>65.51</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" t="s">
-        <v>17</v>
+      <c r="B7">
+        <v>831.42</v>
+      </c>
+      <c r="C7">
+        <v>831.42</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>12.34</v>
+        <v>18.98</v>
       </c>
       <c r="F7">
-        <v>94</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -607,13 +604,13 @@
         <v>20</v>
       </c>
       <c r="D8">
-        <v>1.56</v>
+        <v>3.7</v>
       </c>
       <c r="E8">
-        <v>15.58</v>
+        <v>34.96</v>
       </c>
       <c r="F8">
-        <v>101</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -624,36 +621,36 @@
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>10.19</v>
+        <v>16.98</v>
       </c>
       <c r="F9">
-        <v>56</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
         <v>24</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>25</v>
       </c>
-      <c r="C10" t="s">
-        <v>26</v>
-      </c>
       <c r="D10">
-        <v>11.06</v>
+        <v>17.8</v>
       </c>
       <c r="E10">
-        <v>108.66</v>
+        <v>197.78</v>
       </c>
       <c r="F10">
-        <v>717</v>
+        <v>679</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
-    <t>multi-venue - Sales Summary - 2026-07-14/2026-07-14</t>
+    <t>multi-venue - Sales Summary - 2026-07-15/2026-07-15</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,61 +34,61 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>2,251.52</t>
+  </si>
+  <si>
+    <t>2,248.12</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>3,695.90</t>
+  </si>
+  <si>
+    <t>3,693.73</t>
+  </si>
+  <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>2,225.27</t>
-  </si>
-  <si>
-    <t>2,221.62</t>
+    <t>2,420.96</t>
+  </si>
+  <si>
+    <t>2,416.10</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>1,654.11</t>
+  </si>
+  <si>
+    <t>1,653.19</t>
   </si>
   <si>
     <t>#005 Vineland Orlando FL</t>
   </si>
   <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>2,217.15</t>
-  </si>
-  <si>
-    <t>2,207.83</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>1,848.81</t>
-  </si>
-  <si>
-    <t>1,847.68</t>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,333.90</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>2,204.46</t>
-  </si>
-  <si>
-    <t>2,200.76</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,213.77</t>
-  </si>
-  <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>10,540.88</t>
-  </si>
-  <si>
-    <t>10,523.08</t>
+    <t>12,347.08</t>
+  </si>
+  <si>
+    <t>12,332.97</t>
   </si>
 </sst>
 </file>
@@ -504,133 +504,133 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="E3">
-        <v>43.08</v>
+        <v>48.93</v>
       </c>
       <c r="F3">
-        <v>125</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>7.79</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>9.32</v>
+        <v>4.86</v>
       </c>
       <c r="E5">
-        <v>18.27</v>
+        <v>58.1</v>
       </c>
       <c r="F5">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D6">
-        <v>1.13</v>
+        <v>0.92</v>
       </c>
       <c r="E6">
-        <v>65.51</v>
+        <v>13.58</v>
       </c>
       <c r="F6">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B7">
-        <v>831.42</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>831.42</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>18.98</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>34.96</v>
+        <v>25.95</v>
       </c>
       <c r="F8">
-        <v>146</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" t="s">
         <v>22</v>
       </c>
-      <c r="C9" t="s">
-        <v>22</v>
+      <c r="B9">
+        <v>990.69</v>
+      </c>
+      <c r="C9">
+        <v>987.93</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="E9">
-        <v>16.98</v>
+        <v>4.45</v>
       </c>
       <c r="F9">
-        <v>88</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -644,13 +644,13 @@
         <v>25</v>
       </c>
       <c r="D10">
-        <v>17.8</v>
+        <v>14.11</v>
       </c>
       <c r="E10">
-        <v>197.78</v>
+        <v>158.8</v>
       </c>
       <c r="F10">
-        <v>679</v>
+        <v>732</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-07-15/2026-07-15</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-07-16/2026-07-16</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,61 +34,67 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>3,274.11</t>
+  </si>
+  <si>
+    <t>3,270.26</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>1,852.09</t>
+  </si>
+  <si>
+    <t>1,845.89</t>
+  </si>
+  <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>2,251.52</t>
-  </si>
-  <si>
-    <t>2,248.12</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>3,695.90</t>
-  </si>
-  <si>
-    <t>3,693.73</t>
+    <t>2,543.62</t>
+  </si>
+  <si>
+    <t>2,542.72</t>
+  </si>
+  <si>
+    <t>#005 Vineland Orlando FL</t>
   </si>
   <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>2,420.96</t>
-  </si>
-  <si>
-    <t>2,416.10</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>1,654.11</t>
-  </si>
-  <si>
-    <t>1,653.19</t>
-  </si>
-  <si>
-    <t>#005 Vineland Orlando FL</t>
+    <t>2,952.54</t>
+  </si>
+  <si>
+    <t>2,940.36</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,333.90</t>
+    <t>1,750.33</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
+    <t>1,414.44</t>
+  </si>
+  <si>
+    <t>1,413.52</t>
+  </si>
+  <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>12,347.08</t>
-  </si>
-  <si>
-    <t>12,332.97</t>
+    <t>13,787.13</t>
+  </si>
+  <si>
+    <t>13,763.08</t>
   </si>
 </sst>
 </file>
@@ -504,13 +510,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="E3">
-        <v>48.93</v>
+        <v>33.15</v>
       </c>
       <c r="F3">
-        <v>144</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -524,13 +530,13 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>2.17</v>
+        <v>6.2</v>
       </c>
       <c r="E4">
-        <v>7.79</v>
+        <v>128.55</v>
       </c>
       <c r="F4">
-        <v>165</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -544,53 +550,53 @@
         <v>15</v>
       </c>
       <c r="D5">
-        <v>4.86</v>
+        <v>0.9</v>
       </c>
       <c r="E5">
-        <v>58.1</v>
+        <v>16.98</v>
       </c>
       <c r="F5">
-        <v>136</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>13.58</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
         <v>19</v>
       </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
       <c r="D7">
-        <v>0</v>
+        <v>12.18</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>109.2</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -607,50 +613,50 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>25.95</v>
+        <v>42.05</v>
       </c>
       <c r="F8">
-        <v>108</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
-      <c r="B9">
-        <v>990.69</v>
-      </c>
-      <c r="C9">
-        <v>987.93</v>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
       </c>
       <c r="D9">
-        <v>2.76</v>
+        <v>0.92</v>
       </c>
       <c r="E9">
-        <v>4.45</v>
+        <v>36.76</v>
       </c>
       <c r="F9">
-        <v>59</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D10">
-        <v>14.11</v>
+        <v>24.05</v>
       </c>
       <c r="E10">
-        <v>158.8</v>
+        <v>366.69</v>
       </c>
       <c r="F10">
-        <v>732</v>
+        <v>857</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-07-16/2026-07-16</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-07-17/2026-07-17</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,67 +34,64 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>2,150.93</t>
+  </si>
+  <si>
+    <t>2,148.44</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>3,661.61</t>
+  </si>
+  <si>
+    <t>3,654.56</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>2,543.99</t>
+  </si>
+  <si>
+    <t>2,537.63</t>
+  </si>
+  <si>
+    <t>#005 Vineland Orlando FL</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,732.54</t>
+  </si>
+  <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>3,274.11</t>
-  </si>
-  <si>
-    <t>3,270.26</t>
+    <t>3,906.13</t>
   </si>
   <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>1,852.09</t>
-  </si>
-  <si>
-    <t>1,845.89</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>2,543.62</t>
-  </si>
-  <si>
-    <t>2,542.72</t>
-  </si>
-  <si>
-    <t>#005 Vineland Orlando FL</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>2,952.54</t>
-  </si>
-  <si>
-    <t>2,940.36</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,750.33</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
-    <t>1,414.44</t>
-  </si>
-  <si>
-    <t>1,413.52</t>
+    <t>3,117.78</t>
   </si>
   <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>13,787.13</t>
-  </si>
-  <si>
-    <t>13,763.08</t>
+    <t>17,112.98</t>
+  </si>
+  <si>
+    <t>17,097.08</t>
+  </si>
+  <si>
+    <t>1,088</t>
   </si>
 </sst>
 </file>
@@ -510,13 +507,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>3.85</v>
+        <v>2.49</v>
       </c>
       <c r="E3">
-        <v>33.15</v>
+        <v>20.16</v>
       </c>
       <c r="F3">
-        <v>208</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -530,13 +527,13 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>6.2</v>
+        <v>7.05</v>
       </c>
       <c r="E4">
-        <v>128.55</v>
+        <v>72.69</v>
       </c>
       <c r="F4">
-        <v>117</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -550,13 +547,13 @@
         <v>15</v>
       </c>
       <c r="D5">
-        <v>0.9</v>
+        <v>6.36</v>
       </c>
       <c r="E5">
-        <v>16.98</v>
+        <v>48.94</v>
       </c>
       <c r="F5">
-        <v>171</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -587,76 +584,76 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D7">
-        <v>12.18</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>109.2</v>
+        <v>46.44</v>
       </c>
       <c r="F7">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
         <v>20</v>
       </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>42.05</v>
+        <v>16.18</v>
       </c>
       <c r="F8">
-        <v>134</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
         <v>22</v>
       </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D9">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>36.76</v>
+        <v>46.74</v>
       </c>
       <c r="F9">
-        <v>79</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
         <v>25</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10">
+        <v>15.9</v>
+      </c>
+      <c r="E10">
+        <v>251.15</v>
+      </c>
+      <c r="F10" t="s">
         <v>26</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10">
-        <v>24.05</v>
-      </c>
-      <c r="E10">
-        <v>366.69</v>
-      </c>
-      <c r="F10">
-        <v>857</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-07-17/2026-07-17</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-07-18/2026-07-18</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,64 +34,67 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#005 Vineland Orlando FL</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>3,835.48</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>8,191.75</t>
+  </si>
+  <si>
+    <t>8,173.26</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>4,196.27</t>
+  </si>
+  <si>
+    <t>4,193.87</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>4,421.97</t>
+  </si>
+  <si>
+    <t>4,420.25</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>2,122.29</t>
+  </si>
+  <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>2,150.93</t>
-  </si>
-  <si>
-    <t>2,148.44</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>3,661.61</t>
-  </si>
-  <si>
-    <t>3,654.56</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>2,543.99</t>
-  </si>
-  <si>
-    <t>2,537.63</t>
-  </si>
-  <si>
-    <t>#005 Vineland Orlando FL</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,732.54</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>3,906.13</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>3,117.78</t>
+    <t>2,717.48</t>
+  </si>
+  <si>
+    <t>2,716.31</t>
   </si>
   <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>17,112.98</t>
-  </si>
-  <si>
-    <t>17,097.08</t>
-  </si>
-  <si>
-    <t>1,088</t>
+    <t>25,485.24</t>
+  </si>
+  <si>
+    <t>25,461.46</t>
+  </si>
+  <si>
+    <t>1,461</t>
   </si>
 </sst>
 </file>
@@ -500,100 +503,100 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>20.16</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D4">
-        <v>7.05</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>72.69</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D5">
-        <v>6.36</v>
+        <v>18.49</v>
       </c>
       <c r="E5">
-        <v>48.94</v>
+        <v>80.55</v>
       </c>
       <c r="F5">
-        <v>181</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>15.98</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
         <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="E7">
-        <v>46.44</v>
+        <v>69.73</v>
       </c>
       <c r="F7">
-        <v>145</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -610,10 +613,10 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>16.18</v>
+        <v>15.98</v>
       </c>
       <c r="F8">
-        <v>247</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -624,36 +627,36 @@
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="E9">
-        <v>46.74</v>
+        <v>18.38</v>
       </c>
       <c r="F9">
-        <v>205</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10">
-        <v>15.9</v>
+        <v>23.78</v>
       </c>
       <c r="E10">
-        <v>251.15</v>
+        <v>200.62</v>
       </c>
       <c r="F10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-07-18/2026-07-18</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-07-19/2026-07-19</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,67 +34,64 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>3,539.50</t>
+  </si>
+  <si>
+    <t>3,536.95</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>2,680.07</t>
+  </si>
+  <si>
+    <t>2,674.77</t>
+  </si>
+  <si>
     <t>#005 Vineland Orlando FL</t>
   </si>
   <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>3,835.48</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>8,191.75</t>
-  </si>
-  <si>
-    <t>8,173.26</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>4,196.27</t>
-  </si>
-  <si>
-    <t>4,193.87</t>
+    <t>3,234.08</t>
   </si>
   <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>4,421.97</t>
-  </si>
-  <si>
-    <t>4,420.25</t>
+    <t>1,615.43</t>
+  </si>
+  <si>
+    <t>1,612.35</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>1,849.22</t>
+  </si>
+  <si>
+    <t>1,847.38</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>2,122.29</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
-    <t>2,717.48</t>
-  </si>
-  <si>
-    <t>2,716.31</t>
+    <t>1,678.87</t>
   </si>
   <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>25,485.24</t>
-  </si>
-  <si>
-    <t>25,461.46</t>
-  </si>
-  <si>
-    <t>1,461</t>
+    <t>14,597.17</t>
+  </si>
+  <si>
+    <t>14,584.40</t>
   </si>
 </sst>
 </file>
@@ -503,80 +500,80 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>103.59</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>8.99</v>
       </c>
       <c r="F4">
-        <v>203</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>18.49</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>80.55</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>424</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
         <v>15</v>
       </c>
       <c r="D6">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>15.98</v>
+        <v>89.69</v>
       </c>
       <c r="F6">
-        <v>273</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -590,13 +587,13 @@
         <v>18</v>
       </c>
       <c r="D7">
-        <v>1.72</v>
+        <v>3.08</v>
       </c>
       <c r="E7">
-        <v>69.73</v>
+        <v>13.58</v>
       </c>
       <c r="F7">
-        <v>272</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -607,36 +604,36 @@
         <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="E8">
-        <v>15.98</v>
+        <v>18.38</v>
       </c>
       <c r="F8">
-        <v>149</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
         <v>23</v>
       </c>
       <c r="D9">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>18.38</v>
+        <v>26.16</v>
       </c>
       <c r="F9">
-        <v>140</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -650,13 +647,13 @@
         <v>26</v>
       </c>
       <c r="D10">
-        <v>23.78</v>
+        <v>12.77</v>
       </c>
       <c r="E10">
-        <v>200.62</v>
-      </c>
-      <c r="F10" t="s">
-        <v>27</v>
+        <v>260.39</v>
+      </c>
+      <c r="F10">
+        <v>930</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-07-19/2026-07-19</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-07-20/2026-07-20</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,64 +34,61 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#005 Vineland Orlando FL</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,679.16</t>
+  </si>
+  <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>3,539.50</t>
-  </si>
-  <si>
-    <t>3,536.95</t>
+    <t>1,658.21</t>
+  </si>
+  <si>
+    <t>1,655.55</t>
   </si>
   <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>2,680.07</t>
-  </si>
-  <si>
-    <t>2,674.77</t>
-  </si>
-  <si>
-    <t>#005 Vineland Orlando FL</t>
+    <t>2,355.37</t>
   </si>
   <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>3,234.08</t>
+    <t>1,667.59</t>
   </si>
   <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>1,615.43</t>
-  </si>
-  <si>
-    <t>1,612.35</t>
+    <t>3,426.57</t>
+  </si>
+  <si>
+    <t>3,419.23</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,849.22</t>
-  </si>
-  <si>
-    <t>1,847.38</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,678.87</t>
+    <t>1,044.26</t>
+  </si>
+  <si>
+    <t>1,042.17</t>
   </si>
   <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>14,597.17</t>
-  </si>
-  <si>
-    <t>14,584.40</t>
+    <t>11,831.16</t>
+  </si>
+  <si>
+    <t>11,819.07</t>
   </si>
 </sst>
 </file>
@@ -500,160 +497,160 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>103.59</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>221</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D4">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>8.99</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>188</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>19.7</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>89.69</v>
+        <v>51.96</v>
       </c>
       <c r="F6">
-        <v>195</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
         <v>16</v>
       </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D7">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>13.58</v>
+        <v>23.37</v>
       </c>
       <c r="F7">
-        <v>112</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
         <v>19</v>
       </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
       <c r="D8">
-        <v>1.84</v>
+        <v>7.34</v>
       </c>
       <c r="E8">
-        <v>18.38</v>
+        <v>94.79</v>
       </c>
       <c r="F8">
-        <v>93</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
         <v>22</v>
       </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>23</v>
-      </c>
       <c r="D9">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="E9">
-        <v>26.16</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>121</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
         <v>24</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>25</v>
       </c>
-      <c r="C10" t="s">
-        <v>26</v>
-      </c>
       <c r="D10">
-        <v>12.77</v>
+        <v>12.09</v>
       </c>
       <c r="E10">
-        <v>260.39</v>
+        <v>189.82</v>
       </c>
       <c r="F10">
-        <v>930</v>
+        <v>743</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-07-20/2026-07-20</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-07-21/2026-07-21</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,61 +34,67 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>2,449.18</t>
+  </si>
+  <si>
+    <t>2,446.68</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>2,631.96</t>
+  </si>
+  <si>
+    <t>2,627.43</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>1,563.90</t>
+  </si>
+  <si>
+    <t>1,563.12</t>
+  </si>
+  <si>
     <t>#005 Vineland Orlando FL</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,679.16</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>1,658.21</t>
-  </si>
-  <si>
-    <t>1,655.55</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>2,355.37</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>1,667.59</t>
+    <t>1,740.07</t>
   </si>
   <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>3,426.57</t>
-  </si>
-  <si>
-    <t>3,419.23</t>
+    <t>3,091.20</t>
+  </si>
+  <si>
+    <t>3,086.41</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,044.26</t>
-  </si>
-  <si>
-    <t>1,042.17</t>
+    <t>1,395.75</t>
+  </si>
+  <si>
+    <t>1,393.71</t>
   </si>
   <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>11,831.16</t>
-  </si>
-  <si>
-    <t>11,819.07</t>
+    <t>12,872.06</t>
+  </si>
+  <si>
+    <t>12,857.42</t>
   </si>
 </sst>
 </file>
@@ -497,160 +503,160 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>34.56</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>47.95</v>
       </c>
       <c r="F4">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>2.66</v>
+        <v>0.78</v>
       </c>
       <c r="E5">
-        <v>19.7</v>
+        <v>1.6</v>
       </c>
       <c r="F5">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>51.96</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>151</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>23.37</v>
+        <v>34.96</v>
       </c>
       <c r="F7">
-        <v>95</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D8">
-        <v>7.34</v>
+        <v>4.79</v>
       </c>
       <c r="E8">
-        <v>94.79</v>
+        <v>9.59</v>
       </c>
       <c r="F8">
-        <v>215</v>
+        <v>197</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D9">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>21.37</v>
       </c>
       <c r="F9">
-        <v>55</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D10">
-        <v>12.09</v>
+        <v>14.64</v>
       </c>
       <c r="E10">
-        <v>189.82</v>
+        <v>150.03</v>
       </c>
       <c r="F10">
-        <v>743</v>
+        <v>817</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-07-21/2026-07-21</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-07-22/2026-07-22</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,67 +34,64 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>3,549.80</t>
+  </si>
+  <si>
+    <t>3,548.14</t>
+  </si>
+  <si>
+    <t>#005 Vineland Orlando FL</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>1,824.67</t>
+  </si>
+  <si>
+    <t>1,821.43</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,527.54</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>1,863.00</t>
+  </si>
+  <si>
+    <t>1,858.85</t>
+  </si>
+  <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>2,449.18</t>
-  </si>
-  <si>
-    <t>2,446.68</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>2,631.96</t>
-  </si>
-  <si>
-    <t>2,627.43</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>1,563.90</t>
-  </si>
-  <si>
-    <t>1,563.12</t>
-  </si>
-  <si>
-    <t>#005 Vineland Orlando FL</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,740.07</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>3,091.20</t>
-  </si>
-  <si>
-    <t>3,086.41</t>
+    <t>2,915.32</t>
+  </si>
+  <si>
+    <t>2,910.32</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,395.75</t>
-  </si>
-  <si>
-    <t>1,393.71</t>
+    <t>1,134.23</t>
   </si>
   <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>12,872.06</t>
-  </si>
-  <si>
-    <t>12,857.42</t>
+    <t>12,814.56</t>
+  </si>
+  <si>
+    <t>12,800.51</t>
   </si>
 </sst>
 </file>
@@ -510,93 +507,93 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>2.5</v>
+        <v>1.66</v>
       </c>
       <c r="E3">
-        <v>34.56</v>
+        <v>31.26</v>
       </c>
       <c r="F3">
-        <v>174</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>47.95</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>137</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
       <c r="D5">
-        <v>0.78</v>
+        <v>3.24</v>
       </c>
       <c r="E5">
-        <v>1.6</v>
+        <v>8.28</v>
       </c>
       <c r="F5">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>136.44</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
         <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="E7">
-        <v>34.96</v>
+        <v>8.85</v>
       </c>
       <c r="F7">
-        <v>139</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -610,13 +607,13 @@
         <v>21</v>
       </c>
       <c r="D8">
-        <v>4.79</v>
+        <v>5</v>
       </c>
       <c r="E8">
-        <v>9.59</v>
+        <v>7.99</v>
       </c>
       <c r="F8">
-        <v>197</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -627,36 +624,36 @@
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D9">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>21.37</v>
+        <v>9.19</v>
       </c>
       <c r="F9">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s">
         <v>25</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>26</v>
       </c>
-      <c r="C10" t="s">
-        <v>27</v>
-      </c>
       <c r="D10">
-        <v>14.64</v>
+        <v>14.05</v>
       </c>
       <c r="E10">
-        <v>150.03</v>
+        <v>202.01</v>
       </c>
       <c r="F10">
-        <v>817</v>
+        <v>766</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
   <si>
-    <t>multi-venue - Sales Summary - 2026-07-22/2026-07-22</t>
+    <t>multi-venue - Sales Summary - 2026-07-23/2026-07-23</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,64 +34,64 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#005 Vineland Orlando FL</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,379.54</t>
+  </si>
+  <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>3,549.80</t>
-  </si>
-  <si>
-    <t>3,548.14</t>
-  </si>
-  <si>
-    <t>#005 Vineland Orlando FL</t>
+    <t>3,066.88</t>
+  </si>
+  <si>
+    <t>3,062.28</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>2,117.16</t>
+  </si>
+  <si>
+    <t>2,108.02</t>
   </si>
   <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>1,824.67</t>
-  </si>
-  <si>
-    <t>1,821.43</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,527.54</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>1,863.00</t>
-  </si>
-  <si>
-    <t>1,858.85</t>
+    <t>1,995.79</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>1,065.17</t>
+  </si>
+  <si>
+    <t>1,064.19</t>
   </si>
   <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>2,915.32</t>
-  </si>
-  <si>
-    <t>2,910.32</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
-    <t>1,134.23</t>
+    <t>2,361.92</t>
+  </si>
+  <si>
+    <t>2,360.72</t>
   </si>
   <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>12,814.56</t>
-  </si>
-  <si>
-    <t>12,800.51</t>
+    <t>11,986.46</t>
+  </si>
+  <si>
+    <t>11,970.54</t>
   </si>
 </sst>
 </file>
@@ -500,80 +500,80 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>31.26</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>198</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>44.7</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
       <c r="D5">
-        <v>3.24</v>
+        <v>4.6</v>
       </c>
       <c r="E5">
-        <v>8.28</v>
+        <v>45.95</v>
       </c>
       <c r="F5">
-        <v>112</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
         <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
       </c>
       <c r="C6" t="s">
         <v>15</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>9.14</v>
       </c>
       <c r="E6">
-        <v>136.44</v>
+        <v>12.45</v>
       </c>
       <c r="F6">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -584,56 +584,56 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>8.85</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
         <v>19</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>20</v>
       </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
       <c r="D8">
-        <v>5</v>
+        <v>0.98</v>
       </c>
       <c r="E8">
-        <v>7.99</v>
+        <v>28.57</v>
       </c>
       <c r="F8">
-        <v>171</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
         <v>22</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
       </c>
       <c r="C9" t="s">
         <v>23</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="E9">
-        <v>9.19</v>
+        <v>43.25</v>
       </c>
       <c r="F9">
-        <v>67</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -647,13 +647,13 @@
         <v>26</v>
       </c>
       <c r="D10">
-        <v>14.05</v>
+        <v>15.92</v>
       </c>
       <c r="E10">
-        <v>202.01</v>
+        <v>174.92</v>
       </c>
       <c r="F10">
-        <v>766</v>
+        <v>736</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-07-23/2026-07-23</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-07-24/2026-07-24</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,64 +34,64 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>2,806.00</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>3,295.56</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>2,567.06</t>
+  </si>
+  <si>
+    <t>2,558.83</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>2,255.10</t>
+  </si>
+  <si>
+    <t>2,254.80</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>3,415.83</t>
+  </si>
+  <si>
+    <t>3,409.72</t>
+  </si>
+  <si>
     <t>#005 Vineland Orlando FL</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,379.54</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>3,066.88</t>
-  </si>
-  <si>
-    <t>3,062.28</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>2,117.16</t>
-  </si>
-  <si>
-    <t>2,108.02</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>1,995.79</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
-    <t>1,065.17</t>
-  </si>
-  <si>
-    <t>1,064.19</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>2,361.92</t>
-  </si>
-  <si>
-    <t>2,360.72</t>
+    <t>1,898.77</t>
   </si>
   <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>11,986.46</t>
-  </si>
-  <si>
-    <t>11,970.54</t>
+    <t>16,238.32</t>
+  </si>
+  <si>
+    <t>16,223.68</t>
+  </si>
+  <si>
+    <t>1,012</t>
   </si>
 </sst>
 </file>
@@ -500,120 +500,120 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>24.97</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>44.7</v>
+        <v>15.38</v>
       </c>
       <c r="F4">
-        <v>96</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5">
-        <v>4.6</v>
+        <v>8.23</v>
       </c>
       <c r="E5">
-        <v>45.95</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>194</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6">
-        <v>9.14</v>
+        <v>0.3</v>
       </c>
       <c r="E6">
-        <v>12.45</v>
+        <v>10.19</v>
       </c>
       <c r="F6">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>111</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" t="s">
         <v>20</v>
       </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
       <c r="D8">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>28.57</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -624,36 +624,36 @@
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>43.25</v>
+        <v>69.51</v>
       </c>
       <c r="F9">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
         <v>24</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>25</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10">
+        <v>14.64</v>
+      </c>
+      <c r="E10">
+        <v>120.05</v>
+      </c>
+      <c r="F10" t="s">
         <v>26</v>
-      </c>
-      <c r="D10">
-        <v>15.92</v>
-      </c>
-      <c r="E10">
-        <v>174.92</v>
-      </c>
-      <c r="F10">
-        <v>736</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-07-24/2026-07-24</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-07-25/2026-07-25</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,64 +34,70 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>3,454.40</t>
+  </si>
+  <si>
+    <t>3,440.79</t>
+  </si>
+  <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>2,806.00</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>3,295.56</t>
+    <t>4,817.20</t>
+  </si>
+  <si>
+    <t>4,811.24</t>
   </si>
   <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>2,567.06</t>
-  </si>
-  <si>
-    <t>2,558.83</t>
+    <t>4,798.55</t>
+  </si>
+  <si>
+    <t>4,782.36</t>
+  </si>
+  <si>
+    <t>#005 Vineland Orlando FL</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,964.26</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>5,012.57</t>
+  </si>
+  <si>
+    <t>5,010.75</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>2,255.10</t>
-  </si>
-  <si>
-    <t>2,254.80</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>3,415.83</t>
-  </si>
-  <si>
-    <t>3,409.72</t>
-  </si>
-  <si>
-    <t>#005 Vineland Orlando FL</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,898.77</t>
+    <t>2,075.83</t>
+  </si>
+  <si>
+    <t>2,072.87</t>
   </si>
   <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>16,238.32</t>
-  </si>
-  <si>
-    <t>16,223.68</t>
-  </si>
-  <si>
-    <t>1,012</t>
+    <t>22,122.81</t>
+  </si>
+  <si>
+    <t>22,082.27</t>
+  </si>
+  <si>
+    <t>1,299</t>
   </si>
 </sst>
 </file>
@@ -504,76 +510,76 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>13.61</v>
       </c>
       <c r="E3">
-        <v>24.97</v>
+        <v>84.02</v>
       </c>
       <c r="F3">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="E4">
-        <v>15.38</v>
+        <v>17.98</v>
       </c>
       <c r="F4">
-        <v>195</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>8.23</v>
+        <v>16.19</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>123.75</v>
       </c>
       <c r="F5">
-        <v>136</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
         <v>16</v>
       </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
       <c r="D6">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>10.19</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>118</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -584,76 +590,76 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D7">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>65.52</v>
       </c>
       <c r="F7">
-        <v>224</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
         <v>20</v>
       </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
+      <c r="C8" t="s">
+        <v>21</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>30.36</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="E9">
-        <v>69.51</v>
+        <v>62.73</v>
       </c>
       <c r="F9">
-        <v>144</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D10">
-        <v>14.64</v>
+        <v>40.54</v>
       </c>
       <c r="E10">
-        <v>120.05</v>
+        <v>384.36</v>
       </c>
       <c r="F10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
-    <t>multi-venue - Sales Summary - 2026-07-25/2026-07-25</t>
+    <t>multi-venue - Sales Summary - 2026-07-26/2026-07-26</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,70 +34,70 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>4,328.67</t>
+  </si>
+  <si>
+    <t>4,322.02</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>3,446.25</t>
+  </si>
+  <si>
+    <t>3,441.45</t>
+  </si>
+  <si>
+    <t>#005 Vineland Orlando FL</t>
+  </si>
+  <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>3,454.40</t>
-  </si>
-  <si>
-    <t>3,440.79</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>4,817.20</t>
-  </si>
-  <si>
-    <t>4,811.24</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>4,798.55</t>
-  </si>
-  <si>
-    <t>4,782.36</t>
-  </si>
-  <si>
-    <t>#005 Vineland Orlando FL</t>
+    <t>3,402.06</t>
+  </si>
+  <si>
+    <t>3,399.18</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,964.26</t>
+    <t>2,432.56</t>
   </si>
   <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>5,012.57</t>
-  </si>
-  <si>
-    <t>5,010.75</t>
+    <t>4,263.86</t>
+  </si>
+  <si>
+    <t>4,261.94</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>2,075.83</t>
-  </si>
-  <si>
-    <t>2,072.87</t>
+    <t>2,317.62</t>
+  </si>
+  <si>
+    <t>2,314.56</t>
   </si>
   <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>22,122.81</t>
-  </si>
-  <si>
-    <t>22,082.27</t>
-  </si>
-  <si>
-    <t>1,299</t>
+    <t>20,191.02</t>
+  </si>
+  <si>
+    <t>20,171.71</t>
+  </si>
+  <si>
+    <t>1,220</t>
   </si>
 </sst>
 </file>
@@ -513,13 +513,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>13.61</v>
+        <v>6.65</v>
       </c>
       <c r="E3">
-        <v>84.02</v>
+        <v>122.44</v>
       </c>
       <c r="F3">
-        <v>200</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -533,53 +533,53 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>5.96</v>
+        <v>4.8</v>
       </c>
       <c r="E4">
-        <v>17.98</v>
+        <v>16.98</v>
       </c>
       <c r="F4">
-        <v>294</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>16.19</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>123.75</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>271</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
         <v>16</v>
       </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
       <c r="D6">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>56.44</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -596,10 +596,10 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>65.52</v>
+        <v>42.85</v>
       </c>
       <c r="F7">
-        <v>130</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -613,13 +613,13 @@
         <v>21</v>
       </c>
       <c r="D8">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="E8">
-        <v>30.36</v>
+        <v>69.02</v>
       </c>
       <c r="F8">
-        <v>297</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -633,13 +633,13 @@
         <v>24</v>
       </c>
       <c r="D9">
-        <v>2.96</v>
+        <v>3.06</v>
       </c>
       <c r="E9">
-        <v>62.73</v>
+        <v>26.37</v>
       </c>
       <c r="F9">
-        <v>107</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -653,10 +653,10 @@
         <v>27</v>
       </c>
       <c r="D10">
-        <v>40.54</v>
+        <v>19.31</v>
       </c>
       <c r="E10">
-        <v>384.36</v>
+        <v>334.1</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-07-26/2026-07-26</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-07-27/2026-07-27</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,70 +34,61 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>3,871.21</t>
+  </si>
+  <si>
+    <t>3,869.39</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>2,085.98</t>
+  </si>
+  <si>
+    <t>2,085.63</t>
+  </si>
+  <si>
+    <t>#005 Vineland Orlando FL</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>1,203.40</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>1,003.70</t>
+  </si>
+  <si>
+    <t>1,000.69</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>4,328.67</t>
-  </si>
-  <si>
-    <t>4,322.02</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>3,446.25</t>
-  </si>
-  <si>
-    <t>3,441.45</t>
-  </si>
-  <si>
-    <t>#005 Vineland Orlando FL</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>3,402.06</t>
-  </si>
-  <si>
-    <t>3,399.18</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>2,432.56</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>4,263.86</t>
-  </si>
-  <si>
-    <t>4,261.94</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
-    <t>2,317.62</t>
-  </si>
-  <si>
-    <t>2,314.56</t>
+    <t>2,424.10</t>
+  </si>
+  <si>
+    <t>2,422.12</t>
   </si>
   <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>20,191.02</t>
-  </si>
-  <si>
-    <t>20,171.71</t>
-  </si>
-  <si>
-    <t>1,220</t>
+    <t>10,993.61</t>
+  </si>
+  <si>
+    <t>10,986.45</t>
   </si>
 </sst>
 </file>
@@ -513,13 +504,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>6.65</v>
+        <v>1.82</v>
       </c>
       <c r="E3">
-        <v>122.44</v>
+        <v>18.18</v>
       </c>
       <c r="F3">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -533,13 +524,13 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>4.8</v>
+        <v>0.35</v>
       </c>
       <c r="E4">
-        <v>16.98</v>
+        <v>45.24</v>
       </c>
       <c r="F4">
-        <v>222</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -570,96 +561,96 @@
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>56.44</v>
+        <v>24.37</v>
       </c>
       <c r="F6">
-        <v>214</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
         <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="E7">
-        <v>42.85</v>
+        <v>44.04</v>
       </c>
       <c r="F7">
-        <v>167</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
+      <c r="B8">
+        <v>405.22</v>
+      </c>
+      <c r="C8">
+        <v>405.22</v>
       </c>
       <c r="D8">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>69.02</v>
+        <v>54.04</v>
       </c>
       <c r="F8">
-        <v>260</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
         <v>22</v>
       </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
       <c r="D9">
-        <v>3.06</v>
+        <v>1.98</v>
       </c>
       <c r="E9">
-        <v>26.37</v>
+        <v>8.55</v>
       </c>
       <c r="F9">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
         <v>25</v>
       </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
-      </c>
       <c r="D10">
-        <v>19.31</v>
+        <v>7.16</v>
       </c>
       <c r="E10">
-        <v>334.1</v>
-      </c>
-      <c r="F10" t="s">
-        <v>28</v>
+        <v>194.42</v>
+      </c>
+      <c r="F10">
+        <v>651</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-07-27/2026-07-27</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-07-28/2026-07-28</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,61 +34,64 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>2,438.86</t>
+  </si>
+  <si>
+    <t>2,431.26</t>
+  </si>
+  <si>
+    <t>#005 Vineland Orlando FL</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>1,542.06</t>
+  </si>
+  <si>
+    <t>1,541.30</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>3,871.21</t>
-  </si>
-  <si>
-    <t>3,869.39</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>2,085.98</t>
-  </si>
-  <si>
-    <t>2,085.63</t>
-  </si>
-  <si>
-    <t>#005 Vineland Orlando FL</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>1,203.40</t>
+    <t>3,208.06</t>
+  </si>
+  <si>
+    <t>3,206.34</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>2,556.12</t>
+  </si>
+  <si>
+    <t>2,544.80</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,003.70</t>
-  </si>
-  <si>
-    <t>1,000.69</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>2,424.10</t>
-  </si>
-  <si>
-    <t>2,422.12</t>
+    <t>1,085.98</t>
+  </si>
+  <si>
+    <t>1,081.46</t>
   </si>
   <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>10,993.61</t>
-  </si>
-  <si>
-    <t>10,986.45</t>
+    <t>11,578.61</t>
+  </si>
+  <si>
+    <t>11,552.69</t>
   </si>
 </sst>
 </file>
@@ -504,153 +507,153 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>1.82</v>
+        <v>7.6</v>
       </c>
       <c r="E3">
-        <v>18.18</v>
+        <v>8.99</v>
       </c>
       <c r="F3">
-        <v>232</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>45.24</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>137</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
       <c r="D5">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>37.16</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
+      <c r="B6">
+        <v>747.53</v>
+      </c>
+      <c r="C6">
+        <v>747.53</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>24.37</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
         <v>16</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" t="s">
-        <v>18</v>
-      </c>
       <c r="D7">
-        <v>3.01</v>
+        <v>1.72</v>
       </c>
       <c r="E7">
-        <v>44.04</v>
+        <v>67.12</v>
       </c>
       <c r="F7">
-        <v>59</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
         <v>19</v>
       </c>
-      <c r="B8">
-        <v>405.22</v>
-      </c>
-      <c r="C8">
-        <v>405.22</v>
+      <c r="C8" t="s">
+        <v>20</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>11.32</v>
       </c>
       <c r="E8">
-        <v>54.04</v>
+        <v>23.6</v>
       </c>
       <c r="F8">
-        <v>30</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9">
-        <v>1.98</v>
+        <v>4.52</v>
       </c>
       <c r="E9">
-        <v>8.55</v>
+        <v>15.17</v>
       </c>
       <c r="F9">
-        <v>126</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10">
-        <v>7.16</v>
+        <v>25.92</v>
       </c>
       <c r="E10">
-        <v>194.42</v>
+        <v>152.04</v>
       </c>
       <c r="F10">
-        <v>651</v>
+        <v>712</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-07-28/2026-07-28</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-07-29/2026-07-29</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,64 +34,61 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>2,943.33</t>
+  </si>
+  <si>
+    <t>2,938.46</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>1,317.44</t>
+  </si>
+  <si>
+    <t>1,315.88</t>
+  </si>
+  <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>2,438.86</t>
-  </si>
-  <si>
-    <t>2,431.26</t>
+    <t>2,065.12</t>
+  </si>
+  <si>
+    <t>2,064.22</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>3,171.38</t>
+  </si>
+  <si>
+    <t>3,168.72</t>
   </si>
   <si>
     <t>#005 Vineland Orlando FL</t>
   </si>
   <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>1,542.06</t>
-  </si>
-  <si>
-    <t>1,541.30</t>
-  </si>
-  <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>3,208.06</t>
-  </si>
-  <si>
-    <t>3,206.34</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>2,556.12</t>
-  </si>
-  <si>
-    <t>2,544.80</t>
+    <t>1,017.73</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,085.98</t>
-  </si>
-  <si>
-    <t>1,081.46</t>
-  </si>
-  <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>11,578.61</t>
-  </si>
-  <si>
-    <t>11,552.69</t>
+    <t>11,221.70</t>
+  </si>
+  <si>
+    <t>11,211.71</t>
   </si>
 </sst>
 </file>
@@ -507,153 +504,153 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>7.6</v>
+        <v>4.87</v>
       </c>
       <c r="E3">
-        <v>8.99</v>
+        <v>19.59</v>
       </c>
       <c r="F3">
-        <v>156</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>0.76</v>
+        <v>0.9</v>
       </c>
       <c r="E5">
-        <v>37.16</v>
+        <v>31.96</v>
       </c>
       <c r="F5">
-        <v>91</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6">
-        <v>747.53</v>
-      </c>
-      <c r="C6">
-        <v>747.53</v>
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>17.7</v>
       </c>
       <c r="F6">
-        <v>58</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>67.12</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>198</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8">
-        <v>11.32</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>23.6</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>140</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" t="s">
         <v>22</v>
       </c>
-      <c r="C9" t="s">
-        <v>23</v>
+      <c r="B9">
+        <v>706.7</v>
+      </c>
+      <c r="C9">
+        <v>706.7</v>
       </c>
       <c r="D9">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>15.17</v>
+        <v>18.98</v>
       </c>
       <c r="F9">
-        <v>69</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
         <v>24</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>25</v>
       </c>
-      <c r="C10" t="s">
-        <v>26</v>
-      </c>
       <c r="D10">
-        <v>25.92</v>
+        <v>9.99</v>
       </c>
       <c r="E10">
-        <v>152.04</v>
+        <v>88.23</v>
       </c>
       <c r="F10">
-        <v>712</v>
+        <v>716</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-07-29/2026-07-29</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-07-30/2026-07-30</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,61 +34,64 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>2,837.05</t>
+  </si>
+  <si>
+    <t>2,826.39</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>3,072.23</t>
+  </si>
+  <si>
+    <t>3,065.43</t>
+  </si>
+  <si>
+    <t>#005 Vineland Orlando FL</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>1,227.55</t>
+  </si>
+  <si>
+    <t>1,220.81</t>
+  </si>
+  <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>2,943.33</t>
-  </si>
-  <si>
-    <t>2,938.46</t>
+    <t>3,320.56</t>
+  </si>
+  <si>
+    <t>3,316.05</t>
   </si>
   <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>1,317.44</t>
-  </si>
-  <si>
-    <t>1,315.88</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>2,065.12</t>
-  </si>
-  <si>
-    <t>2,064.22</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>3,171.38</t>
-  </si>
-  <si>
-    <t>3,168.72</t>
-  </si>
-  <si>
-    <t>#005 Vineland Orlando FL</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,017.73</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
+    <t>1,382.04</t>
+  </si>
+  <si>
+    <t>1,375.24</t>
   </si>
   <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>11,221.70</t>
-  </si>
-  <si>
-    <t>11,211.71</t>
+    <t>12,532.23</t>
+  </si>
+  <si>
+    <t>12,496.72</t>
   </si>
 </sst>
 </file>
@@ -504,13 +507,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>4.87</v>
+        <v>10.66</v>
       </c>
       <c r="E3">
-        <v>19.59</v>
+        <v>27.55</v>
       </c>
       <c r="F3">
-        <v>178</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -524,133 +527,133 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>1.56</v>
+        <v>6.8</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>9.48</v>
       </c>
       <c r="F4">
-        <v>88</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>31.96</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>151</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
+        <v>14</v>
+      </c>
+      <c r="B6">
+        <v>692.8</v>
+      </c>
+      <c r="C6">
+        <v>692.8</v>
       </c>
       <c r="D6">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>17.7</v>
+        <v>17.98</v>
       </c>
       <c r="F6">
-        <v>171</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>6.74</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>62.56</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
         <v>20</v>
       </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
       <c r="D8">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>9.19</v>
       </c>
       <c r="F8">
-        <v>82</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
         <v>22</v>
       </c>
-      <c r="B9">
-        <v>706.7</v>
-      </c>
-      <c r="C9">
-        <v>706.7</v>
+      <c r="C9" t="s">
+        <v>23</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="E9">
-        <v>18.98</v>
+        <v>7.79</v>
       </c>
       <c r="F9">
-        <v>46</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10">
-        <v>9.99</v>
+        <v>35.51</v>
       </c>
       <c r="E10">
-        <v>88.23</v>
+        <v>134.55</v>
       </c>
       <c r="F10">
-        <v>716</v>
+        <v>754</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
-    <t>multi-venue - Sales Summary - 2026-07-30/2026-07-30</t>
+    <t>multi-venue - Sales Summary - 2026-07-31/2026-07-31</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,64 +34,64 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>3,372.34</t>
+  </si>
+  <si>
+    <t>3,366.88</t>
+  </si>
+  <si>
+    <t>#005 Vineland Orlando FL</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>2,805.69</t>
+  </si>
+  <si>
+    <t>2,804.64</t>
+  </si>
+  <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>2,837.05</t>
-  </si>
-  <si>
-    <t>2,826.39</t>
+    <t>3,014.79</t>
+  </si>
+  <si>
+    <t>3,006.18</t>
   </si>
   <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>3,072.23</t>
-  </si>
-  <si>
-    <t>3,065.43</t>
-  </si>
-  <si>
-    <t>#005 Vineland Orlando FL</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
+    <t>3,281.59</t>
+  </si>
+  <si>
+    <t>3,274.39</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,227.55</t>
-  </si>
-  <si>
-    <t>1,220.81</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>3,320.56</t>
-  </si>
-  <si>
-    <t>3,316.05</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>1,382.04</t>
-  </si>
-  <si>
-    <t>1,375.24</t>
+    <t>2,200.19</t>
+  </si>
+  <si>
+    <t>2,197.90</t>
   </si>
   <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>12,532.23</t>
-  </si>
-  <si>
-    <t>12,496.72</t>
+    <t>15,451.78</t>
+  </si>
+  <si>
+    <t>15,427.17</t>
   </si>
 </sst>
 </file>
@@ -507,73 +507,73 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>10.66</v>
+        <v>5.46</v>
       </c>
       <c r="E3">
-        <v>27.55</v>
+        <v>54.86</v>
       </c>
       <c r="F3">
-        <v>152</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>9.48</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>777.18</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>777.18</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>17.98</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
         <v>14</v>
       </c>
-      <c r="B6">
-        <v>692.8</v>
-      </c>
-      <c r="C6">
-        <v>692.8</v>
-      </c>
       <c r="D6">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="E6">
-        <v>17.98</v>
+        <v>20.68</v>
       </c>
       <c r="F6">
-        <v>54</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -587,13 +587,13 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>6.74</v>
+        <v>8.61</v>
       </c>
       <c r="E7">
-        <v>62.56</v>
+        <v>35.8</v>
       </c>
       <c r="F7">
-        <v>69</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -607,13 +607,13 @@
         <v>20</v>
       </c>
       <c r="D8">
-        <v>4.51</v>
+        <v>7.2</v>
       </c>
       <c r="E8">
-        <v>9.19</v>
+        <v>25.97</v>
       </c>
       <c r="F8">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -627,13 +627,13 @@
         <v>23</v>
       </c>
       <c r="D9">
-        <v>6.8</v>
+        <v>2.29</v>
       </c>
       <c r="E9">
-        <v>7.79</v>
+        <v>10.19</v>
       </c>
       <c r="F9">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -647,13 +647,13 @@
         <v>26</v>
       </c>
       <c r="D10">
-        <v>35.51</v>
+        <v>24.61</v>
       </c>
       <c r="E10">
-        <v>134.55</v>
+        <v>165.48</v>
       </c>
       <c r="F10">
-        <v>754</v>
+        <v>907</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-07-31/2026-07-31</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-08-01/2026-08-01</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,64 +34,64 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#005 Vineland Orlando FL</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>4,712.93</t>
+  </si>
+  <si>
+    <t>4,710.73</t>
+  </si>
+  <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>3,372.34</t>
-  </si>
-  <si>
-    <t>3,366.88</t>
-  </si>
-  <si>
-    <t>#005 Vineland Orlando FL</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
+    <t>4,494.69</t>
+  </si>
+  <si>
+    <t>4,491.42</t>
   </si>
   <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>2,805.69</t>
-  </si>
-  <si>
-    <t>2,804.64</t>
+    <t>3,500.08</t>
+  </si>
+  <si>
+    <t>3,493.86</t>
   </si>
   <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>3,014.79</t>
-  </si>
-  <si>
-    <t>3,006.18</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>3,281.59</t>
-  </si>
-  <si>
-    <t>3,274.39</t>
+    <t>5,233.35</t>
+  </si>
+  <si>
+    <t>5,225.39</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>2,200.19</t>
-  </si>
-  <si>
-    <t>2,197.90</t>
+    <t>1,678.24</t>
   </si>
   <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>15,451.78</t>
-  </si>
-  <si>
-    <t>15,427.17</t>
+    <t>20,543.07</t>
+  </si>
+  <si>
+    <t>20,523.42</t>
+  </si>
+  <si>
+    <t>1,232</t>
   </si>
 </sst>
 </file>
@@ -500,60 +500,60 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>5.46</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>54.86</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>210</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>923.78</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>923.78</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>24.97</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="B5">
-        <v>777.18</v>
-      </c>
-      <c r="C5">
-        <v>777.18</v>
-      </c>
       <c r="D5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="E5">
-        <v>17.98</v>
+        <v>66.92</v>
       </c>
       <c r="F5">
-        <v>56</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -567,13 +567,13 @@
         <v>14</v>
       </c>
       <c r="D6">
-        <v>1.05</v>
+        <v>3.27</v>
       </c>
       <c r="E6">
-        <v>20.68</v>
+        <v>39.05</v>
       </c>
       <c r="F6">
-        <v>168</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -587,13 +587,13 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>8.61</v>
+        <v>6.22</v>
       </c>
       <c r="E7">
-        <v>35.8</v>
+        <v>52.74</v>
       </c>
       <c r="F7">
-        <v>164</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -607,13 +607,13 @@
         <v>20</v>
       </c>
       <c r="D8">
-        <v>7.2</v>
+        <v>7.96</v>
       </c>
       <c r="E8">
-        <v>25.97</v>
+        <v>65.35</v>
       </c>
       <c r="F8">
-        <v>210</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -624,36 +624,36 @@
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>10.19</v>
+        <v>41.75</v>
       </c>
       <c r="F9">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
         <v>24</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>25</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10">
+        <v>19.65</v>
+      </c>
+      <c r="E10">
+        <v>290.78</v>
+      </c>
+      <c r="F10" t="s">
         <v>26</v>
-      </c>
-      <c r="D10">
-        <v>24.61</v>
-      </c>
-      <c r="E10">
-        <v>165.48</v>
-      </c>
-      <c r="F10">
-        <v>907</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-08-01/2026-08-01</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-08-02/2026-08-02</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,64 +34,70 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>4,368.38</t>
+  </si>
+  <si>
+    <t>4,357.00</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>3,655.31</t>
+  </si>
+  <si>
+    <t>3,652.21</t>
+  </si>
+  <si>
     <t>#005 Vineland Orlando FL</t>
   </si>
   <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>3,289.64</t>
+  </si>
+  <si>
+    <t>3,288.94</t>
+  </si>
+  <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>4,712.93</t>
-  </si>
-  <si>
-    <t>4,710.73</t>
+    <t>1,227.33</t>
   </si>
   <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>4,494.69</t>
-  </si>
-  <si>
-    <t>4,491.42</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>3,500.08</t>
-  </si>
-  <si>
-    <t>3,493.86</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>5,233.35</t>
-  </si>
-  <si>
-    <t>5,225.39</t>
+    <t>4,762.77</t>
+  </si>
+  <si>
+    <t>4,759.03</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,678.24</t>
+    <t>2,254.34</t>
+  </si>
+  <si>
+    <t>2,253.22</t>
   </si>
   <si>
     <t>REPORT SUMMARY (7 entries)</t>
   </si>
   <si>
-    <t>20,543.07</t>
-  </si>
-  <si>
-    <t>20,523.42</t>
-  </si>
-  <si>
-    <t>1,232</t>
+    <t>19,557.77</t>
+  </si>
+  <si>
+    <t>19,537.73</t>
+  </si>
+  <si>
+    <t>1,129</t>
   </si>
 </sst>
 </file>
@@ -500,160 +506,160 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>11.38</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>36.1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>923.78</v>
-      </c>
-      <c r="C4">
-        <v>923.78</v>
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="E4">
         <v>24.97</v>
       </c>
       <c r="F4">
-        <v>88</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>66.92</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D6">
-        <v>3.27</v>
+        <v>0.7</v>
       </c>
       <c r="E6">
-        <v>39.05</v>
+        <v>7.79</v>
       </c>
       <c r="F6">
-        <v>267</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7">
-        <v>6.22</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>52.74</v>
+        <v>15.98</v>
       </c>
       <c r="F7">
-        <v>191</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8">
-        <v>7.96</v>
+        <v>3.74</v>
       </c>
       <c r="E8">
-        <v>65.35</v>
+        <v>71.93</v>
       </c>
       <c r="F8">
-        <v>306</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="E9">
-        <v>41.75</v>
+        <v>9.19</v>
       </c>
       <c r="F9">
-        <v>98</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D10">
-        <v>19.65</v>
+        <v>20.04</v>
       </c>
       <c r="E10">
-        <v>290.78</v>
+        <v>165.96</v>
       </c>
       <c r="F10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-08-02/2026-08-02</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-08-03/2026-08-03</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,70 +34,58 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>2,338.07</t>
+  </si>
+  <si>
+    <t>2,332.57</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>2,483.63</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,094.37</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>2,880.80</t>
+  </si>
+  <si>
+    <t>2,878.58</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>1,117.60</t>
+  </si>
+  <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>4,368.38</t>
-  </si>
-  <si>
-    <t>4,357.00</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>3,655.31</t>
-  </si>
-  <si>
-    <t>3,652.21</t>
-  </si>
-  <si>
-    <t>#005 Vineland Orlando FL</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>3,289.64</t>
-  </si>
-  <si>
-    <t>3,288.94</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,227.33</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>4,762.77</t>
-  </si>
-  <si>
-    <t>4,759.03</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
-    <t>2,254.34</t>
-  </si>
-  <si>
-    <t>2,253.22</t>
-  </si>
-  <si>
-    <t>REPORT SUMMARY (7 entries)</t>
-  </si>
-  <si>
-    <t>19,557.77</t>
-  </si>
-  <si>
-    <t>19,537.73</t>
-  </si>
-  <si>
-    <t>1,129</t>
+    <t>3,179.10</t>
+  </si>
+  <si>
+    <t>3,175.62</t>
+  </si>
+  <si>
+    <t>REPORT SUMMARY (6 entries)</t>
+  </si>
+  <si>
+    <t>13,093.57</t>
+  </si>
+  <si>
+    <t>13,082.37</t>
   </si>
 </sst>
 </file>
@@ -474,7 +462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -513,13 +501,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>11.38</v>
+        <v>5.5</v>
       </c>
       <c r="E3">
-        <v>36.1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>249</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -530,27 +518,27 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>24.97</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>215</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
+      <c r="C5" t="s">
+        <v>13</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -559,7 +547,7 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -573,13 +561,13 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>0.7</v>
+        <v>2.22</v>
       </c>
       <c r="E6">
-        <v>7.79</v>
+        <v>83.31</v>
       </c>
       <c r="F6">
-        <v>176</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -596,10 +584,10 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>15.98</v>
+        <v>12.19</v>
       </c>
       <c r="F7">
-        <v>93</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -613,13 +601,13 @@
         <v>21</v>
       </c>
       <c r="D8">
-        <v>3.74</v>
+        <v>3.48</v>
       </c>
       <c r="E8">
-        <v>71.93</v>
+        <v>21.3</v>
       </c>
       <c r="F8">
-        <v>271</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -633,33 +621,13 @@
         <v>24</v>
       </c>
       <c r="D9">
-        <v>1.12</v>
+        <v>11.2</v>
       </c>
       <c r="E9">
-        <v>9.19</v>
+        <v>116.8</v>
       </c>
       <c r="F9">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10">
-        <v>20.04</v>
-      </c>
-      <c r="E10">
-        <v>165.96</v>
-      </c>
-      <c r="F10" t="s">
-        <v>28</v>
+        <v>691</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-08-03/2026-08-03</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-08-04/2026-08-04</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,58 +34,52 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>1,309.42</t>
+  </si>
+  <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>2,338.07</t>
-  </si>
-  <si>
-    <t>2,332.57</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>2,483.63</t>
+    <t>2,563.35</t>
+  </si>
+  <si>
+    <t>2,561.95</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,094.37</t>
-  </si>
-  <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>2,880.80</t>
-  </si>
-  <si>
-    <t>2,878.58</t>
+    <t>2,609.34</t>
+  </si>
+  <si>
+    <t>2,608.48</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>2,209.88</t>
+  </si>
+  <si>
+    <t>2,194.46</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,117.60</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>3,179.10</t>
-  </si>
-  <si>
-    <t>3,175.62</t>
-  </si>
-  <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>13,093.57</t>
-  </si>
-  <si>
-    <t>13,082.37</t>
+    <t>10,412.55</t>
+  </si>
+  <si>
+    <t>10,393.85</t>
   </si>
 </sst>
 </file>
@@ -498,136 +492,136 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>153</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>16.28</v>
       </c>
       <c r="F4">
-        <v>53</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
+      <c r="B5">
+        <v>827.62</v>
+      </c>
+      <c r="C5">
+        <v>827.62</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>16.58</v>
       </c>
       <c r="F5">
-        <v>77</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
       <c r="D6">
-        <v>2.22</v>
+        <v>0.86</v>
       </c>
       <c r="E6">
-        <v>83.31</v>
+        <v>9.59</v>
       </c>
       <c r="F6">
-        <v>188</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
         <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
       </c>
       <c r="D7">
+        <v>15.42</v>
+      </c>
+      <c r="E7">
         <v>0</v>
       </c>
-      <c r="E7">
-        <v>12.19</v>
-      </c>
       <c r="F7">
-        <v>50</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
+      <c r="B8">
+        <v>892.94</v>
+      </c>
+      <c r="C8">
+        <v>891.92</v>
       </c>
       <c r="D8">
-        <v>3.48</v>
+        <v>1.02</v>
       </c>
       <c r="E8">
-        <v>21.3</v>
+        <v>31.57</v>
       </c>
       <c r="F8">
-        <v>170</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
         <v>22</v>
       </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
       <c r="D9">
-        <v>11.2</v>
+        <v>18.7</v>
       </c>
       <c r="E9">
-        <v>116.8</v>
+        <v>74.02</v>
       </c>
       <c r="F9">
-        <v>691</v>
+        <v>639</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-08-04/2026-08-04</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-08-05/2026-08-05</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,52 +34,55 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>2,789.27</t>
+  </si>
+  <si>
+    <t>2,780.19</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>2,219.77</t>
+  </si>
+  <si>
+    <t>2,217.67</t>
+  </si>
+  <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>1,309.42</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>2,563.35</t>
-  </si>
-  <si>
-    <t>2,561.95</t>
+    <t>1,344.98</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>2,609.34</t>
-  </si>
-  <si>
-    <t>2,608.48</t>
+    <t>1,236.37</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
   </si>
   <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>2,209.88</t>
-  </si>
-  <si>
-    <t>2,194.46</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
+    <t>2,099.00</t>
+  </si>
+  <si>
+    <t>2,090.05</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>10,412.55</t>
-  </si>
-  <si>
-    <t>10,393.85</t>
+    <t>10,575.19</t>
+  </si>
+  <si>
+    <t>10,555.06</t>
   </si>
 </sst>
 </file>
@@ -492,136 +495,136 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>9.08</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>42.54</v>
       </c>
       <c r="F3">
-        <v>85</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="E4">
-        <v>16.28</v>
+        <v>39.95</v>
       </c>
       <c r="F4">
-        <v>165</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5">
-        <v>827.62</v>
-      </c>
-      <c r="C5">
-        <v>827.62</v>
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>16.58</v>
+        <v>62.93</v>
       </c>
       <c r="F5">
-        <v>58</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>9.59</v>
+        <v>19.98</v>
       </c>
       <c r="F6">
-        <v>158</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" t="s">
-        <v>18</v>
+      <c r="B7">
+        <v>885.8</v>
+      </c>
+      <c r="C7">
+        <v>885.8</v>
       </c>
       <c r="D7">
-        <v>15.42</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>122</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
         <v>19</v>
       </c>
-      <c r="B8">
-        <v>892.94</v>
-      </c>
-      <c r="C8">
-        <v>891.92</v>
+      <c r="C8" t="s">
+        <v>20</v>
       </c>
       <c r="D8">
-        <v>1.02</v>
+        <v>8.95</v>
       </c>
       <c r="E8">
-        <v>31.57</v>
+        <v>18.7</v>
       </c>
       <c r="F8">
-        <v>51</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9">
-        <v>18.7</v>
+        <v>20.13</v>
       </c>
       <c r="E9">
-        <v>74.02</v>
+        <v>184.1</v>
       </c>
       <c r="F9">
-        <v>639</v>
+        <v>677</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
-    <t>multi-venue - Sales Summary - 2026-08-05/2026-08-05</t>
+    <t>multi-venue - Sales Summary - 2026-08-06/2026-08-06</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,55 +34,55 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>2,762.24</t>
+  </si>
+  <si>
+    <t>2,756.21</t>
+  </si>
+  <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>2,789.27</t>
-  </si>
-  <si>
-    <t>2,780.19</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>2,219.77</t>
-  </si>
-  <si>
-    <t>2,217.67</t>
+    <t>2,910.06</t>
+  </si>
+  <si>
+    <t>2,909.20</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>2,400.84</t>
+  </si>
+  <si>
+    <t>2,391.32</t>
   </si>
   <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>1,344.98</t>
+    <t>1,590.65</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,236.37</t>
-  </si>
-  <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>2,099.00</t>
-  </si>
-  <si>
-    <t>2,090.05</t>
+    <t>1,239.92</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>10,575.19</t>
-  </si>
-  <si>
-    <t>10,555.06</t>
+    <t>11,285.36</t>
+  </si>
+  <si>
+    <t>11,268.95</t>
   </si>
 </sst>
 </file>
@@ -498,13 +498,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>9.08</v>
+        <v>6.03</v>
       </c>
       <c r="E3">
-        <v>42.54</v>
+        <v>11.99</v>
       </c>
       <c r="F3">
-        <v>198</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -518,13 +518,13 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>2.1</v>
+        <v>0.86</v>
       </c>
       <c r="E4">
-        <v>39.95</v>
+        <v>35.36</v>
       </c>
       <c r="F4">
-        <v>140</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -535,47 +535,47 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5">
+        <v>9.52</v>
+      </c>
+      <c r="E5">
         <v>0</v>
       </c>
-      <c r="E5">
-        <v>62.93</v>
-      </c>
       <c r="F5">
-        <v>83</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>19.98</v>
+        <v>7.79</v>
       </c>
       <c r="F6">
-        <v>92</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7">
-        <v>885.8</v>
+        <v>381.65</v>
       </c>
       <c r="C7">
-        <v>885.8</v>
+        <v>381.65</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -584,27 +584,27 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
         <v>20</v>
       </c>
       <c r="D8">
-        <v>8.95</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>18.7</v>
+        <v>10.19</v>
       </c>
       <c r="F8">
-        <v>116</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -618,13 +618,13 @@
         <v>23</v>
       </c>
       <c r="D9">
-        <v>20.13</v>
+        <v>16.41</v>
       </c>
       <c r="E9">
-        <v>184.1</v>
+        <v>65.33</v>
       </c>
       <c r="F9">
-        <v>677</v>
+        <v>690</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-08-06/2026-08-06</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-08-07/2026-08-07</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,55 +34,61 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>3,005.70</t>
+  </si>
+  <si>
+    <t>3,003.55</t>
+  </si>
+  <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>2,762.24</t>
-  </si>
-  <si>
-    <t>2,756.21</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>2,910.06</t>
-  </si>
-  <si>
-    <t>2,909.20</t>
+    <t>3,250.59</t>
+  </si>
+  <si>
+    <t>3,242.99</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>4,418.90</t>
+  </si>
+  <si>
+    <t>4,417.14</t>
   </si>
   <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>2,400.84</t>
-  </si>
-  <si>
-    <t>2,391.32</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>1,590.65</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
+    <t>2,931.43</t>
+  </si>
+  <si>
+    <t>2,908.99</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,239.92</t>
+    <t>1,375.21</t>
+  </si>
+  <si>
+    <t>1,374.61</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>11,285.36</t>
-  </si>
-  <si>
-    <t>11,268.95</t>
+    <t>15,372.15</t>
+  </si>
+  <si>
+    <t>15,337.60</t>
   </si>
 </sst>
 </file>
@@ -498,13 +504,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>6.03</v>
+        <v>2.15</v>
       </c>
       <c r="E3">
-        <v>11.99</v>
+        <v>28.27</v>
       </c>
       <c r="F3">
-        <v>164</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -518,113 +524,113 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>0.86</v>
+        <v>7.6</v>
       </c>
       <c r="E4">
-        <v>35.36</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>179</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
+      <c r="B5">
+        <v>390.32</v>
+      </c>
+      <c r="C5">
+        <v>390.32</v>
       </c>
       <c r="D5">
-        <v>9.52</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>17.98</v>
       </c>
       <c r="F5">
-        <v>138</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
         <v>16</v>
       </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
       <c r="D6">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="E6">
-        <v>7.79</v>
+        <v>15.58</v>
       </c>
       <c r="F6">
-        <v>109</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
         <v>18</v>
       </c>
-      <c r="B7">
-        <v>381.65</v>
-      </c>
-      <c r="C7">
-        <v>381.65</v>
+      <c r="C7" t="s">
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>22.44</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>111.2</v>
       </c>
       <c r="F7">
-        <v>36</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E8">
-        <v>10.19</v>
+        <v>38.56</v>
       </c>
       <c r="F8">
-        <v>64</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D9">
-        <v>16.41</v>
+        <v>34.55</v>
       </c>
       <c r="E9">
-        <v>65.33</v>
+        <v>211.59</v>
       </c>
       <c r="F9">
-        <v>690</v>
+        <v>951</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-08-07/2026-08-07</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-08-08/2026-08-08</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -37,58 +37,61 @@
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>3,005.70</t>
-  </si>
-  <si>
-    <t>3,003.55</t>
+    <t>4,646.97</t>
+  </si>
+  <si>
+    <t>4,636.38</t>
   </si>
   <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>3,250.59</t>
-  </si>
-  <si>
-    <t>3,242.99</t>
+    <t>4,492.61</t>
+  </si>
+  <si>
+    <t>4,488.71</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>5,758.62</t>
+  </si>
+  <si>
+    <t>5,751.40</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
+    <t>1,338.84</t>
+  </si>
+  <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>4,418.90</t>
-  </si>
-  <si>
-    <t>4,417.14</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>2,931.43</t>
-  </si>
-  <si>
-    <t>2,908.99</t>
+    <t>4,343.22</t>
+  </si>
+  <si>
+    <t>4,335.22</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,375.21</t>
-  </si>
-  <si>
-    <t>1,374.61</t>
+    <t>2,721.42</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>15,372.15</t>
-  </si>
-  <si>
-    <t>15,337.60</t>
+    <t>23,301.68</t>
+  </si>
+  <si>
+    <t>23,271.97</t>
+  </si>
+  <si>
+    <t>1,351</t>
   </si>
 </sst>
 </file>
@@ -504,13 +507,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>2.15</v>
+        <v>10.59</v>
       </c>
       <c r="E3">
-        <v>28.27</v>
+        <v>52.3</v>
       </c>
       <c r="F3">
-        <v>207</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -524,93 +527,93 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>7.6</v>
+        <v>3.9</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>76.4</v>
       </c>
       <c r="F4">
-        <v>216</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="B5">
-        <v>390.32</v>
-      </c>
-      <c r="C5">
-        <v>390.32</v>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>7.22</v>
       </c>
       <c r="E5">
-        <v>17.98</v>
+        <v>143.25</v>
       </c>
       <c r="F5">
-        <v>28</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>15.58</v>
+        <v>43.15</v>
       </c>
       <c r="F6">
-        <v>253</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7">
-        <v>22.44</v>
+        <v>8</v>
       </c>
       <c r="E7">
-        <v>111.2</v>
+        <v>46.83</v>
       </c>
       <c r="F7">
-        <v>165</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
         <v>22</v>
       </c>
       <c r="D8">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>38.56</v>
+        <v>19.38</v>
       </c>
       <c r="F8">
-        <v>82</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -624,13 +627,13 @@
         <v>25</v>
       </c>
       <c r="D9">
-        <v>34.55</v>
+        <v>29.71</v>
       </c>
       <c r="E9">
-        <v>211.59</v>
-      </c>
-      <c r="F9">
-        <v>951</v>
+        <v>381.31</v>
+      </c>
+      <c r="F9" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-08-08/2026-08-08</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-08-09/2026-08-09</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,64 +34,61 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>3,310.03</t>
+  </si>
+  <si>
+    <t>3,297.28</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>5,380.56</t>
+  </si>
+  <si>
+    <t>5,370.28</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>4,092.15</t>
+  </si>
+  <si>
+    <t>4,090.59</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>2,152.45</t>
+  </si>
+  <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>4,646.97</t>
-  </si>
-  <si>
-    <t>4,636.38</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>4,492.61</t>
-  </si>
-  <si>
-    <t>4,488.71</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>5,758.62</t>
-  </si>
-  <si>
-    <t>5,751.40</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,338.84</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>4,343.22</t>
-  </si>
-  <si>
-    <t>4,335.22</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
-    <t>2,721.42</t>
+    <t>4,553.57</t>
+  </si>
+  <si>
+    <t>4,550.45</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>23,301.68</t>
-  </si>
-  <si>
-    <t>23,271.97</t>
-  </si>
-  <si>
-    <t>1,351</t>
+    <t>20,437.99</t>
+  </si>
+  <si>
+    <t>20,410.28</t>
+  </si>
+  <si>
+    <t>1,124</t>
   </si>
 </sst>
 </file>
@@ -507,133 +504,133 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>10.59</v>
+        <v>12.75</v>
       </c>
       <c r="E3">
-        <v>52.3</v>
+        <v>33.96</v>
       </c>
       <c r="F3">
-        <v>280</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
+      <c r="B4">
+        <v>949.23</v>
+      </c>
+      <c r="C4">
+        <v>949.23</v>
       </c>
       <c r="D4">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>76.4</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>286</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
       <c r="D5">
-        <v>7.22</v>
+        <v>10.28</v>
       </c>
       <c r="E5">
-        <v>143.25</v>
+        <v>43.95</v>
       </c>
       <c r="F5">
-        <v>314</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
         <v>16</v>
       </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
       <c r="D6">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="E6">
-        <v>43.15</v>
+        <v>23.37</v>
       </c>
       <c r="F6">
-        <v>101</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D7">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>46.83</v>
+        <v>47.95</v>
       </c>
       <c r="F7">
-        <v>246</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
         <v>21</v>
       </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
       <c r="D8">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="E8">
-        <v>19.38</v>
+        <v>66.52</v>
       </c>
       <c r="F8">
-        <v>124</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
         <v>23</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>24</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9">
+        <v>27.71</v>
+      </c>
+      <c r="E9">
+        <v>215.75</v>
+      </c>
+      <c r="F9" t="s">
         <v>25</v>
-      </c>
-      <c r="D9">
-        <v>29.71</v>
-      </c>
-      <c r="E9">
-        <v>381.31</v>
-      </c>
-      <c r="F9" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-08-09/2026-08-09</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-08-10/2026-08-10</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -37,58 +37,46 @@
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>3,310.03</t>
-  </si>
-  <si>
-    <t>3,297.28</t>
+    <t>2,094.78</t>
+  </si>
+  <si>
+    <t>2,090.22</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>3,187.87</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>5,380.56</t>
-  </si>
-  <si>
-    <t>5,370.28</t>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>2,965.32</t>
+  </si>
+  <si>
+    <t>2,961.79</t>
   </si>
   <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>4,092.15</t>
-  </si>
-  <si>
-    <t>4,090.59</t>
+    <t>1,557.64</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>2,152.45</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>4,553.57</t>
-  </si>
-  <si>
-    <t>4,550.45</t>
-  </si>
-  <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>20,437.99</t>
-  </si>
-  <si>
-    <t>20,410.28</t>
-  </si>
-  <si>
-    <t>1,124</t>
+    <t>11,223.99</t>
+  </si>
+  <si>
+    <t>11,213.14</t>
   </si>
 </sst>
 </file>
@@ -504,133 +492,133 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>12.75</v>
+        <v>4.56</v>
       </c>
       <c r="E3">
-        <v>33.96</v>
+        <v>15.98</v>
       </c>
       <c r="F3">
-        <v>208</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4">
-        <v>949.23</v>
-      </c>
-      <c r="C4">
-        <v>949.23</v>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>47.23</v>
       </c>
       <c r="F4">
-        <v>67</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" t="s">
-        <v>13</v>
+      <c r="B5">
+        <v>566.58</v>
+      </c>
+      <c r="C5">
+        <v>566.58</v>
       </c>
       <c r="D5">
-        <v>10.28</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>43.95</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>263</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
       <c r="D6">
-        <v>1.56</v>
+        <v>3.53</v>
       </c>
       <c r="E6">
-        <v>23.37</v>
+        <v>47.95</v>
       </c>
       <c r="F6">
-        <v>220</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>47.95</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>107</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
+        <v>18</v>
+      </c>
+      <c r="B8">
+        <v>851.8</v>
+      </c>
+      <c r="C8">
+        <v>849.04</v>
       </c>
       <c r="D8">
-        <v>3.12</v>
+        <v>2.76</v>
       </c>
       <c r="E8">
-        <v>66.52</v>
+        <v>21.38</v>
       </c>
       <c r="F8">
-        <v>259</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D9">
-        <v>27.71</v>
+        <v>10.85</v>
       </c>
       <c r="E9">
-        <v>215.75</v>
-      </c>
-      <c r="F9" t="s">
-        <v>25</v>
+        <v>132.54</v>
+      </c>
+      <c r="F9">
+        <v>670</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-08-10/2026-08-10</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-08-11/2026-08-11</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,49 +34,58 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>1,781.83</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>2,184.55</t>
+  </si>
+  <si>
+    <t>2,183.69</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>2,675.99</t>
+  </si>
+  <si>
+    <t>2,664.74</t>
+  </si>
+  <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>2,094.78</t>
-  </si>
-  <si>
-    <t>2,090.22</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>3,187.87</t>
+    <t>1,527.95</t>
+  </si>
+  <si>
+    <t>1,526.29</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>1,015.21</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>2,965.32</t>
-  </si>
-  <si>
-    <t>2,961.79</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>1,557.64</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
+    <t>1,270.09</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>11,223.99</t>
-  </si>
-  <si>
-    <t>11,213.14</t>
+    <t>10,455.62</t>
+  </si>
+  <si>
+    <t>10,441.85</t>
   </si>
 </sst>
 </file>
@@ -489,136 +498,136 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>15.98</v>
+        <v>53.49</v>
       </c>
       <c r="F3">
-        <v>140</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="E4">
-        <v>47.23</v>
+        <v>19.18</v>
       </c>
       <c r="F4">
-        <v>158</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B5">
-        <v>566.58</v>
-      </c>
-      <c r="C5">
-        <v>566.58</v>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>11.25</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>55.59</v>
       </c>
       <c r="F5">
-        <v>44</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D6">
-        <v>3.53</v>
+        <v>1.66</v>
       </c>
       <c r="E6">
-        <v>47.95</v>
+        <v>31.96</v>
       </c>
       <c r="F6">
-        <v>190</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>10.19</v>
       </c>
       <c r="F7">
-        <v>90</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8">
-        <v>851.8</v>
-      </c>
-      <c r="C8">
-        <v>849.04</v>
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
       </c>
       <c r="D8">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>21.38</v>
+        <v>8.99</v>
       </c>
       <c r="F8">
-        <v>48</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D9">
-        <v>10.85</v>
+        <v>13.77</v>
       </c>
       <c r="E9">
-        <v>132.54</v>
+        <v>179.4</v>
       </c>
       <c r="F9">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-08-11/2026-08-11</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-08-12/2026-08-12</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,58 +34,55 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>1,681.94</t>
+  </si>
+  <si>
+    <t>1,681.44</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>2,324.67</t>
+  </si>
+  <si>
+    <t>2,316.58</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,245.33</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>2,247.17</t>
+  </si>
+  <si>
+    <t>2,243.52</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>1,781.83</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>2,184.55</t>
-  </si>
-  <si>
-    <t>2,183.69</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>2,675.99</t>
-  </si>
-  <si>
-    <t>2,664.74</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>1,527.95</t>
-  </si>
-  <si>
-    <t>1,526.29</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
-    <t>1,015.21</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,270.09</t>
+    <t>1,236.45</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>10,455.62</t>
-  </si>
-  <si>
-    <t>10,441.85</t>
+    <t>9,671.67</t>
+  </si>
+  <si>
+    <t>9,659.43</t>
   </si>
 </sst>
 </file>
@@ -498,56 +495,56 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
+        <v>0.5</v>
+      </c>
+      <c r="E3">
         <v>0</v>
       </c>
-      <c r="E3">
-        <v>53.49</v>
-      </c>
       <c r="F3">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>0.86</v>
+        <v>8.09</v>
       </c>
       <c r="E4">
-        <v>19.18</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
       </c>
       <c r="D5">
-        <v>11.25</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>55.59</v>
+        <v>17.08</v>
       </c>
       <c r="F5">
-        <v>146</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -561,73 +558,73 @@
         <v>17</v>
       </c>
       <c r="D6">
-        <v>1.66</v>
+        <v>3.65</v>
       </c>
       <c r="E6">
-        <v>31.96</v>
+        <v>48.95</v>
       </c>
       <c r="F6">
-        <v>107</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
+      <c r="B7">
+        <v>936.11</v>
+      </c>
+      <c r="C7">
+        <v>936.11</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>10.19</v>
+        <v>1.59</v>
       </c>
       <c r="F7">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
         <v>20</v>
       </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>8.99</v>
+        <v>34.16</v>
       </c>
       <c r="F8">
-        <v>90</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
         <v>22</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>23</v>
       </c>
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
       <c r="D9">
-        <v>13.77</v>
+        <v>12.24</v>
       </c>
       <c r="E9">
-        <v>179.4</v>
+        <v>101.78</v>
       </c>
       <c r="F9">
-        <v>671</v>
+        <v>631</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-08-12/2026-08-12</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-08-13/2026-08-13</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,55 +34,61 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>2,402.54</t>
+  </si>
+  <si>
+    <t>2,399.30</t>
+  </si>
+  <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>1,681.94</t>
-  </si>
-  <si>
-    <t>1,681.44</t>
+    <t>1,753.86</t>
+  </si>
+  <si>
+    <t>1,751.26</t>
   </si>
   <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>2,324.67</t>
-  </si>
-  <si>
-    <t>2,316.58</t>
+    <t>2,022.64</t>
+  </si>
+  <si>
+    <t>2,017.99</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>1,178.25</t>
+  </si>
+  <si>
+    <t>1,177.95</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,245.33</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>2,247.17</t>
-  </si>
-  <si>
-    <t>2,243.52</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
+    <t>1,633.34</t>
   </si>
   <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>1,236.45</t>
+    <t>1,395.60</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>9,671.67</t>
-  </si>
-  <si>
-    <t>9,659.43</t>
+    <t>10,386.23</t>
+  </si>
+  <si>
+    <t>10,375.44</t>
   </si>
 </sst>
 </file>
@@ -498,13 +504,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>0.5</v>
+        <v>3.24</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>40.35</v>
       </c>
       <c r="F3">
-        <v>122</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -518,13 +524,13 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>8.09</v>
+        <v>2.6</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>34.96</v>
       </c>
       <c r="F4">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -535,96 +541,96 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="E5">
-        <v>17.08</v>
+        <v>19.7</v>
       </c>
       <c r="F5">
-        <v>95</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6">
-        <v>3.65</v>
+        <v>0.3</v>
       </c>
       <c r="E6">
-        <v>48.95</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>153</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7">
-        <v>936.11</v>
-      </c>
-      <c r="C7">
-        <v>936.11</v>
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>1.59</v>
+        <v>58.83</v>
       </c>
       <c r="F7">
-        <v>51</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>34.16</v>
+        <v>7.79</v>
       </c>
       <c r="F8">
-        <v>77</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D9">
-        <v>12.24</v>
+        <v>10.79</v>
       </c>
       <c r="E9">
-        <v>101.78</v>
+        <v>161.63</v>
       </c>
       <c r="F9">
-        <v>631</v>
+        <v>683</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-08-13/2026-08-13</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-08-14/2026-08-14</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,61 +34,64 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>2,808.58</t>
+  </si>
+  <si>
+    <t>2,807.78</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>2,511.41</t>
+  </si>
+  <si>
+    <t>2,506.63</t>
+  </si>
+  <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>2,402.54</t>
-  </si>
-  <si>
-    <t>2,399.30</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>1,753.86</t>
-  </si>
-  <si>
-    <t>1,751.26</t>
+    <t>2,764.50</t>
+  </si>
+  <si>
+    <t>2,759.24</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,437.52</t>
   </si>
   <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>2,022.64</t>
-  </si>
-  <si>
-    <t>2,017.99</t>
+    <t>2,729.31</t>
+  </si>
+  <si>
+    <t>2,714.83</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,178.25</t>
-  </si>
-  <si>
-    <t>1,177.95</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,633.34</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>1,395.60</t>
+    <t>1,648.70</t>
+  </si>
+  <si>
+    <t>1,642.20</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>10,386.23</t>
-  </si>
-  <si>
-    <t>10,375.44</t>
+    <t>13,900.02</t>
+  </si>
+  <si>
+    <t>13,868.20</t>
   </si>
 </sst>
 </file>
@@ -504,13 +507,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>3.24</v>
+        <v>0.8</v>
       </c>
       <c r="E3">
-        <v>40.35</v>
+        <v>40.85</v>
       </c>
       <c r="F3">
-        <v>150</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -524,13 +527,13 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>2.6</v>
+        <v>4.78</v>
       </c>
       <c r="E4">
-        <v>34.96</v>
+        <v>16.98</v>
       </c>
       <c r="F4">
-        <v>132</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -544,13 +547,13 @@
         <v>15</v>
       </c>
       <c r="D5">
-        <v>4.65</v>
+        <v>5.26</v>
       </c>
       <c r="E5">
-        <v>19.7</v>
+        <v>45.95</v>
       </c>
       <c r="F5">
-        <v>114</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -561,36 +564,36 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>10.99</v>
       </c>
       <c r="F6">
-        <v>71</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
         <v>19</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>14.48</v>
       </c>
       <c r="E7">
-        <v>58.83</v>
+        <v>8.85</v>
       </c>
       <c r="F7">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -601,36 +604,36 @@
         <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="E8">
-        <v>7.79</v>
+        <v>39.74</v>
       </c>
       <c r="F8">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9">
-        <v>10.79</v>
+        <v>31.82</v>
       </c>
       <c r="E9">
-        <v>161.63</v>
+        <v>163.36</v>
       </c>
       <c r="F9">
-        <v>683</v>
+        <v>863</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-08-14/2026-08-14</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-08-15/2026-08-15</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,64 +34,67 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>4,059.61</t>
+  </si>
+  <si>
+    <t>4,056.08</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,648.01</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>4,808.89</t>
+  </si>
+  <si>
+    <t>4,797.76</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>3,870.50</t>
+  </si>
+  <si>
+    <t>3,862.92</t>
+  </si>
+  <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>2,808.58</t>
-  </si>
-  <si>
-    <t>2,807.78</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>2,511.41</t>
-  </si>
-  <si>
-    <t>2,506.63</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>2,764.50</t>
-  </si>
-  <si>
-    <t>2,759.24</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,437.52</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>2,729.31</t>
-  </si>
-  <si>
-    <t>2,714.83</t>
+    <t>5,185.78</t>
+  </si>
+  <si>
+    <t>5,184.02</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,648.70</t>
-  </si>
-  <si>
-    <t>1,642.20</t>
+    <t>2,050.38</t>
+  </si>
+  <si>
+    <t>2,048.54</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>13,900.02</t>
-  </si>
-  <si>
-    <t>13,868.20</t>
+    <t>21,623.17</t>
+  </si>
+  <si>
+    <t>21,597.33</t>
+  </si>
+  <si>
+    <t>1,264</t>
   </si>
 </sst>
 </file>
@@ -507,13 +510,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>0.8</v>
+        <v>3.53</v>
       </c>
       <c r="E3">
-        <v>40.85</v>
+        <v>7.99</v>
       </c>
       <c r="F3">
-        <v>178</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -524,56 +527,56 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>16.98</v>
+        <v>57.93</v>
       </c>
       <c r="F4">
-        <v>169</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>14</v>
       </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
       <c r="D5">
-        <v>5.26</v>
+        <v>11.13</v>
       </c>
       <c r="E5">
-        <v>45.95</v>
+        <v>90.55</v>
       </c>
       <c r="F5">
-        <v>188</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
         <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>7.58</v>
       </c>
       <c r="E6">
-        <v>10.99</v>
+        <v>54.29</v>
       </c>
       <c r="F6">
-        <v>102</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -587,13 +590,13 @@
         <v>20</v>
       </c>
       <c r="D7">
-        <v>14.48</v>
+        <v>1.76</v>
       </c>
       <c r="E7">
-        <v>8.85</v>
+        <v>111.21</v>
       </c>
       <c r="F7">
-        <v>137</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -607,13 +610,13 @@
         <v>23</v>
       </c>
       <c r="D8">
-        <v>6.5</v>
+        <v>1.84</v>
       </c>
       <c r="E8">
-        <v>39.74</v>
+        <v>53.54</v>
       </c>
       <c r="F8">
-        <v>89</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -627,13 +630,13 @@
         <v>26</v>
       </c>
       <c r="D9">
-        <v>31.82</v>
+        <v>25.84</v>
       </c>
       <c r="E9">
-        <v>163.36</v>
-      </c>
-      <c r="F9">
-        <v>863</v>
+        <v>375.51</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
   <si>
-    <t>multi-venue - Sales Summary - 2026-08-15/2026-08-15</t>
+    <t>multi-venue - Sales Summary - 2026-08-16/2026-08-16</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,67 +34,67 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>3,915.57</t>
+  </si>
+  <si>
+    <t>3,913.79</t>
+  </si>
+  <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>4,059.61</t>
-  </si>
-  <si>
-    <t>4,056.08</t>
+    <t>3,535.62</t>
+  </si>
+  <si>
+    <t>3,531.12</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>4,775.85</t>
+  </si>
+  <si>
+    <t>4,774.86</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>3,538.30</t>
+  </si>
+  <si>
+    <t>3,514.34</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,648.01</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>4,808.89</t>
-  </si>
-  <si>
-    <t>4,797.76</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>3,870.50</t>
-  </si>
-  <si>
-    <t>3,862.92</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>5,185.78</t>
-  </si>
-  <si>
-    <t>5,184.02</t>
+    <t>1,827.46</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>2,050.38</t>
-  </si>
-  <si>
-    <t>2,048.54</t>
+    <t>2,097.38</t>
+  </si>
+  <si>
+    <t>2,096.18</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>21,623.17</t>
-  </si>
-  <si>
-    <t>21,597.33</t>
-  </si>
-  <si>
-    <t>1,264</t>
+    <t>19,690.18</t>
+  </si>
+  <si>
+    <t>19,657.75</t>
+  </si>
+  <si>
+    <t>1,131</t>
   </si>
 </sst>
 </file>
@@ -510,13 +510,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>3.53</v>
+        <v>1.78</v>
       </c>
       <c r="E3">
-        <v>7.99</v>
+        <v>-3</v>
       </c>
       <c r="F3">
-        <v>274</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -527,76 +527,76 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="E4">
-        <v>57.93</v>
+        <v>28.56</v>
       </c>
       <c r="F4">
-        <v>127</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>11.13</v>
+        <v>0.99</v>
       </c>
       <c r="E5">
-        <v>90.55</v>
+        <v>67.1</v>
       </c>
       <c r="F5">
-        <v>262</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6">
-        <v>7.58</v>
+        <v>23.96</v>
       </c>
       <c r="E6">
-        <v>54.29</v>
+        <v>87.91</v>
       </c>
       <c r="F6">
-        <v>253</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
       </c>
       <c r="D7">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>111.21</v>
+        <v>42.45</v>
       </c>
       <c r="F7">
-        <v>238</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -610,13 +610,13 @@
         <v>23</v>
       </c>
       <c r="D8">
-        <v>1.84</v>
+        <v>1.2</v>
       </c>
       <c r="E8">
-        <v>53.54</v>
+        <v>89.51</v>
       </c>
       <c r="F8">
-        <v>110</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -630,10 +630,10 @@
         <v>26</v>
       </c>
       <c r="D9">
-        <v>25.84</v>
+        <v>32.43</v>
       </c>
       <c r="E9">
-        <v>375.51</v>
+        <v>312.53</v>
       </c>
       <c r="F9" t="s">
         <v>27</v>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-08-16/2026-08-16</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-08-17/2026-08-17</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -37,64 +37,55 @@
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>3,915.57</t>
-  </si>
-  <si>
-    <t>3,913.79</t>
+    <t>2,612.66</t>
+  </si>
+  <si>
+    <t>2,605.13</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>2,561.53</t>
+  </si>
+  <si>
+    <t>2,554.98</t>
   </si>
   <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>3,535.62</t>
-  </si>
-  <si>
-    <t>3,531.12</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>4,775.85</t>
-  </si>
-  <si>
-    <t>4,774.86</t>
+    <t>1,496.68</t>
+  </si>
+  <si>
+    <t>1,496.18</t>
   </si>
   <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>3,538.30</t>
-  </si>
-  <si>
-    <t>3,514.34</t>
+    <t>1,182.69</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,827.46</t>
+    <t>1,528.87</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>2,097.38</t>
-  </si>
-  <si>
-    <t>2,096.18</t>
+    <t>1,281.88</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>19,690.18</t>
-  </si>
-  <si>
-    <t>19,657.75</t>
-  </si>
-  <si>
-    <t>1,131</t>
+    <t>10,664.31</t>
+  </si>
+  <si>
+    <t>10,649.73</t>
   </si>
 </sst>
 </file>
@@ -510,13 +501,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>1.78</v>
+        <v>7.53</v>
       </c>
       <c r="E3">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>244</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -530,13 +521,13 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>4.5</v>
+        <v>6.55</v>
       </c>
       <c r="E4">
-        <v>28.56</v>
+        <v>10.85</v>
       </c>
       <c r="F4">
-        <v>226</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -550,13 +541,13 @@
         <v>15</v>
       </c>
       <c r="D5">
-        <v>0.99</v>
+        <v>0.5</v>
       </c>
       <c r="E5">
-        <v>67.1</v>
+        <v>15.98</v>
       </c>
       <c r="F5">
-        <v>233</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -567,76 +558,76 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6">
-        <v>23.96</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>87.91</v>
+        <v>25.37</v>
       </c>
       <c r="F6">
-        <v>183</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
         <v>19</v>
       </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>42.45</v>
+        <v>19.08</v>
       </c>
       <c r="F7">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
         <v>21</v>
       </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D8">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>89.51</v>
+        <v>2.49</v>
       </c>
       <c r="F8">
-        <v>121</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
         <v>24</v>
       </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" t="s">
-        <v>26</v>
-      </c>
       <c r="D9">
-        <v>32.43</v>
+        <v>14.58</v>
       </c>
       <c r="E9">
-        <v>312.53</v>
-      </c>
-      <c r="F9" t="s">
-        <v>27</v>
+        <v>73.77</v>
+      </c>
+      <c r="F9">
+        <v>675</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-08-17/2026-08-17</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-08-18/2026-08-18</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,58 +34,58 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>1,280.80</t>
+  </si>
+  <si>
+    <t>1,280.02</t>
+  </si>
+  <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>2,612.66</t>
-  </si>
-  <si>
-    <t>2,605.13</t>
+    <t>2,080.52</t>
+  </si>
+  <si>
+    <t>2,077.74</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,541.17</t>
   </si>
   <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>2,561.53</t>
-  </si>
-  <si>
-    <t>2,554.98</t>
+    <t>2,610.12</t>
+  </si>
+  <si>
+    <t>2,596.44</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
   </si>
   <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>1,496.68</t>
-  </si>
-  <si>
-    <t>1,496.18</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>1,182.69</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,528.87</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
-    <t>1,281.88</t>
+    <t>1,706.12</t>
+  </si>
+  <si>
+    <t>1,698.53</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>10,664.31</t>
-  </si>
-  <si>
-    <t>10,649.73</t>
+    <t>9,880.92</t>
+  </si>
+  <si>
+    <t>9,855.79</t>
   </si>
 </sst>
 </file>
@@ -501,13 +501,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>7.53</v>
+        <v>0.78</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>176</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -521,13 +521,13 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>6.55</v>
+        <v>2.78</v>
       </c>
       <c r="E4">
-        <v>10.85</v>
+        <v>30.77</v>
       </c>
       <c r="F4">
-        <v>136</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -538,76 +538,76 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>15.98</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>105</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
         <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>13.68</v>
       </c>
       <c r="E6">
-        <v>25.37</v>
+        <v>18.7</v>
       </c>
       <c r="F6">
-        <v>77</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
+      <c r="B7">
+        <v>662.19</v>
+      </c>
+      <c r="C7">
+        <v>661.89</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E7">
-        <v>19.08</v>
+        <v>9.39</v>
       </c>
       <c r="F7">
-        <v>118</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
         <v>20</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
       </c>
       <c r="C8" t="s">
         <v>21</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>7.59</v>
       </c>
       <c r="E8">
-        <v>2.49</v>
+        <v>-20.27</v>
       </c>
       <c r="F8">
-        <v>63</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -621,13 +621,13 @@
         <v>24</v>
       </c>
       <c r="D9">
-        <v>14.58</v>
+        <v>25.13</v>
       </c>
       <c r="E9">
-        <v>73.77</v>
+        <v>38.59</v>
       </c>
       <c r="F9">
-        <v>675</v>
+        <v>656</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-08-18/2026-08-18</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-08-19/2026-08-19</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,58 +34,52 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>1,720.54</t>
+  </si>
+  <si>
+    <t>1,715.34</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>2,194.69</t>
+  </si>
+  <si>
+    <t>2,193.83</t>
+  </si>
+  <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>1,280.80</t>
-  </si>
-  <si>
-    <t>1,280.02</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>2,080.52</t>
-  </si>
-  <si>
-    <t>2,077.74</t>
-  </si>
-  <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,541.17</t>
+    <t>1,405.34</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
   </si>
   <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>2,610.12</t>
-  </si>
-  <si>
-    <t>2,596.44</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>1,706.12</t>
-  </si>
-  <si>
-    <t>1,698.53</t>
+    <t>2,186.71</t>
+  </si>
+  <si>
+    <t>2,183.73</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>9,880.92</t>
-  </si>
-  <si>
-    <t>9,855.79</t>
+    <t>9,373.23</t>
+  </si>
+  <si>
+    <t>9,362.63</t>
   </si>
 </sst>
 </file>
@@ -501,13 +495,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>0.78</v>
+        <v>5.2</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>89</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -521,113 +515,113 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>2.78</v>
+        <v>0.86</v>
       </c>
       <c r="E4">
-        <v>30.77</v>
+        <v>41.76</v>
       </c>
       <c r="F4">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
+      <c r="B5">
+        <v>943.93</v>
+      </c>
+      <c r="C5">
+        <v>942.37</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>15.58</v>
       </c>
       <c r="F5">
-        <v>119</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D6">
-        <v>13.68</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>18.7</v>
+        <v>31.96</v>
       </c>
       <c r="F6">
-        <v>140</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B7">
-        <v>662.19</v>
+        <v>922.02</v>
       </c>
       <c r="C7">
-        <v>661.89</v>
+        <v>922.02</v>
       </c>
       <c r="D7">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>9.39</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
         <v>19</v>
       </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
       <c r="D8">
-        <v>7.59</v>
+        <v>2.98</v>
       </c>
       <c r="E8">
-        <v>-20.27</v>
+        <v>4.25</v>
       </c>
       <c r="F8">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
         <v>22</v>
       </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
       <c r="D9">
-        <v>25.13</v>
+        <v>10.6</v>
       </c>
       <c r="E9">
-        <v>38.59</v>
+        <v>93.55</v>
       </c>
       <c r="F9">
-        <v>656</v>
+        <v>615</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-08-19/2026-08-19</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-08-20/2026-08-20</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -37,49 +37,52 @@
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>1,720.54</t>
-  </si>
-  <si>
-    <t>1,715.34</t>
+    <t>1,639.50</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>2,396.66</t>
+  </si>
+  <si>
+    <t>2,387.87</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,513.56</t>
   </si>
   <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>2,194.69</t>
-  </si>
-  <si>
-    <t>2,193.83</t>
+    <t>2,232.71</t>
   </si>
   <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,405.34</t>
+    <t>1,550.46</t>
+  </si>
+  <si>
+    <t>1,549.68</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>2,186.71</t>
-  </si>
-  <si>
-    <t>2,183.73</t>
+    <t>1,270.92</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>9,373.23</t>
-  </si>
-  <si>
-    <t>9,362.63</t>
+    <t>10,603.81</t>
+  </si>
+  <si>
+    <t>10,594.24</t>
   </si>
 </sst>
 </file>
@@ -492,56 +495,56 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
       <c r="D4">
-        <v>0.86</v>
+        <v>8.79</v>
       </c>
       <c r="E4">
-        <v>41.76</v>
+        <v>58.5</v>
       </c>
       <c r="F4">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="B5">
-        <v>943.93</v>
-      </c>
-      <c r="C5">
-        <v>942.37</v>
+      <c r="C5" t="s">
+        <v>13</v>
       </c>
       <c r="D5">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>15.58</v>
+        <v>10.09</v>
       </c>
       <c r="F5">
-        <v>68</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -558,70 +561,70 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>31.96</v>
+        <v>26.77</v>
       </c>
       <c r="F6">
-        <v>113</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
-      <c r="B7">
-        <v>922.02</v>
-      </c>
-      <c r="C7">
-        <v>922.02</v>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>23.37</v>
       </c>
       <c r="F7">
-        <v>56</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>4.25</v>
+        <v>37.56</v>
       </c>
       <c r="F8">
-        <v>123</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9">
-        <v>10.6</v>
+        <v>9.57</v>
       </c>
       <c r="E9">
-        <v>93.55</v>
+        <v>156.29</v>
       </c>
       <c r="F9">
-        <v>615</v>
+        <v>692</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-08-20/2026-08-20</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-08-21/2026-08-21</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,55 +34,61 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>2,806.51</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>2,370.00</t>
+  </si>
+  <si>
+    <t>2,368.08</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>3,049.20</t>
+  </si>
+  <si>
+    <t>3,021.10</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,587.87</t>
+  </si>
+  <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>1,639.50</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>2,396.66</t>
-  </si>
-  <si>
-    <t>2,387.87</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,513.56</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>2,232.71</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>1,550.46</t>
-  </si>
-  <si>
-    <t>1,549.68</t>
+    <t>2,163.86</t>
+  </si>
+  <si>
+    <t>2,160.56</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,270.92</t>
+    <t>2,101.35</t>
+  </si>
+  <si>
+    <t>2,100.27</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>10,603.81</t>
-  </si>
-  <si>
-    <t>10,594.24</t>
+    <t>14,078.79</t>
+  </si>
+  <si>
+    <t>14,044.39</t>
   </si>
 </sst>
 </file>
@@ -501,10 +507,10 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>54.44</v>
       </c>
       <c r="F3">
-        <v>120</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -518,13 +524,13 @@
         <v>11</v>
       </c>
       <c r="D4">
-        <v>8.79</v>
+        <v>1.92</v>
       </c>
       <c r="E4">
-        <v>58.5</v>
+        <v>8.59</v>
       </c>
       <c r="F4">
-        <v>138</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -535,96 +541,96 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>28.1</v>
       </c>
       <c r="E5">
-        <v>10.09</v>
+        <v>8.85</v>
       </c>
       <c r="F5">
-        <v>118</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>26.77</v>
+        <v>34.96</v>
       </c>
       <c r="F6">
-        <v>149</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>0.78</v>
+        <v>3.3</v>
       </c>
       <c r="E7">
-        <v>23.37</v>
+        <v>16.98</v>
       </c>
       <c r="F7">
-        <v>92</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="E8">
-        <v>37.56</v>
+        <v>38.15</v>
       </c>
       <c r="F8">
-        <v>75</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D9">
-        <v>9.57</v>
+        <v>34.4</v>
       </c>
       <c r="E9">
-        <v>156.29</v>
+        <v>161.97</v>
       </c>
       <c r="F9">
-        <v>692</v>
+        <v>887</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-08-21/2026-08-21</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-08-22/2026-08-22</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -37,58 +37,64 @@
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>2,806.51</t>
+    <t>3,424.31</t>
+  </si>
+  <si>
+    <t>3,422.75</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>5,470.95</t>
+  </si>
+  <si>
+    <t>5,461.56</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>4,210.04</t>
+  </si>
+  <si>
+    <t>4,204.49</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>2,044.10</t>
   </si>
   <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>2,370.00</t>
-  </si>
-  <si>
-    <t>2,368.08</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>3,049.20</t>
-  </si>
-  <si>
-    <t>3,021.10</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,587.87</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>2,163.86</t>
-  </si>
-  <si>
-    <t>2,160.56</t>
+    <t>4,122.93</t>
+  </si>
+  <si>
+    <t>4,116.85</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>2,101.35</t>
-  </si>
-  <si>
-    <t>2,100.27</t>
+    <t>2,313.93</t>
+  </si>
+  <si>
+    <t>2,312.71</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>14,078.79</t>
-  </si>
-  <si>
-    <t>14,044.39</t>
+    <t>21,586.26</t>
+  </si>
+  <si>
+    <t>21,562.46</t>
+  </si>
+  <si>
+    <t>1,313</t>
   </si>
 </sst>
 </file>
@@ -501,136 +507,136 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="E3">
-        <v>54.44</v>
+        <v>40.75</v>
       </c>
       <c r="F3">
-        <v>177</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>1.92</v>
+        <v>9.39</v>
       </c>
       <c r="E4">
-        <v>8.59</v>
+        <v>49.94</v>
       </c>
       <c r="F4">
-        <v>165</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>28.1</v>
+        <v>5.55</v>
       </c>
       <c r="E5">
-        <v>8.85</v>
+        <v>17.98</v>
       </c>
       <c r="F5">
-        <v>164</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>34.96</v>
+        <v>42.45</v>
       </c>
       <c r="F6">
-        <v>118</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7">
-        <v>3.3</v>
+        <v>6.08</v>
       </c>
       <c r="E7">
-        <v>16.98</v>
+        <v>28.27</v>
       </c>
       <c r="F7">
-        <v>150</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="E8">
-        <v>38.15</v>
+        <v>39.76</v>
       </c>
       <c r="F8">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9">
-        <v>34.4</v>
+        <v>23.8</v>
       </c>
       <c r="E9">
-        <v>161.97</v>
-      </c>
-      <c r="F9">
-        <v>887</v>
+        <v>219.15</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
   <si>
-    <t>multi-venue - Sales Summary - 2026-08-22/2026-08-22</t>
+    <t>multi-venue - Sales Summary - 2026-08-23/2026-08-23</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -37,64 +37,64 @@
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>3,424.31</t>
-  </si>
-  <si>
-    <t>3,422.75</t>
+    <t>2,864.74</t>
+  </si>
+  <si>
+    <t>2,859.39</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>3,269.97</t>
+  </si>
+  <si>
+    <t>3,265.77</t>
   </si>
   <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>5,470.95</t>
-  </si>
-  <si>
-    <t>5,461.56</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>4,210.04</t>
-  </si>
-  <si>
-    <t>4,204.49</t>
+    <t>4,254.91</t>
+  </si>
+  <si>
+    <t>4,253.20</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>2,044.10</t>
+    <t>1,432.67</t>
   </si>
   <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>4,122.93</t>
-  </si>
-  <si>
-    <t>4,116.85</t>
+    <t>3,868.48</t>
+  </si>
+  <si>
+    <t>3,858.12</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>2,313.93</t>
-  </si>
-  <si>
-    <t>2,312.71</t>
+    <t>1,654.23</t>
+  </si>
+  <si>
+    <t>1,652.91</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>21,586.26</t>
-  </si>
-  <si>
-    <t>21,562.46</t>
-  </si>
-  <si>
-    <t>1,313</t>
+    <t>17,345.00</t>
+  </si>
+  <si>
+    <t>17,322.06</t>
+  </si>
+  <si>
+    <t>1,038</t>
   </si>
 </sst>
 </file>
@@ -510,13 +510,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>1.56</v>
+        <v>5.35</v>
       </c>
       <c r="E3">
-        <v>40.75</v>
+        <v>16.98</v>
       </c>
       <c r="F3">
-        <v>212</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -530,13 +530,13 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>9.39</v>
+        <v>4.2</v>
       </c>
       <c r="E4">
-        <v>49.94</v>
+        <v>8.99</v>
       </c>
       <c r="F4">
-        <v>297</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -550,13 +550,13 @@
         <v>15</v>
       </c>
       <c r="D5">
-        <v>5.55</v>
+        <v>1.71</v>
       </c>
       <c r="E5">
-        <v>17.98</v>
+        <v>88.3</v>
       </c>
       <c r="F5">
-        <v>280</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -573,10 +573,10 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>42.45</v>
+        <v>16.98</v>
       </c>
       <c r="F6">
-        <v>156</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -590,13 +590,13 @@
         <v>20</v>
       </c>
       <c r="D7">
-        <v>6.08</v>
+        <v>10.36</v>
       </c>
       <c r="E7">
-        <v>28.27</v>
+        <v>28.37</v>
       </c>
       <c r="F7">
-        <v>252</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -610,13 +610,13 @@
         <v>23</v>
       </c>
       <c r="D8">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="E8">
-        <v>39.76</v>
+        <v>-7.19</v>
       </c>
       <c r="F8">
-        <v>116</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -630,10 +630,10 @@
         <v>26</v>
       </c>
       <c r="D9">
-        <v>23.8</v>
+        <v>22.94</v>
       </c>
       <c r="E9">
-        <v>219.15</v>
+        <v>152.43</v>
       </c>
       <c r="F9" t="s">
         <v>27</v>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-08-23/2026-08-23</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-08-24/2026-08-24</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,67 +34,55 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,220.58</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>1,214.60</t>
+  </si>
+  <si>
+    <t>1,213.30</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>2,700.77</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>2,192.96</t>
+  </si>
+  <si>
+    <t>2,187.78</t>
+  </si>
+  <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>2,864.74</t>
-  </si>
-  <si>
-    <t>2,859.39</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>3,269.97</t>
-  </si>
-  <si>
-    <t>3,265.77</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>4,254.91</t>
-  </si>
-  <si>
-    <t>4,253.20</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,432.67</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>3,868.48</t>
-  </si>
-  <si>
-    <t>3,858.12</t>
+    <t>1,292.10</t>
+  </si>
+  <si>
+    <t>1,289.46</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,654.23</t>
-  </si>
-  <si>
-    <t>1,652.91</t>
-  </si>
-  <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>17,345.00</t>
-  </si>
-  <si>
-    <t>17,322.06</t>
-  </si>
-  <si>
-    <t>1,038</t>
+    <t>9,094.76</t>
+  </si>
+  <si>
+    <t>9,082.38</t>
   </si>
 </sst>
 </file>
@@ -507,136 +495,136 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>16.98</v>
+        <v>23.97</v>
       </c>
       <c r="F3">
-        <v>157</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
       <c r="D4">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="E4">
-        <v>8.99</v>
+        <v>7.99</v>
       </c>
       <c r="F4">
-        <v>219</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D5">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>88.3</v>
+        <v>8.85</v>
       </c>
       <c r="F5">
-        <v>235</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
         <v>16</v>
       </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
       <c r="D6">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="E6">
-        <v>16.98</v>
+        <v>34.36</v>
       </c>
       <c r="F6">
-        <v>107</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
-        <v>20</v>
-      </c>
       <c r="D7">
-        <v>10.36</v>
+        <v>2.64</v>
       </c>
       <c r="E7">
-        <v>28.37</v>
+        <v>8.79</v>
       </c>
       <c r="F7">
-        <v>230</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
+        <v>20</v>
+      </c>
+      <c r="B8">
+        <v>473.75</v>
+      </c>
+      <c r="C8">
+        <v>470.49</v>
       </c>
       <c r="D8">
-        <v>1.32</v>
+        <v>3.26</v>
       </c>
       <c r="E8">
-        <v>-7.19</v>
+        <v>2.49</v>
       </c>
       <c r="F8">
-        <v>90</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D9">
-        <v>22.94</v>
+        <v>12.38</v>
       </c>
       <c r="E9">
-        <v>152.43</v>
-      </c>
-      <c r="F9" t="s">
-        <v>27</v>
+        <v>86.45</v>
+      </c>
+      <c r="F9">
+        <v>589</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
-    <t>multi-venue - Sales Summary - 2026-08-24/2026-08-24</t>
+    <t>multi-venue - Sales Summary - 2026-08-25/2026-08-25</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,55 +34,55 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>1,324.79</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>1,133.94</t>
+  </si>
+  <si>
+    <t>1,131.74</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>2,143.52</t>
+  </si>
+  <si>
+    <t>2,139.50</t>
+  </si>
+  <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,220.58</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>1,214.60</t>
-  </si>
-  <si>
-    <t>1,213.30</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>2,700.77</t>
+    <t>1,593.42</t>
   </si>
   <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>2,192.96</t>
-  </si>
-  <si>
-    <t>2,187.78</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>1,292.10</t>
-  </si>
-  <si>
-    <t>1,289.46</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
+    <t>2,037.33</t>
+  </si>
+  <si>
+    <t>2,035.51</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>9,094.76</t>
-  </si>
-  <si>
-    <t>9,082.38</t>
+    <t>8,901.63</t>
+  </si>
+  <si>
+    <t>8,893.59</t>
   </si>
 </sst>
 </file>
@@ -491,120 +491,120 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
+      <c r="B3">
+        <v>668.63</v>
+      </c>
+      <c r="C3">
+        <v>668.63</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>23.97</v>
+        <v>11.19</v>
       </c>
       <c r="F3">
-        <v>94</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D4">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>7.99</v>
+        <v>26.37</v>
       </c>
       <c r="F4">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
       <c r="D5">
+        <v>2.2</v>
+      </c>
+      <c r="E5">
         <v>0</v>
       </c>
-      <c r="E5">
-        <v>8.85</v>
-      </c>
       <c r="F5">
-        <v>139</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
       <c r="D6">
-        <v>5.18</v>
+        <v>4.02</v>
       </c>
       <c r="E6">
-        <v>34.36</v>
+        <v>46.25</v>
       </c>
       <c r="F6">
-        <v>143</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D7">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>8.79</v>
+        <v>8.59</v>
       </c>
       <c r="F7">
-        <v>87</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
         <v>20</v>
       </c>
-      <c r="B8">
-        <v>473.75</v>
-      </c>
-      <c r="C8">
-        <v>470.49</v>
-      </c>
       <c r="D8">
-        <v>3.26</v>
+        <v>1.82</v>
       </c>
       <c r="E8">
-        <v>2.49</v>
+        <v>25.77</v>
       </c>
       <c r="F8">
-        <v>35</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -618,13 +618,13 @@
         <v>23</v>
       </c>
       <c r="D9">
-        <v>12.38</v>
+        <v>8.04</v>
       </c>
       <c r="E9">
-        <v>86.45</v>
+        <v>118.17</v>
       </c>
       <c r="F9">
-        <v>589</v>
+        <v>579</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-08-25/2026-08-25</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-08-26/2026-08-26</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -37,52 +37,55 @@
     <t>#006 Aventura, FL</t>
   </si>
   <si>
+    <t>1,065.72</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>1,465.58</t>
+  </si>
+  <si>
+    <t>1,463.68</t>
+  </si>
+  <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>1,324.79</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>1,133.94</t>
-  </si>
-  <si>
-    <t>1,131.74</t>
+    <t>1,002.98</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,105.80</t>
   </si>
   <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>2,143.52</t>
-  </si>
-  <si>
-    <t>2,139.50</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,593.42</t>
+    <t>1,581.87</t>
+  </si>
+  <si>
+    <t>1,578.20</t>
   </si>
   <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>2,037.33</t>
-  </si>
-  <si>
-    <t>2,035.51</t>
+    <t>1,566.49</t>
+  </si>
+  <si>
+    <t>1,565.99</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>8,901.63</t>
-  </si>
-  <si>
-    <t>8,893.59</t>
+    <t>7,788.44</t>
+  </si>
+  <si>
+    <t>7,778.76</t>
   </si>
 </sst>
 </file>
@@ -491,80 +494,80 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3">
-        <v>668.63</v>
-      </c>
-      <c r="C3">
-        <v>668.63</v>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>11.19</v>
+        <v>10.19</v>
       </c>
       <c r="F3">
-        <v>43</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D4">
+        <v>1.9</v>
+      </c>
+      <c r="E4">
         <v>0</v>
       </c>
-      <c r="E4">
-        <v>26.37</v>
-      </c>
       <c r="F4">
-        <v>84</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="C5">
+        <v>999.37</v>
       </c>
       <c r="D5">
-        <v>2.2</v>
+        <v>3.61</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>79</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
         <v>15</v>
       </c>
       <c r="D6">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>46.25</v>
+        <v>7.99</v>
       </c>
       <c r="F6">
-        <v>121</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -575,56 +578,56 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7">
+        <v>3.67</v>
+      </c>
+      <c r="E7">
         <v>0</v>
       </c>
-      <c r="E7">
-        <v>8.59</v>
-      </c>
       <c r="F7">
-        <v>128</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8">
-        <v>1.82</v>
+        <v>0.5</v>
       </c>
       <c r="E8">
-        <v>25.77</v>
+        <v>45.15</v>
       </c>
       <c r="F8">
-        <v>124</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D9">
-        <v>8.04</v>
+        <v>9.68</v>
       </c>
       <c r="E9">
-        <v>118.17</v>
+        <v>63.33</v>
       </c>
       <c r="F9">
-        <v>579</v>
+        <v>498</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-08-26/2026-08-26</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-08-27/2026-08-27</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,58 +34,61 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>1,432.96</t>
+  </si>
+  <si>
+    <t>1,427.51</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>2,758.30</t>
+  </si>
+  <si>
+    <t>2,742.39</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>1,141.59</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,258.52</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>2,203.92</t>
+  </si>
+  <si>
+    <t>2,196.67</t>
+  </si>
+  <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,065.72</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>1,465.58</t>
-  </si>
-  <si>
-    <t>1,463.68</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>1,002.98</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,105.80</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>1,581.87</t>
-  </si>
-  <si>
-    <t>1,578.20</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>1,566.49</t>
-  </si>
-  <si>
-    <t>1,565.99</t>
+    <t>1,050.21</t>
+  </si>
+  <si>
+    <t>1,049.29</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>7,788.44</t>
-  </si>
-  <si>
-    <t>7,778.76</t>
+    <t>9,845.50</t>
+  </si>
+  <si>
+    <t>9,815.97</t>
   </si>
 </sst>
 </file>
@@ -498,136 +501,136 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="E3">
-        <v>10.19</v>
+        <v>24.97</v>
       </c>
       <c r="F3">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>1.9</v>
+        <v>15.91</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="F4">
-        <v>99</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5">
-        <v>999.37</v>
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
       </c>
       <c r="D5">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>66</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>7.99</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>81</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>3.67</v>
+        <v>7.25</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="F7">
-        <v>88</v>
+        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>0.5</v>
+        <v>0.92</v>
       </c>
       <c r="E8">
-        <v>45.15</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>104</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9">
-        <v>9.68</v>
+        <v>29.53</v>
       </c>
       <c r="E9">
-        <v>63.33</v>
+        <v>37.51</v>
       </c>
       <c r="F9">
-        <v>498</v>
+        <v>650</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
   <si>
-    <t>multi-venue - Sales Summary - 2026-08-27/2026-08-27</t>
+    <t>multi-venue - Sales Summary - 2026-08-28/2026-08-28</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,61 +34,61 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>2,179.69</t>
+  </si>
+  <si>
+    <t>2,164.50</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>2,716.47</t>
+  </si>
+  <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>1,432.96</t>
-  </si>
-  <si>
-    <t>1,427.51</t>
+    <t>1,795.19</t>
+  </si>
+  <si>
+    <t>1,787.69</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,030.10</t>
   </si>
   <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>2,758.30</t>
-  </si>
-  <si>
-    <t>2,742.39</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>1,141.59</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,258.52</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>2,203.92</t>
-  </si>
-  <si>
-    <t>2,196.67</t>
+    <t>2,416.19</t>
+  </si>
+  <si>
+    <t>2,406.11</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,050.21</t>
-  </si>
-  <si>
-    <t>1,049.29</t>
+    <t>1,597.70</t>
+  </si>
+  <si>
+    <t>1,595.66</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>9,845.50</t>
-  </si>
-  <si>
-    <t>9,815.97</t>
+    <t>11,735.34</t>
+  </si>
+  <si>
+    <t>11,700.53</t>
   </si>
 </sst>
 </file>
@@ -504,13 +504,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>5.45</v>
+        <v>15.19</v>
       </c>
       <c r="E3">
-        <v>24.97</v>
+        <v>29.77</v>
       </c>
       <c r="F3">
-        <v>100</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -521,36 +521,36 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>15.91</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>8.85</v>
+        <v>66.92</v>
       </c>
       <c r="F4">
-        <v>148</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
         <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>9.48</v>
       </c>
       <c r="F5">
-        <v>82</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -567,10 +567,10 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>7.99</v>
       </c>
       <c r="F6">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -584,13 +584,13 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>7.25</v>
+        <v>10.08</v>
       </c>
       <c r="E7">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>159</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -604,13 +604,13 @@
         <v>22</v>
       </c>
       <c r="D8">
-        <v>0.92</v>
+        <v>2.04</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>18.38</v>
       </c>
       <c r="F8">
-        <v>66</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -624,13 +624,13 @@
         <v>25</v>
       </c>
       <c r="D9">
-        <v>29.53</v>
+        <v>34.81</v>
       </c>
       <c r="E9">
-        <v>37.51</v>
+        <v>132.54</v>
       </c>
       <c r="F9">
-        <v>650</v>
+        <v>787</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-08-28/2026-08-28</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-08-29/2026-08-29</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -37,58 +37,61 @@
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>2,179.69</t>
-  </si>
-  <si>
-    <t>2,164.50</t>
+    <t>4,180.40</t>
+  </si>
+  <si>
+    <t>4,172.92</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>4,289.48</t>
+  </si>
+  <si>
+    <t>4,284.65</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>3,656.27</t>
+  </si>
+  <si>
+    <t>3,651.77</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,349.82</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>2,251.59</t>
   </si>
   <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>2,716.47</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>1,795.19</t>
-  </si>
-  <si>
-    <t>1,787.69</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,030.10</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>2,416.19</t>
-  </si>
-  <si>
-    <t>2,406.11</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
-    <t>1,597.70</t>
-  </si>
-  <si>
-    <t>1,595.66</t>
+    <t>3,683.09</t>
+  </si>
+  <si>
+    <t>3,682.21</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>11,735.34</t>
-  </si>
-  <si>
-    <t>11,700.53</t>
+    <t>19,410.65</t>
+  </si>
+  <si>
+    <t>19,392.96</t>
+  </si>
+  <si>
+    <t>1,141</t>
   </si>
 </sst>
 </file>
@@ -504,13 +507,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>15.19</v>
+        <v>7.48</v>
       </c>
       <c r="E3">
-        <v>29.77</v>
+        <v>29.07</v>
       </c>
       <c r="F3">
-        <v>153</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -521,76 +524,76 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="E4">
-        <v>66.92</v>
+        <v>73.94</v>
       </c>
       <c r="F4">
-        <v>183</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="E5">
-        <v>9.48</v>
+        <v>53.93</v>
       </c>
       <c r="F5">
-        <v>128</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>7.99</v>
+        <v>39.95</v>
       </c>
       <c r="F6">
-        <v>87</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
       </c>
       <c r="D7">
-        <v>10.08</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>9.19</v>
       </c>
       <c r="F7">
-        <v>143</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -604,13 +607,13 @@
         <v>22</v>
       </c>
       <c r="D8">
-        <v>2.04</v>
+        <v>0.88</v>
       </c>
       <c r="E8">
-        <v>18.38</v>
+        <v>74.21</v>
       </c>
       <c r="F8">
-        <v>93</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -624,13 +627,13 @@
         <v>25</v>
       </c>
       <c r="D9">
-        <v>34.81</v>
+        <v>17.69</v>
       </c>
       <c r="E9">
-        <v>132.54</v>
-      </c>
-      <c r="F9">
-        <v>787</v>
+        <v>280.29</v>
+      </c>
+      <c r="F9" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
   <si>
-    <t>multi-venue - Sales Summary - 2026-08-29/2026-08-29</t>
+    <t>multi-venue - Sales Summary - 2026-08-30/2026-08-30</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,64 +34,64 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>3,399.90</t>
+  </si>
+  <si>
+    <t>3,399.10</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
+    <t>1,671.06</t>
+  </si>
+  <si>
+    <t>1,670.76</t>
+  </si>
+  <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>4,180.40</t>
-  </si>
-  <si>
-    <t>4,172.92</t>
+    <t>3,839.86</t>
+  </si>
+  <si>
+    <t>3,839.00</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>3,791.36</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,530.60</t>
   </si>
   <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>4,289.48</t>
-  </si>
-  <si>
-    <t>4,284.65</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>3,656.27</t>
-  </si>
-  <si>
-    <t>3,651.77</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,349.82</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
-    <t>2,251.59</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>3,683.09</t>
-  </si>
-  <si>
-    <t>3,682.21</t>
+    <t>3,467.61</t>
+  </si>
+  <si>
+    <t>3,462.14</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>19,410.65</t>
-  </si>
-  <si>
-    <t>19,392.96</t>
-  </si>
-  <si>
-    <t>1,141</t>
+    <t>17,700.39</t>
+  </si>
+  <si>
+    <t>17,692.96</t>
+  </si>
+  <si>
+    <t>1,036</t>
   </si>
 </sst>
 </file>
@@ -507,13 +507,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>7.48</v>
+        <v>0.8</v>
       </c>
       <c r="E3">
-        <v>29.07</v>
+        <v>4.99</v>
       </c>
       <c r="F3">
-        <v>266</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -527,13 +527,13 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>4.83</v>
+        <v>0.3</v>
       </c>
       <c r="E4">
-        <v>73.94</v>
+        <v>10.19</v>
       </c>
       <c r="F4">
-        <v>232</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -547,13 +547,13 @@
         <v>15</v>
       </c>
       <c r="D5">
-        <v>4.5</v>
+        <v>0.86</v>
       </c>
       <c r="E5">
-        <v>53.93</v>
+        <v>26.67</v>
       </c>
       <c r="F5">
-        <v>235</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -570,10 +570,10 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>39.95</v>
+        <v>62.73</v>
       </c>
       <c r="F6">
-        <v>101</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -590,10 +590,10 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>9.19</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -607,13 +607,13 @@
         <v>22</v>
       </c>
       <c r="D8">
-        <v>0.88</v>
+        <v>5.47</v>
       </c>
       <c r="E8">
-        <v>74.21</v>
+        <v>46.75</v>
       </c>
       <c r="F8">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -627,10 +627,10 @@
         <v>25</v>
       </c>
       <c r="D9">
-        <v>17.69</v>
+        <v>7.43</v>
       </c>
       <c r="E9">
-        <v>280.29</v>
+        <v>151.33</v>
       </c>
       <c r="F9" t="s">
         <v>26</v>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-08-30/2026-08-30</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-08-31/2026-08-31</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,64 +34,52 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#006 Aventura, FL</t>
+  </si>
+  <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>3,399.90</t>
-  </si>
-  <si>
-    <t>3,399.10</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
-  </si>
-  <si>
-    <t>1,671.06</t>
-  </si>
-  <si>
-    <t>1,670.76</t>
+    <t>1,326.07</t>
+  </si>
+  <si>
+    <t>1,325.27</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>2,289.59</t>
   </si>
   <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>3,839.86</t>
-  </si>
-  <si>
-    <t>3,839.00</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>3,791.36</t>
+    <t>1,628.21</t>
+  </si>
+  <si>
+    <t>1,627.05</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>1,754.97</t>
+  </si>
+  <si>
+    <t>1,749.82</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,530.60</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>3,467.61</t>
-  </si>
-  <si>
-    <t>3,462.14</t>
-  </si>
-  <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>17,700.39</t>
-  </si>
-  <si>
-    <t>17,692.96</t>
-  </si>
-  <si>
-    <t>1,036</t>
+    <t>8,481.04</t>
+  </si>
+  <si>
+    <t>8,473.93</t>
   </si>
 </sst>
 </file>
@@ -500,140 +488,140 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
+      <c r="B3">
+        <v>632.98</v>
+      </c>
+      <c r="C3">
+        <v>632.98</v>
       </c>
       <c r="D3">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>208</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
       <c r="D4">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="E4">
-        <v>10.19</v>
+        <v>8.99</v>
       </c>
       <c r="F4">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D5">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>26.67</v>
+        <v>80.9</v>
       </c>
       <c r="F5">
-        <v>226</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="E6">
-        <v>62.73</v>
+        <v>12.59</v>
       </c>
       <c r="F6">
-        <v>227</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
       <c r="D7">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>30.54</v>
       </c>
       <c r="F7">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>22</v>
+        <v>19</v>
+      </c>
+      <c r="B8">
+        <v>849.22</v>
+      </c>
+      <c r="C8">
+        <v>849.22</v>
       </c>
       <c r="D8">
-        <v>5.47</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>46.75</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>192</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D9">
-        <v>7.43</v>
+        <v>7.11</v>
       </c>
       <c r="E9">
-        <v>151.33</v>
-      </c>
-      <c r="F9" t="s">
-        <v>26</v>
+        <v>133.02</v>
+      </c>
+      <c r="F9">
+        <v>463</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-08-31/2026-08-31</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-09-01/2026-09-01</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,52 +34,55 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>2,057.01</t>
+  </si>
+  <si>
+    <t>2,051.03</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>1,265.00</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>1,091.88</t>
+  </si>
+  <si>
+    <t>1,091.00</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,035.61</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>1,599.32</t>
+  </si>
+  <si>
+    <t>1,593.27</t>
+  </si>
+  <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>1,326.07</t>
-  </si>
-  <si>
-    <t>1,325.27</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>2,289.59</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>1,628.21</t>
-  </si>
-  <si>
-    <t>1,627.05</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>1,754.97</t>
-  </si>
-  <si>
-    <t>1,749.82</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>8,481.04</t>
-  </si>
-  <si>
-    <t>8,473.93</t>
+    <t>7,591.40</t>
+  </si>
+  <si>
+    <t>7,577.32</t>
   </si>
 </sst>
 </file>
@@ -488,140 +491,140 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3">
-        <v>632.98</v>
-      </c>
-      <c r="C3">
-        <v>632.98</v>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>5.98</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>44</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>8.99</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>71</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="E5">
-        <v>80.9</v>
+        <v>8.99</v>
       </c>
       <c r="F5">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>12.59</v>
+        <v>15.98</v>
       </c>
       <c r="F6">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>5.15</v>
+        <v>6.05</v>
       </c>
       <c r="E7">
-        <v>30.54</v>
+        <v>27.77</v>
       </c>
       <c r="F7">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8">
-        <v>849.22</v>
+        <v>542.58</v>
       </c>
       <c r="C8">
-        <v>849.22</v>
+        <v>541.41</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>65</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9">
-        <v>7.11</v>
+        <v>14.08</v>
       </c>
       <c r="E9">
-        <v>133.02</v>
+        <v>52.74</v>
       </c>
       <c r="F9">
-        <v>463</v>
+        <v>489</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-09-01/2026-09-01</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-09-02/2026-09-02</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,43 +34,37 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>1,406.61</t>
+  </si>
+  <si>
+    <t>1,398.24</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>1,581.82</t>
+  </si>
+  <si>
+    <t>1,580.92</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>2,057.01</t>
-  </si>
-  <si>
-    <t>2,051.03</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>1,265.00</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>1,091.88</t>
-  </si>
-  <si>
-    <t>1,091.00</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,035.61</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>1,599.32</t>
-  </si>
-  <si>
-    <t>1,593.27</t>
+    <t>1,553.82</t>
+  </si>
+  <si>
+    <t>1,502.15</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
@@ -79,10 +73,10 @@
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>7,591.40</t>
-  </si>
-  <si>
-    <t>7,577.32</t>
+    <t>6,901.74</t>
+  </si>
+  <si>
+    <t>6,840.50</t>
   </si>
 </sst>
 </file>
@@ -498,10 +492,10 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>5.98</v>
+        <v>8.37</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>38.36</v>
       </c>
       <c r="F3">
         <v>102</v>
@@ -515,116 +509,116 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>41.95</v>
       </c>
       <c r="F4">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
-        <v>14</v>
+      <c r="B5">
+        <v>810.36</v>
+      </c>
+      <c r="C5">
+        <v>810.36</v>
       </c>
       <c r="D5">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>8.99</v>
+        <v>7.99</v>
       </c>
       <c r="F5">
-        <v>75</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
+        <v>14</v>
+      </c>
+      <c r="B6">
+        <v>794.99</v>
+      </c>
+      <c r="C6">
+        <v>794.99</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>15.98</v>
+        <v>3.49</v>
       </c>
       <c r="F6">
-        <v>73</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
         <v>17</v>
       </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
       <c r="D7">
-        <v>6.05</v>
+        <v>51.67</v>
       </c>
       <c r="E7">
-        <v>27.77</v>
+        <v>27.95</v>
       </c>
       <c r="F7">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B8">
-        <v>542.58</v>
+        <v>754.14</v>
       </c>
       <c r="C8">
-        <v>541.41</v>
+        <v>753.84</v>
       </c>
       <c r="D8">
-        <v>1.17</v>
+        <v>0.3</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
         <v>21</v>
       </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>23</v>
-      </c>
       <c r="D9">
-        <v>14.08</v>
+        <v>61.24</v>
       </c>
       <c r="E9">
-        <v>52.74</v>
+        <v>119.74</v>
       </c>
       <c r="F9">
-        <v>489</v>
+        <v>447</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-09-02/2026-09-02</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-09-03/2026-09-03</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -37,46 +37,40 @@
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>1,406.61</t>
-  </si>
-  <si>
-    <t>1,398.24</t>
+    <t>1,988.84</t>
+  </si>
+  <si>
+    <t>1,986.25</t>
   </si>
   <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>1,581.82</t>
-  </si>
-  <si>
-    <t>1,580.92</t>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>1,005.34</t>
+  </si>
+  <si>
+    <t>1,000.53</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>1,553.82</t>
-  </si>
-  <si>
-    <t>1,502.15</t>
-  </si>
-  <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>6,901.74</t>
-  </si>
-  <si>
-    <t>6,840.50</t>
+    <t>6,597.34</t>
+  </si>
+  <si>
+    <t>6,588.14</t>
   </si>
 </sst>
 </file>
@@ -492,133 +486,133 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>8.37</v>
+        <v>2.59</v>
       </c>
       <c r="E3">
-        <v>38.36</v>
+        <v>16.97</v>
       </c>
       <c r="F3">
-        <v>102</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
+      <c r="B4">
+        <v>960.48</v>
+      </c>
+      <c r="C4">
+        <v>958.68</v>
       </c>
       <c r="D4">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="E4">
-        <v>41.95</v>
+        <v>11.48</v>
       </c>
       <c r="F4">
-        <v>105</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B5">
-        <v>810.36</v>
+        <v>878.93</v>
       </c>
       <c r="C5">
-        <v>810.36</v>
+        <v>878.93</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>7.99</v>
+        <v>43.37</v>
       </c>
       <c r="F5">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
         <v>14</v>
       </c>
-      <c r="B6">
-        <v>794.99</v>
-      </c>
-      <c r="C6">
-        <v>794.99</v>
-      </c>
       <c r="D6">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="E6">
-        <v>3.49</v>
+        <v>2.99</v>
       </c>
       <c r="F6">
-        <v>45</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
+      <c r="B7">
+        <v>994.11</v>
+      </c>
+      <c r="C7">
+        <v>994.11</v>
       </c>
       <c r="D7">
-        <v>51.67</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>27.95</v>
+        <v>39.95</v>
       </c>
       <c r="F7">
-        <v>89</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B8">
-        <v>754.14</v>
+        <v>769.64</v>
       </c>
       <c r="C8">
-        <v>753.84</v>
+        <v>769.64</v>
       </c>
       <c r="D8">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>9.19</v>
       </c>
       <c r="F8">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
         <v>19</v>
       </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>21</v>
-      </c>
       <c r="D9">
-        <v>61.24</v>
+        <v>9.2</v>
       </c>
       <c r="E9">
-        <v>119.74</v>
+        <v>123.95</v>
       </c>
       <c r="F9">
-        <v>447</v>
+        <v>456</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-09-03/2026-09-03</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-09-04/2026-09-04</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,43 +34,58 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>2,042.97</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>2,202.44</t>
+  </si>
+  <si>
+    <t>2,196.63</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>1,515.98</t>
+  </si>
+  <si>
+    <t>1,515.18</t>
+  </si>
+  <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>1,988.84</t>
-  </si>
-  <si>
-    <t>1,986.25</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>1,005.34</t>
-  </si>
-  <si>
-    <t>1,000.53</t>
+    <t>2,345.82</t>
+  </si>
+  <si>
+    <t>2,342.97</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
+    <t>1,077.08</t>
+  </si>
+  <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
+    <t>1,260.86</t>
+  </si>
+  <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>6,597.34</t>
-  </si>
-  <si>
-    <t>6,588.14</t>
+    <t>10,445.15</t>
+  </si>
+  <si>
+    <t>10,435.69</t>
   </si>
 </sst>
 </file>
@@ -483,13 +498,13 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>16.97</v>
+        <v>90.69</v>
       </c>
       <c r="F3">
         <v>131</v>
@@ -497,93 +512,93 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="B4">
-        <v>960.48</v>
-      </c>
-      <c r="C4">
-        <v>958.68</v>
+      <c r="C4" t="s">
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>1.8</v>
+        <v>5.81</v>
       </c>
       <c r="E4">
-        <v>11.48</v>
+        <v>17.7</v>
       </c>
       <c r="F4">
-        <v>72</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5">
-        <v>878.93</v>
-      </c>
-      <c r="C5">
-        <v>878.93</v>
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E5">
-        <v>43.37</v>
+        <v>17.68</v>
       </c>
       <c r="F5">
-        <v>69</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D6">
-        <v>4.81</v>
+        <v>2.85</v>
       </c>
       <c r="E6">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>62</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7">
-        <v>994.11</v>
-      </c>
-      <c r="C7">
-        <v>994.11</v>
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>39.95</v>
+        <v>16.98</v>
       </c>
       <c r="F7">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8">
-        <v>769.64</v>
-      </c>
-      <c r="C8">
-        <v>769.64</v>
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -592,27 +607,27 @@
         <v>9.19</v>
       </c>
       <c r="F8">
-        <v>47</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D9">
-        <v>9.2</v>
+        <v>9.46</v>
       </c>
       <c r="E9">
-        <v>123.95</v>
+        <v>152.24</v>
       </c>
       <c r="F9">
-        <v>456</v>
+        <v>667</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-09-04/2026-09-04</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-09-05/2026-09-05</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,58 +34,64 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>5,057.09</t>
+  </si>
+  <si>
+    <t>5,041.60</t>
+  </si>
+  <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>4,338.48</t>
+  </si>
+  <si>
+    <t>4,337.68</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,817.59</t>
+  </si>
+  <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>2,042.97</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>2,202.44</t>
-  </si>
-  <si>
-    <t>2,196.63</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>1,515.98</t>
-  </si>
-  <si>
-    <t>1,515.18</t>
+    <t>3,264.67</t>
+  </si>
+  <si>
+    <t>3,259.79</t>
   </si>
   <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>2,345.82</t>
-  </si>
-  <si>
-    <t>2,342.97</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,077.08</t>
+    <t>4,092.30</t>
+  </si>
+  <si>
+    <t>4,086.78</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,260.86</t>
+    <t>1,653.32</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>10,445.15</t>
-  </si>
-  <si>
-    <t>10,435.69</t>
+    <t>20,223.45</t>
+  </si>
+  <si>
+    <t>20,196.76</t>
+  </si>
+  <si>
+    <t>1,215</t>
   </si>
 </sst>
 </file>
@@ -498,56 +504,56 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>15.49</v>
       </c>
       <c r="E3">
-        <v>90.69</v>
+        <v>83.09</v>
       </c>
       <c r="F3">
-        <v>131</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>5.81</v>
+        <v>0.8</v>
       </c>
       <c r="E4">
-        <v>17.7</v>
+        <v>14.97</v>
       </c>
       <c r="F4">
-        <v>119</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
       </c>
       <c r="D5">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>17.68</v>
+        <v>17.58</v>
       </c>
       <c r="F5">
-        <v>106</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -561,13 +567,13 @@
         <v>17</v>
       </c>
       <c r="D6">
-        <v>2.85</v>
+        <v>4.88</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>27.96</v>
       </c>
       <c r="F6">
-        <v>152</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -578,56 +584,56 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="E7">
-        <v>16.98</v>
+        <v>47.64</v>
       </c>
       <c r="F7">
-        <v>82</v>
+        <v>242</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>9.19</v>
+        <v>19.38</v>
       </c>
       <c r="F8">
-        <v>77</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9">
-        <v>9.46</v>
+        <v>26.69</v>
       </c>
       <c r="E9">
-        <v>152.24</v>
-      </c>
-      <c r="F9">
-        <v>667</v>
+        <v>210.62</v>
+      </c>
+      <c r="F9" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
   <si>
-    <t>multi-venue - Sales Summary - 2026-09-05/2026-09-05</t>
+    <t>multi-venue - Sales Summary - 2026-09-06/2026-09-06</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,64 +34,64 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>3,398.64</t>
+  </si>
+  <si>
+    <t>3,396.74</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>4,127.88</t>
+  </si>
+  <si>
+    <t>4,125.34</t>
+  </si>
+  <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>5,057.09</t>
-  </si>
-  <si>
-    <t>5,041.60</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>4,338.48</t>
-  </si>
-  <si>
-    <t>4,337.68</t>
+    <t>4,751.51</t>
+  </si>
+  <si>
+    <t>4,740.65</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>3,937.27</t>
+  </si>
+  <si>
+    <t>3,928.90</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,817.59</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>3,264.67</t>
-  </si>
-  <si>
-    <t>3,259.79</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>4,092.30</t>
-  </si>
-  <si>
-    <t>4,086.78</t>
+    <t>1,563.24</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,653.32</t>
+    <t>2,207.19</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>20,223.45</t>
-  </si>
-  <si>
-    <t>20,196.76</t>
-  </si>
-  <si>
-    <t>1,215</t>
+    <t>19,985.73</t>
+  </si>
+  <si>
+    <t>19,962.06</t>
+  </si>
+  <si>
+    <t>1,154</t>
   </si>
 </sst>
 </file>
@@ -507,13 +507,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>15.49</v>
+        <v>1.9</v>
       </c>
       <c r="E3">
-        <v>83.09</v>
+        <v>36.55</v>
       </c>
       <c r="F3">
-        <v>269</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -527,13 +527,13 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>0.8</v>
+        <v>2.54</v>
       </c>
       <c r="E4">
-        <v>14.97</v>
+        <v>58.33</v>
       </c>
       <c r="F4">
-        <v>272</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -544,56 +544,56 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>10.86</v>
       </c>
       <c r="E5">
-        <v>17.58</v>
+        <v>159.79</v>
       </c>
       <c r="F5">
-        <v>142</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6">
-        <v>4.88</v>
+        <v>8.37</v>
       </c>
       <c r="E6">
-        <v>27.96</v>
+        <v>26.77</v>
       </c>
       <c r="F6">
-        <v>190</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
       </c>
       <c r="D7">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>47.64</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>242</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -610,10 +610,10 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>19.38</v>
+        <v>1.99</v>
       </c>
       <c r="F8">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -627,10 +627,10 @@
         <v>25</v>
       </c>
       <c r="D9">
-        <v>26.69</v>
+        <v>23.67</v>
       </c>
       <c r="E9">
-        <v>210.62</v>
+        <v>283.43</v>
       </c>
       <c r="F9" t="s">
         <v>26</v>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-09-06/2026-09-06</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-09-07/2026-09-07</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,64 +34,58 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>1,691.20</t>
+  </si>
+  <si>
+    <t>1,689.44</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>4,287.10</t>
+  </si>
+  <si>
+    <t>4,279.70</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>3,682.64</t>
+  </si>
+  <si>
+    <t>3,669.46</t>
+  </si>
+  <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>3,398.64</t>
-  </si>
-  <si>
-    <t>3,396.74</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>4,127.88</t>
-  </si>
-  <si>
-    <t>4,125.34</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>4,751.51</t>
-  </si>
-  <si>
-    <t>4,740.65</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>3,937.27</t>
-  </si>
-  <si>
-    <t>3,928.90</t>
+    <t>3,083.42</t>
+  </si>
+  <si>
+    <t>3,079.92</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,563.24</t>
+    <t>1,689.52</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>2,207.19</t>
-  </si>
-  <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>19,985.73</t>
-  </si>
-  <si>
-    <t>19,962.06</t>
-  </si>
-  <si>
-    <t>1,154</t>
+    <t>15,236.91</t>
+  </si>
+  <si>
+    <t>15,210.05</t>
   </si>
 </sst>
 </file>
@@ -507,13 +501,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="E3">
-        <v>36.55</v>
+        <v>44.15</v>
       </c>
       <c r="F3">
-        <v>204</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -527,13 +521,13 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>2.54</v>
+        <v>7.4</v>
       </c>
       <c r="E4">
-        <v>58.33</v>
+        <v>115.1</v>
       </c>
       <c r="F4">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -547,13 +541,13 @@
         <v>15</v>
       </c>
       <c r="D5">
-        <v>10.86</v>
+        <v>13.18</v>
       </c>
       <c r="E5">
-        <v>159.79</v>
+        <v>7.38</v>
       </c>
       <c r="F5">
-        <v>254</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -567,13 +561,13 @@
         <v>18</v>
       </c>
       <c r="D6">
-        <v>8.37</v>
+        <v>3.5</v>
       </c>
       <c r="E6">
-        <v>26.77</v>
+        <v>33.96</v>
       </c>
       <c r="F6">
-        <v>240</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -590,50 +584,50 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>17.98</v>
       </c>
       <c r="F7">
-        <v>118</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>22</v>
+      <c r="B8">
+        <v>803.03</v>
+      </c>
+      <c r="C8">
+        <v>802.01</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="E8">
-        <v>1.99</v>
+        <v>30.57</v>
       </c>
       <c r="F8">
-        <v>110</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
         <v>23</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>24</v>
       </c>
-      <c r="C9" t="s">
-        <v>25</v>
-      </c>
       <c r="D9">
-        <v>23.67</v>
+        <v>26.86</v>
       </c>
       <c r="E9">
-        <v>283.43</v>
-      </c>
-      <c r="F9" t="s">
-        <v>26</v>
+        <v>249.14</v>
+      </c>
+      <c r="F9">
+        <v>949</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-09-07/2026-09-07</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-09-08/2026-09-08</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,58 +34,43 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#001 Florida Mall Orlando FL</t>
+  </si>
+  <si>
+    <t>1,175.25</t>
+  </si>
+  <si>
+    <t>1,173.65</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>1,691.20</t>
-  </si>
-  <si>
-    <t>1,689.44</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>4,287.10</t>
-  </si>
-  <si>
-    <t>4,279.70</t>
-  </si>
-  <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>3,682.64</t>
-  </si>
-  <si>
-    <t>3,669.46</t>
-  </si>
-  <si>
-    <t>#001 Florida Mall Orlando FL</t>
-  </si>
-  <si>
-    <t>3,083.42</t>
-  </si>
-  <si>
-    <t>3,079.92</t>
+    <t>1,824.47</t>
+  </si>
+  <si>
+    <t>1,821.95</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,689.52</t>
-  </si>
-  <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>15,236.91</t>
-  </si>
-  <si>
-    <t>15,210.05</t>
+    <t>5,891.53</t>
+  </si>
+  <si>
+    <t>5,883.13</t>
   </si>
 </sst>
 </file>
@@ -501,133 +486,133 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="E3">
-        <v>44.15</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>103</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
+      <c r="B4">
+        <v>738.09</v>
+      </c>
+      <c r="C4">
+        <v>734.71</v>
       </c>
       <c r="D4">
-        <v>7.4</v>
+        <v>3.38</v>
       </c>
       <c r="E4">
-        <v>115.1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>223</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>723.82</v>
+      </c>
+      <c r="C5">
+        <v>722.92</v>
       </c>
       <c r="D5">
-        <v>13.18</v>
+        <v>0.9</v>
       </c>
       <c r="E5">
-        <v>7.38</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>237</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D6">
-        <v>3.5</v>
+        <v>2.52</v>
       </c>
       <c r="E6">
-        <v>33.96</v>
+        <v>8.59</v>
       </c>
       <c r="F6">
-        <v>202</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>20</v>
+        <v>15</v>
+      </c>
+      <c r="B7">
+        <v>856.48</v>
+      </c>
+      <c r="C7">
+        <v>856.48</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>17.98</v>
+        <v>3.99</v>
       </c>
       <c r="F7">
-        <v>131</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B8">
-        <v>803.03</v>
+        <v>573.42</v>
       </c>
       <c r="C8">
-        <v>802.01</v>
+        <v>573.42</v>
       </c>
       <c r="D8">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>30.57</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>53</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D9">
-        <v>26.86</v>
+        <v>8.4</v>
       </c>
       <c r="E9">
-        <v>249.14</v>
+        <v>12.58</v>
       </c>
       <c r="F9">
-        <v>949</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-09-08/2026-09-08</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-09-09/2026-09-09</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -37,40 +37,46 @@
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>1,175.25</t>
-  </si>
-  <si>
-    <t>1,173.65</t>
+    <t>1,351.58</t>
+  </si>
+  <si>
+    <t>1,350.68</t>
+  </si>
+  <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>1,006.75</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,265.83</t>
+  </si>
+  <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>1,727.80</t>
+  </si>
+  <si>
+    <t>1,724.79</t>
   </si>
   <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>1,824.47</t>
-  </si>
-  <si>
-    <t>1,821.95</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>5,891.53</t>
-  </si>
-  <si>
-    <t>5,883.13</t>
+    <t>6,302.94</t>
+  </si>
+  <si>
+    <t>6,294.58</t>
   </si>
 </sst>
 </file>
@@ -486,133 +492,133 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="F3">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4">
-        <v>738.09</v>
-      </c>
-      <c r="C4">
-        <v>734.71</v>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>43.05</v>
       </c>
       <c r="F4">
-        <v>48</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5">
-        <v>723.82</v>
-      </c>
-      <c r="C5">
-        <v>722.92</v>
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
       </c>
       <c r="D5">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>26.97</v>
       </c>
       <c r="F5">
-        <v>49</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D6">
-        <v>2.52</v>
+        <v>3.01</v>
       </c>
       <c r="E6">
         <v>8.59</v>
       </c>
       <c r="F6">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7">
-        <v>856.48</v>
+        <v>526.63</v>
       </c>
       <c r="C7">
-        <v>856.48</v>
+        <v>522.18</v>
       </c>
       <c r="D7">
+        <v>4.45</v>
+      </c>
+      <c r="E7">
         <v>0</v>
       </c>
-      <c r="E7">
-        <v>3.99</v>
-      </c>
       <c r="F7">
-        <v>66</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B8">
-        <v>573.42</v>
+        <v>424.35</v>
       </c>
       <c r="C8">
-        <v>573.42</v>
+        <v>424.35</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>9.19</v>
       </c>
       <c r="F8">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D9">
-        <v>8.4</v>
+        <v>8.36</v>
       </c>
       <c r="E9">
-        <v>12.58</v>
+        <v>91.39</v>
       </c>
       <c r="F9">
-        <v>388</v>
+        <v>450</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-09-09/2026-09-09</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-09-10/2026-09-10</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,49 +34,46 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#003 Sawgrass Mills Mall FL</t>
+  </si>
+  <si>
+    <t>1,537.52</t>
+  </si>
+  <si>
+    <t>1,530.96</t>
+  </si>
+  <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>1,351.58</t>
-  </si>
-  <si>
-    <t>1,350.68</t>
+    <t>1,613.28</t>
+  </si>
+  <si>
+    <t>1,609.88</t>
   </si>
   <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
-    <t>1,006.75</t>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>#006 Aventura, FL</t>
   </si>
   <si>
     <t>Lucciano's Vineland 2026</t>
   </si>
   <si>
-    <t>1,265.83</t>
-  </si>
-  <si>
-    <t>#003 Sawgrass Mills Mall FL</t>
-  </si>
-  <si>
-    <t>1,727.80</t>
-  </si>
-  <si>
-    <t>1,724.79</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>#006 Aventura, FL</t>
+    <t>1,389.23</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>6,302.94</t>
-  </si>
-  <si>
-    <t>6,294.58</t>
+    <t>6,597.12</t>
+  </si>
+  <si>
+    <t>6,578.84</t>
   </si>
 </sst>
 </file>
@@ -492,13 +489,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>0.9</v>
+        <v>6.56</v>
       </c>
       <c r="E3">
-        <v>3.59</v>
+        <v>9.59</v>
       </c>
       <c r="F3">
-        <v>100</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -509,116 +506,116 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4">
+        <v>3.4</v>
+      </c>
+      <c r="E4">
         <v>0</v>
       </c>
-      <c r="E4">
-        <v>43.05</v>
-      </c>
       <c r="F4">
-        <v>75</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
-        <v>13</v>
+      <c r="B5">
+        <v>810.55</v>
+      </c>
+      <c r="C5">
+        <v>810.55</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>26.97</v>
+        <v>8.79</v>
       </c>
       <c r="F5">
-        <v>96</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
+      <c r="B6">
+        <v>495.74</v>
+      </c>
+      <c r="C6">
+        <v>488.4</v>
       </c>
       <c r="D6">
-        <v>3.01</v>
+        <v>7.34</v>
       </c>
       <c r="E6">
-        <v>8.59</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>115</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B7">
-        <v>526.63</v>
+        <v>750.8</v>
       </c>
       <c r="C7">
-        <v>522.18</v>
+        <v>749.82</v>
       </c>
       <c r="D7">
-        <v>4.45</v>
+        <v>0.98</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>20.37</v>
       </c>
       <c r="F7">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8">
-        <v>424.35</v>
-      </c>
-      <c r="C8">
-        <v>424.35</v>
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>9.19</v>
+        <v>17.98</v>
       </c>
       <c r="F8">
-        <v>28</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
         <v>19</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>20</v>
       </c>
-      <c r="C9" t="s">
-        <v>21</v>
-      </c>
       <c r="D9">
-        <v>8.36</v>
+        <v>18.28</v>
       </c>
       <c r="E9">
-        <v>91.39</v>
+        <v>56.73</v>
       </c>
       <c r="F9">
-        <v>450</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-09-10/2026-09-10</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-09-11/2026-09-11</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -37,43 +37,61 @@
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>1,537.52</t>
-  </si>
-  <si>
-    <t>1,530.96</t>
+    <t>2,113.17</t>
+  </si>
+  <si>
+    <t>2,108.17</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,211.84</t>
   </si>
   <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>1,613.28</t>
-  </si>
-  <si>
-    <t>1,609.88</t>
+    <t>1,910.01</t>
+  </si>
+  <si>
+    <t>1,907.23</t>
   </si>
   <si>
     <t>#004 Weston Town Center FL</t>
   </si>
   <si>
+    <t>2,380.86</t>
+  </si>
+  <si>
+    <t>2,379.10</t>
+  </si>
+  <si>
     <t>#002 American Dream Mall NJ</t>
   </si>
   <si>
+    <t>1,091.27</t>
+  </si>
+  <si>
+    <t>1,087.99</t>
+  </si>
+  <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,389.23</t>
+    <t>1,324.59</t>
+  </si>
+  <si>
+    <t>1,319.49</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>6,597.12</t>
-  </si>
-  <si>
-    <t>6,578.84</t>
+    <t>10,031.74</t>
+  </si>
+  <si>
+    <t>10,013.82</t>
   </si>
 </sst>
 </file>
@@ -489,13 +507,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>6.56</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>9.59</v>
+        <v>39.21</v>
       </c>
       <c r="F3">
-        <v>117</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -506,116 +524,116 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>80.91</v>
       </c>
       <c r="F4">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="B5">
-        <v>810.55</v>
-      </c>
-      <c r="C5">
-        <v>810.55</v>
+      <c r="C5" t="s">
+        <v>14</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="E5">
-        <v>8.79</v>
+        <v>23.97</v>
       </c>
       <c r="F5">
-        <v>53</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6">
-        <v>495.74</v>
-      </c>
-      <c r="C6">
-        <v>488.4</v>
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
       </c>
       <c r="D6">
-        <v>7.34</v>
+        <v>1.76</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>57.73</v>
       </c>
       <c r="F6">
-        <v>34</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7">
-        <v>750.8</v>
-      </c>
-      <c r="C7">
-        <v>749.82</v>
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
       </c>
       <c r="D7">
-        <v>0.98</v>
+        <v>3.28</v>
       </c>
       <c r="E7">
-        <v>20.37</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>43</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="E8">
-        <v>17.98</v>
+        <v>18.16</v>
       </c>
       <c r="F8">
-        <v>113</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D9">
-        <v>18.28</v>
+        <v>17.92</v>
       </c>
       <c r="E9">
-        <v>56.73</v>
+        <v>219.98</v>
       </c>
       <c r="F9">
-        <v>470</v>
+        <v>698</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
-  <si>
-    <t>multi-venue - Sales Summary - 2026-09-11/2026-09-11</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
+  <si>
+    <t>multi-venue - Sales Summary - 2026-09-12/2026-09-12</t>
   </si>
   <si>
     <t>Venue Name</t>
@@ -34,64 +34,64 @@
     <t>Bill Count</t>
   </si>
   <si>
+    <t>#004 Weston Town Center FL</t>
+  </si>
+  <si>
+    <t>3,004.77</t>
+  </si>
+  <si>
+    <t>3,001.55</t>
+  </si>
+  <si>
+    <t>Lucciano's Vineland 2026</t>
+  </si>
+  <si>
+    <t>1,627.38</t>
+  </si>
+  <si>
     <t>#003 Sawgrass Mills Mall FL</t>
   </si>
   <si>
-    <t>2,113.17</t>
-  </si>
-  <si>
-    <t>2,108.17</t>
-  </si>
-  <si>
-    <t>Lucciano's Vineland 2026</t>
-  </si>
-  <si>
-    <t>1,211.84</t>
+    <t>3,783.26</t>
+  </si>
+  <si>
+    <t>3,777.10</t>
+  </si>
+  <si>
+    <t>#002 American Dream Mall NJ</t>
+  </si>
+  <si>
+    <t>3,249.28</t>
+  </si>
+  <si>
+    <t>3,234.30</t>
   </si>
   <si>
     <t>#001 Florida Mall Orlando FL</t>
   </si>
   <si>
-    <t>1,910.01</t>
-  </si>
-  <si>
-    <t>1,907.23</t>
-  </si>
-  <si>
-    <t>#004 Weston Town Center FL</t>
-  </si>
-  <si>
-    <t>2,380.86</t>
-  </si>
-  <si>
-    <t>2,379.10</t>
-  </si>
-  <si>
-    <t>#002 American Dream Mall NJ</t>
-  </si>
-  <si>
-    <t>1,091.27</t>
-  </si>
-  <si>
-    <t>1,087.99</t>
+    <t>3,738.50</t>
+  </si>
+  <si>
+    <t>3,735.90</t>
   </si>
   <si>
     <t>#006 Aventura, FL</t>
   </si>
   <si>
-    <t>1,324.59</t>
-  </si>
-  <si>
-    <t>1,319.49</t>
+    <t>1,632.67</t>
   </si>
   <si>
     <t>REPORT SUMMARY (6 entries)</t>
   </si>
   <si>
-    <t>10,031.74</t>
-  </si>
-  <si>
-    <t>10,013.82</t>
+    <t>17,035.86</t>
+  </si>
+  <si>
+    <t>17,008.90</t>
+  </si>
+  <si>
+    <t>1,063</t>
   </si>
 </sst>
 </file>
@@ -507,13 +507,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>3.22</v>
       </c>
       <c r="E3">
-        <v>39.21</v>
+        <v>67.32</v>
       </c>
       <c r="F3">
-        <v>142</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -530,10 +530,10 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>80.91</v>
+        <v>26.97</v>
       </c>
       <c r="F4">
-        <v>107</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -547,13 +547,13 @@
         <v>14</v>
       </c>
       <c r="D5">
-        <v>2.78</v>
+        <v>6.16</v>
       </c>
       <c r="E5">
-        <v>23.97</v>
+        <v>35.36</v>
       </c>
       <c r="F5">
-        <v>140</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -567,13 +567,13 @@
         <v>17</v>
       </c>
       <c r="D6">
-        <v>1.76</v>
+        <v>14.98</v>
       </c>
       <c r="E6">
-        <v>57.73</v>
+        <v>21.3</v>
       </c>
       <c r="F6">
-        <v>166</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -587,13 +587,13 @@
         <v>20</v>
       </c>
       <c r="D7">
-        <v>3.28</v>
+        <v>2.6</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>13.48</v>
       </c>
       <c r="F7">
-        <v>74</v>
+        <v>253</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -604,36 +604,36 @@
         <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>18.16</v>
+        <v>21.37</v>
       </c>
       <c r="F8">
-        <v>69</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
         <v>24</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>25</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9">
+        <v>26.96</v>
+      </c>
+      <c r="E9">
+        <v>185.8</v>
+      </c>
+      <c r="F9" t="s">
         <v>26</v>
-      </c>
-      <c r="D9">
-        <v>17.92</v>
-      </c>
-      <c r="E9">
-        <v>219.98</v>
-      </c>
-      <c r="F9">
-        <v>698</v>
       </c>
     </row>
   </sheetData>
